--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/AssetSvrBussRepAssetCreditNonstdInfo.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/AssetSvrBussRepAssetCreditNonstdInfo.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\华夏\需求文档\需求确认材料\数据补录模板\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\code\huaxia\tams-svreport-parent\tams-svreport\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -20,9 +20,6 @@
     <sheet name="币种填写规则" sheetId="6" r:id="rId6"/>
     <sheet name="枚举值" sheetId="7" r:id="rId7"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId8"/>
-  </externalReferences>
   <definedNames>
     <definedName name="_C01境内存款">枚举值!$B$18</definedName>
     <definedName name="_C02境外存款">枚举值!$B$19</definedName>
@@ -73,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1542" uniqueCount="1393">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1544" uniqueCount="1393">
   <si>
     <t>公共信息（必填）</t>
   </si>
@@ -6213,135 +6210,6 @@
       <alignment horizontal="right"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="22" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="23" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="14" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="15" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="49" fontId="2" fillId="6" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -6372,10 +6240,139 @@
       <alignment horizontal="right"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="22" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="23" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="14" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="15" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -6397,19 +6394,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="CHB_ASSET_INFO_ENUM"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6748,7 +6732,7 @@
     <col min="2" max="2" width="15.375" style="61"/>
     <col min="3" max="3" width="16.5" style="61" customWidth="1"/>
     <col min="4" max="4" width="18.5" style="61" customWidth="1"/>
-    <col min="5" max="5" width="9.875" style="61" customWidth="1"/>
+    <col min="5" max="5" width="19.5" style="61" customWidth="1"/>
     <col min="6" max="6" width="18.125" style="61" customWidth="1"/>
     <col min="7" max="7" width="19.75" style="61" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="13.625" style="61" customWidth="1"/>
@@ -6760,7 +6744,7 @@
     <col min="14" max="14" width="19.875" style="61" customWidth="1"/>
     <col min="15" max="15" width="9" style="73"/>
     <col min="16" max="17" width="9" style="72"/>
-    <col min="18" max="18" width="21.875" style="124" customWidth="1"/>
+    <col min="18" max="18" width="21.875" style="81" customWidth="1"/>
     <col min="19" max="19" width="21.875" style="72" customWidth="1"/>
     <col min="20" max="20" width="18.875" style="61" customWidth="1"/>
     <col min="21" max="21" width="11.875" style="61" customWidth="1"/>
@@ -6786,11 +6770,11 @@
     <col min="49" max="49" width="19.375" style="61" customWidth="1"/>
     <col min="50" max="51" width="14.5" style="61" customWidth="1"/>
     <col min="52" max="54" width="16.625" style="61" customWidth="1"/>
-    <col min="55" max="55" width="16.625" style="124" customWidth="1"/>
+    <col min="55" max="55" width="16.625" style="81" customWidth="1"/>
     <col min="56" max="56" width="20.25" style="61" customWidth="1"/>
     <col min="57" max="57" width="16.625" style="61" customWidth="1"/>
     <col min="58" max="60" width="19.5" style="61" customWidth="1"/>
-    <col min="61" max="61" width="19.5" style="124" customWidth="1"/>
+    <col min="61" max="61" width="19.5" style="81" customWidth="1"/>
     <col min="62" max="62" width="19.5" style="61" customWidth="1"/>
     <col min="63" max="63" width="19.5" style="73" customWidth="1"/>
     <col min="64" max="64" width="14" style="61" customWidth="1"/>
@@ -6808,90 +6792,90 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:78" s="58" customFormat="1" ht="14.25" thickBot="1">
-      <c r="A1" s="74" t="s">
+      <c r="A1" s="82" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="75"/>
-      <c r="D1" s="75"/>
-      <c r="E1" s="76"/>
-      <c r="F1" s="125" t="s">
+      <c r="B1" s="83"/>
+      <c r="C1" s="83"/>
+      <c r="D1" s="83"/>
+      <c r="E1" s="84"/>
+      <c r="F1" s="86" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="126"/>
-      <c r="H1" s="126"/>
-      <c r="I1" s="126"/>
-      <c r="J1" s="126"/>
-      <c r="K1" s="126"/>
-      <c r="L1" s="126"/>
-      <c r="M1" s="126"/>
-      <c r="N1" s="126"/>
-      <c r="O1" s="126"/>
-      <c r="P1" s="126"/>
-      <c r="Q1" s="126"/>
-      <c r="R1" s="126"/>
-      <c r="S1" s="126"/>
-      <c r="T1" s="126"/>
-      <c r="U1" s="126"/>
-      <c r="V1" s="126"/>
-      <c r="W1" s="126"/>
-      <c r="X1" s="126"/>
-      <c r="Y1" s="126"/>
-      <c r="Z1" s="126"/>
-      <c r="AA1" s="126"/>
-      <c r="AB1" s="126"/>
-      <c r="AC1" s="126"/>
-      <c r="AD1" s="126"/>
-      <c r="AE1" s="126"/>
-      <c r="AF1" s="126"/>
-      <c r="AG1" s="126"/>
-      <c r="AH1" s="126"/>
-      <c r="AI1" s="126"/>
-      <c r="AJ1" s="126"/>
-      <c r="AK1" s="126"/>
-      <c r="AL1" s="126"/>
-      <c r="AM1" s="126"/>
-      <c r="AN1" s="126"/>
-      <c r="AO1" s="126"/>
-      <c r="AP1" s="126"/>
-      <c r="AQ1" s="126"/>
-      <c r="AR1" s="126"/>
-      <c r="AS1" s="126"/>
-      <c r="AT1" s="126"/>
-      <c r="AU1" s="126"/>
-      <c r="AV1" s="126"/>
-      <c r="AW1" s="126"/>
-      <c r="AX1" s="126"/>
-      <c r="AY1" s="126"/>
-      <c r="AZ1" s="126"/>
-      <c r="BA1" s="126"/>
-      <c r="BB1" s="126"/>
-      <c r="BC1" s="126"/>
-      <c r="BD1" s="126"/>
-      <c r="BE1" s="126"/>
-      <c r="BF1" s="126"/>
-      <c r="BG1" s="126"/>
-      <c r="BH1" s="126"/>
-      <c r="BI1" s="126"/>
-      <c r="BJ1" s="126"/>
-      <c r="BK1" s="126"/>
-      <c r="BL1" s="126"/>
-      <c r="BM1" s="126"/>
-      <c r="BN1" s="126"/>
-      <c r="BO1" s="126"/>
-      <c r="BP1" s="126"/>
-      <c r="BQ1" s="126"/>
-      <c r="BR1" s="126"/>
-      <c r="BS1" s="126"/>
-      <c r="BT1" s="126"/>
-      <c r="BU1" s="126"/>
-      <c r="BV1" s="126"/>
-      <c r="BW1" s="126"/>
-      <c r="BX1" s="77" t="s">
+      <c r="G1" s="87"/>
+      <c r="H1" s="87"/>
+      <c r="I1" s="87"/>
+      <c r="J1" s="87"/>
+      <c r="K1" s="87"/>
+      <c r="L1" s="87"/>
+      <c r="M1" s="87"/>
+      <c r="N1" s="87"/>
+      <c r="O1" s="87"/>
+      <c r="P1" s="87"/>
+      <c r="Q1" s="87"/>
+      <c r="R1" s="87"/>
+      <c r="S1" s="87"/>
+      <c r="T1" s="87"/>
+      <c r="U1" s="87"/>
+      <c r="V1" s="87"/>
+      <c r="W1" s="87"/>
+      <c r="X1" s="87"/>
+      <c r="Y1" s="87"/>
+      <c r="Z1" s="87"/>
+      <c r="AA1" s="87"/>
+      <c r="AB1" s="87"/>
+      <c r="AC1" s="87"/>
+      <c r="AD1" s="87"/>
+      <c r="AE1" s="87"/>
+      <c r="AF1" s="87"/>
+      <c r="AG1" s="87"/>
+      <c r="AH1" s="87"/>
+      <c r="AI1" s="87"/>
+      <c r="AJ1" s="87"/>
+      <c r="AK1" s="87"/>
+      <c r="AL1" s="87"/>
+      <c r="AM1" s="87"/>
+      <c r="AN1" s="87"/>
+      <c r="AO1" s="87"/>
+      <c r="AP1" s="87"/>
+      <c r="AQ1" s="87"/>
+      <c r="AR1" s="87"/>
+      <c r="AS1" s="87"/>
+      <c r="AT1" s="87"/>
+      <c r="AU1" s="87"/>
+      <c r="AV1" s="87"/>
+      <c r="AW1" s="87"/>
+      <c r="AX1" s="87"/>
+      <c r="AY1" s="87"/>
+      <c r="AZ1" s="87"/>
+      <c r="BA1" s="87"/>
+      <c r="BB1" s="87"/>
+      <c r="BC1" s="87"/>
+      <c r="BD1" s="87"/>
+      <c r="BE1" s="87"/>
+      <c r="BF1" s="87"/>
+      <c r="BG1" s="87"/>
+      <c r="BH1" s="87"/>
+      <c r="BI1" s="87"/>
+      <c r="BJ1" s="87"/>
+      <c r="BK1" s="87"/>
+      <c r="BL1" s="87"/>
+      <c r="BM1" s="87"/>
+      <c r="BN1" s="87"/>
+      <c r="BO1" s="87"/>
+      <c r="BP1" s="87"/>
+      <c r="BQ1" s="87"/>
+      <c r="BR1" s="87"/>
+      <c r="BS1" s="87"/>
+      <c r="BT1" s="87"/>
+      <c r="BU1" s="87"/>
+      <c r="BV1" s="87"/>
+      <c r="BW1" s="87"/>
+      <c r="BX1" s="85" t="s">
         <v>1238</v>
       </c>
-      <c r="BY1" s="77"/>
-      <c r="BZ1" s="77"/>
+      <c r="BY1" s="85"/>
+      <c r="BZ1" s="85"/>
     </row>
     <row r="2" spans="1:78" s="59" customFormat="1">
       <c r="A2" s="64" t="s">
@@ -6909,202 +6893,202 @@
       <c r="E2" s="64" t="s">
         <v>17</v>
       </c>
-      <c r="F2" s="117" t="s">
+      <c r="F2" s="74" t="s">
         <v>1328</v>
       </c>
-      <c r="G2" s="117" t="s">
+      <c r="G2" s="74" t="s">
         <v>1329</v>
       </c>
-      <c r="H2" s="117" t="s">
+      <c r="H2" s="74" t="s">
         <v>1330</v>
       </c>
-      <c r="I2" s="117" t="s">
+      <c r="I2" s="74" t="s">
         <v>1331</v>
       </c>
-      <c r="J2" s="117" t="s">
+      <c r="J2" s="74" t="s">
         <v>1332</v>
       </c>
-      <c r="K2" s="117" t="s">
+      <c r="K2" s="74" t="s">
         <v>1333</v>
       </c>
-      <c r="L2" s="117" t="s">
+      <c r="L2" s="74" t="s">
         <v>1324</v>
       </c>
-      <c r="M2" s="117" t="s">
+      <c r="M2" s="74" t="s">
         <v>1334</v>
       </c>
-      <c r="N2" s="117" t="s">
+      <c r="N2" s="74" t="s">
         <v>1335</v>
       </c>
-      <c r="O2" s="117" t="s">
+      <c r="O2" s="74" t="s">
         <v>1336</v>
       </c>
-      <c r="P2" s="117" t="s">
+      <c r="P2" s="74" t="s">
         <v>1337</v>
       </c>
-      <c r="Q2" s="117" t="s">
+      <c r="Q2" s="74" t="s">
         <v>1338</v>
       </c>
-      <c r="R2" s="117" t="s">
+      <c r="R2" s="74" t="s">
         <v>1339</v>
       </c>
-      <c r="S2" s="117" t="s">
+      <c r="S2" s="74" t="s">
         <v>1340</v>
       </c>
-      <c r="T2" s="117" t="s">
+      <c r="T2" s="74" t="s">
         <v>1341</v>
       </c>
-      <c r="U2" s="117" t="s">
+      <c r="U2" s="74" t="s">
         <v>1325</v>
       </c>
-      <c r="V2" s="117" t="s">
+      <c r="V2" s="74" t="s">
         <v>1342</v>
       </c>
-      <c r="W2" s="117" t="s">
+      <c r="W2" s="74" t="s">
         <v>1343</v>
       </c>
-      <c r="X2" s="117" t="s">
+      <c r="X2" s="74" t="s">
         <v>1344</v>
       </c>
-      <c r="Y2" s="117" t="s">
+      <c r="Y2" s="74" t="s">
         <v>1345</v>
       </c>
-      <c r="Z2" s="117" t="s">
+      <c r="Z2" s="74" t="s">
         <v>1346</v>
       </c>
-      <c r="AA2" s="117" t="s">
+      <c r="AA2" s="74" t="s">
         <v>1347</v>
       </c>
-      <c r="AB2" s="117" t="s">
+      <c r="AB2" s="74" t="s">
         <v>1348</v>
       </c>
-      <c r="AC2" s="117" t="s">
+      <c r="AC2" s="74" t="s">
         <v>1349</v>
       </c>
-      <c r="AD2" s="117" t="s">
+      <c r="AD2" s="74" t="s">
         <v>1350</v>
       </c>
-      <c r="AE2" s="117" t="s">
+      <c r="AE2" s="74" t="s">
         <v>1351</v>
       </c>
-      <c r="AF2" s="117" t="s">
+      <c r="AF2" s="74" t="s">
         <v>1352</v>
       </c>
-      <c r="AG2" s="117" t="s">
+      <c r="AG2" s="74" t="s">
         <v>1353</v>
       </c>
-      <c r="AH2" s="117" t="s">
+      <c r="AH2" s="74" t="s">
         <v>1354</v>
       </c>
-      <c r="AI2" s="117" t="s">
+      <c r="AI2" s="74" t="s">
         <v>1355</v>
       </c>
-      <c r="AJ2" s="117" t="s">
+      <c r="AJ2" s="74" t="s">
         <v>1356</v>
       </c>
-      <c r="AK2" s="117" t="s">
+      <c r="AK2" s="74" t="s">
         <v>1357</v>
       </c>
-      <c r="AL2" s="117" t="s">
+      <c r="AL2" s="74" t="s">
         <v>1358</v>
       </c>
-      <c r="AM2" s="117" t="s">
+      <c r="AM2" s="74" t="s">
         <v>1359</v>
       </c>
-      <c r="AN2" s="117" t="s">
+      <c r="AN2" s="74" t="s">
         <v>1360</v>
       </c>
-      <c r="AO2" s="117" t="s">
+      <c r="AO2" s="74" t="s">
         <v>1361</v>
       </c>
-      <c r="AP2" s="117" t="s">
+      <c r="AP2" s="74" t="s">
         <v>1362</v>
       </c>
-      <c r="AQ2" s="117" t="s">
+      <c r="AQ2" s="74" t="s">
         <v>1363</v>
       </c>
-      <c r="AR2" s="117" t="s">
+      <c r="AR2" s="74" t="s">
         <v>1364</v>
       </c>
-      <c r="AS2" s="117" t="s">
+      <c r="AS2" s="74" t="s">
         <v>1365</v>
       </c>
-      <c r="AT2" s="117" t="s">
+      <c r="AT2" s="74" t="s">
         <v>1366</v>
       </c>
-      <c r="AU2" s="117" t="s">
+      <c r="AU2" s="74" t="s">
         <v>1367</v>
       </c>
-      <c r="AV2" s="117" t="s">
+      <c r="AV2" s="74" t="s">
         <v>1368</v>
       </c>
-      <c r="AW2" s="117" t="s">
+      <c r="AW2" s="74" t="s">
         <v>1369</v>
       </c>
-      <c r="AX2" s="117" t="s">
+      <c r="AX2" s="74" t="s">
         <v>1370</v>
       </c>
-      <c r="AY2" s="117" t="s">
+      <c r="AY2" s="74" t="s">
         <v>1371</v>
       </c>
-      <c r="AZ2" s="117" t="s">
+      <c r="AZ2" s="74" t="s">
         <v>1372</v>
       </c>
-      <c r="BA2" s="117" t="s">
+      <c r="BA2" s="74" t="s">
         <v>1373</v>
       </c>
-      <c r="BB2" s="117" t="s">
+      <c r="BB2" s="74" t="s">
         <v>1374</v>
       </c>
-      <c r="BC2" s="117" t="s">
+      <c r="BC2" s="74" t="s">
         <v>1375</v>
       </c>
-      <c r="BD2" s="117" t="s">
+      <c r="BD2" s="74" t="s">
         <v>1376</v>
       </c>
-      <c r="BE2" s="117" t="s">
+      <c r="BE2" s="74" t="s">
         <v>1377</v>
       </c>
-      <c r="BF2" s="117" t="s">
+      <c r="BF2" s="74" t="s">
         <v>1378</v>
       </c>
-      <c r="BG2" s="117" t="s">
+      <c r="BG2" s="74" t="s">
         <v>1379</v>
       </c>
-      <c r="BH2" s="117" t="s">
+      <c r="BH2" s="74" t="s">
         <v>1380</v>
       </c>
-      <c r="BI2" s="117" t="s">
+      <c r="BI2" s="74" t="s">
         <v>1381</v>
       </c>
-      <c r="BJ2" s="117" t="s">
+      <c r="BJ2" s="74" t="s">
         <v>1382</v>
       </c>
-      <c r="BK2" s="118" t="s">
+      <c r="BK2" s="75" t="s">
         <v>1383</v>
       </c>
-      <c r="BL2" s="117" t="s">
+      <c r="BL2" s="74" t="s">
         <v>1384</v>
       </c>
-      <c r="BM2" s="117" t="s">
+      <c r="BM2" s="74" t="s">
         <v>1385</v>
       </c>
-      <c r="BN2" s="117" t="s">
+      <c r="BN2" s="74" t="s">
         <v>1386</v>
       </c>
-      <c r="BO2" s="117" t="s">
+      <c r="BO2" s="74" t="s">
         <v>1387</v>
       </c>
-      <c r="BP2" s="117" t="s">
+      <c r="BP2" s="74" t="s">
         <v>1388</v>
       </c>
-      <c r="BQ2" s="117" t="s">
+      <c r="BQ2" s="74" t="s">
         <v>1389</v>
       </c>
-      <c r="BR2" s="117" t="s">
+      <c r="BR2" s="74" t="s">
         <v>1390</v>
       </c>
-      <c r="BS2" s="117" t="s">
+      <c r="BS2" s="74" t="s">
         <v>1391</v>
       </c>
       <c r="BT2" s="66" t="s">
@@ -7135,78 +7119,82 @@
       <c r="C3" s="61"/>
       <c r="D3" s="61"/>
       <c r="E3" s="61"/>
-      <c r="F3" s="119"/>
-      <c r="G3" s="119"/>
-      <c r="H3" s="119"/>
-      <c r="I3" s="120"/>
-      <c r="J3" s="119"/>
-      <c r="K3" s="119"/>
-      <c r="L3" s="119"/>
-      <c r="M3" s="119"/>
-      <c r="N3" s="119"/>
-      <c r="O3" s="121"/>
-      <c r="P3" s="122"/>
-      <c r="Q3" s="122"/>
-      <c r="R3" s="123"/>
-      <c r="S3" s="122"/>
-      <c r="T3" s="119"/>
-      <c r="U3" s="119"/>
-      <c r="V3" s="119"/>
-      <c r="W3" s="119"/>
-      <c r="X3" s="121"/>
-      <c r="Y3" s="121"/>
-      <c r="Z3" s="122"/>
-      <c r="AA3" s="122"/>
-      <c r="AB3" s="122"/>
-      <c r="AC3" s="122"/>
-      <c r="AD3" s="121"/>
-      <c r="AE3" s="119"/>
-      <c r="AF3" s="119"/>
-      <c r="AG3" s="119"/>
-      <c r="AH3" s="119"/>
-      <c r="AI3" s="119"/>
-      <c r="AJ3" s="119"/>
-      <c r="AK3" s="119"/>
-      <c r="AL3" s="119"/>
-      <c r="AM3" s="119"/>
-      <c r="AN3" s="119"/>
-      <c r="AO3" s="119"/>
-      <c r="AP3" s="119"/>
-      <c r="AQ3" s="119"/>
-      <c r="AR3" s="119"/>
-      <c r="AS3" s="119"/>
-      <c r="AT3" s="119"/>
-      <c r="AU3" s="119"/>
-      <c r="AV3" s="119"/>
-      <c r="AW3" s="119"/>
-      <c r="AX3" s="119"/>
-      <c r="AY3" s="119"/>
-      <c r="AZ3" s="119"/>
-      <c r="BA3" s="119"/>
-      <c r="BB3" s="119"/>
-      <c r="BC3" s="123"/>
-      <c r="BD3" s="119"/>
-      <c r="BE3" s="119"/>
-      <c r="BF3" s="119"/>
-      <c r="BG3" s="119"/>
-      <c r="BH3" s="119"/>
-      <c r="BI3" s="123"/>
-      <c r="BJ3" s="119"/>
-      <c r="BK3" s="121"/>
-      <c r="BL3" s="119"/>
-      <c r="BM3" s="119"/>
-      <c r="BN3" s="119"/>
-      <c r="BO3" s="119"/>
-      <c r="BP3" s="119"/>
-      <c r="BQ3" s="119"/>
-      <c r="BR3" s="121"/>
-      <c r="BS3" s="121"/>
+      <c r="F3" s="76"/>
+      <c r="G3" s="76"/>
+      <c r="H3" s="76"/>
+      <c r="I3" s="77"/>
+      <c r="J3" s="76"/>
+      <c r="K3" s="76"/>
+      <c r="L3" s="76"/>
+      <c r="M3" s="76"/>
+      <c r="N3" s="76"/>
+      <c r="O3" s="78"/>
+      <c r="P3" s="79"/>
+      <c r="Q3" s="79"/>
+      <c r="R3" s="80"/>
+      <c r="S3" s="79"/>
+      <c r="T3" s="76"/>
+      <c r="U3" s="76"/>
+      <c r="V3" s="76"/>
+      <c r="W3" s="76"/>
+      <c r="X3" s="78"/>
+      <c r="Y3" s="78"/>
+      <c r="Z3" s="79"/>
+      <c r="AA3" s="79"/>
+      <c r="AB3" s="79"/>
+      <c r="AC3" s="79"/>
+      <c r="AD3" s="78"/>
+      <c r="AE3" s="76"/>
+      <c r="AF3" s="76"/>
+      <c r="AG3" s="76"/>
+      <c r="AH3" s="76"/>
+      <c r="AI3" s="76"/>
+      <c r="AJ3" s="76"/>
+      <c r="AK3" s="76"/>
+      <c r="AL3" s="76"/>
+      <c r="AM3" s="76"/>
+      <c r="AN3" s="76"/>
+      <c r="AO3" s="76"/>
+      <c r="AP3" s="76"/>
+      <c r="AQ3" s="76"/>
+      <c r="AR3" s="76"/>
+      <c r="AS3" s="76"/>
+      <c r="AT3" s="76"/>
+      <c r="AU3" s="76"/>
+      <c r="AV3" s="76"/>
+      <c r="AW3" s="76"/>
+      <c r="AX3" s="76"/>
+      <c r="AY3" s="76"/>
+      <c r="AZ3" s="76"/>
+      <c r="BA3" s="76"/>
+      <c r="BB3" s="76"/>
+      <c r="BC3" s="80"/>
+      <c r="BD3" s="76"/>
+      <c r="BE3" s="76"/>
+      <c r="BF3" s="76"/>
+      <c r="BG3" s="76"/>
+      <c r="BH3" s="76"/>
+      <c r="BI3" s="80"/>
+      <c r="BJ3" s="76"/>
+      <c r="BK3" s="78"/>
+      <c r="BL3" s="76"/>
+      <c r="BM3" s="76"/>
+      <c r="BN3" s="76"/>
+      <c r="BO3" s="76"/>
+      <c r="BP3" s="76"/>
+      <c r="BQ3" s="76"/>
+      <c r="BR3" s="78"/>
+      <c r="BS3" s="78"/>
       <c r="BT3" s="62"/>
       <c r="BU3" s="61"/>
       <c r="BV3" s="61"/>
       <c r="BW3" s="61"/>
-      <c r="BX3" s="63"/>
-      <c r="BY3" s="63"/>
+      <c r="BX3" s="63" t="s">
+        <v>1247</v>
+      </c>
+      <c r="BY3" s="63" t="s">
+        <v>1260</v>
+      </c>
       <c r="BZ3" s="63"/>
     </row>
     <row r="4" spans="1:78" s="60" customFormat="1">
@@ -7215,72 +7203,72 @@
       <c r="C4" s="61"/>
       <c r="D4" s="61"/>
       <c r="E4" s="61"/>
-      <c r="F4" s="119"/>
-      <c r="G4" s="119"/>
-      <c r="H4" s="119"/>
-      <c r="I4" s="120"/>
-      <c r="J4" s="119"/>
-      <c r="K4" s="119"/>
-      <c r="L4" s="119"/>
-      <c r="M4" s="119"/>
-      <c r="N4" s="119"/>
-      <c r="O4" s="121"/>
-      <c r="P4" s="122"/>
-      <c r="Q4" s="122"/>
-      <c r="R4" s="123"/>
-      <c r="S4" s="122"/>
-      <c r="T4" s="119"/>
-      <c r="U4" s="119"/>
-      <c r="V4" s="119"/>
-      <c r="W4" s="119"/>
-      <c r="X4" s="121"/>
-      <c r="Y4" s="121"/>
-      <c r="Z4" s="122"/>
-      <c r="AA4" s="122"/>
-      <c r="AB4" s="122"/>
-      <c r="AC4" s="122"/>
-      <c r="AD4" s="121"/>
-      <c r="AE4" s="119"/>
-      <c r="AF4" s="119"/>
-      <c r="AG4" s="119"/>
-      <c r="AH4" s="119"/>
-      <c r="AI4" s="119"/>
-      <c r="AJ4" s="119"/>
-      <c r="AK4" s="119"/>
-      <c r="AL4" s="119"/>
-      <c r="AM4" s="119"/>
-      <c r="AN4" s="119"/>
-      <c r="AO4" s="119"/>
-      <c r="AP4" s="119"/>
-      <c r="AQ4" s="119"/>
-      <c r="AR4" s="119"/>
-      <c r="AS4" s="119"/>
-      <c r="AT4" s="119"/>
-      <c r="AU4" s="119"/>
-      <c r="AV4" s="119"/>
-      <c r="AW4" s="119"/>
-      <c r="AX4" s="119"/>
-      <c r="AY4" s="119"/>
-      <c r="AZ4" s="119"/>
-      <c r="BA4" s="119"/>
-      <c r="BB4" s="119"/>
-      <c r="BC4" s="123"/>
-      <c r="BD4" s="119"/>
-      <c r="BE4" s="119"/>
-      <c r="BF4" s="119"/>
-      <c r="BG4" s="119"/>
-      <c r="BH4" s="119"/>
-      <c r="BI4" s="123"/>
-      <c r="BJ4" s="119"/>
-      <c r="BK4" s="121"/>
-      <c r="BL4" s="119"/>
-      <c r="BM4" s="119"/>
-      <c r="BN4" s="119"/>
-      <c r="BO4" s="119"/>
-      <c r="BP4" s="119"/>
-      <c r="BQ4" s="119"/>
-      <c r="BR4" s="121"/>
-      <c r="BS4" s="121"/>
+      <c r="F4" s="76"/>
+      <c r="G4" s="76"/>
+      <c r="H4" s="76"/>
+      <c r="I4" s="77"/>
+      <c r="J4" s="76"/>
+      <c r="K4" s="76"/>
+      <c r="L4" s="76"/>
+      <c r="M4" s="76"/>
+      <c r="N4" s="76"/>
+      <c r="O4" s="78"/>
+      <c r="P4" s="79"/>
+      <c r="Q4" s="79"/>
+      <c r="R4" s="80"/>
+      <c r="S4" s="79"/>
+      <c r="T4" s="76"/>
+      <c r="U4" s="76"/>
+      <c r="V4" s="76"/>
+      <c r="W4" s="76"/>
+      <c r="X4" s="78"/>
+      <c r="Y4" s="78"/>
+      <c r="Z4" s="79"/>
+      <c r="AA4" s="79"/>
+      <c r="AB4" s="79"/>
+      <c r="AC4" s="79"/>
+      <c r="AD4" s="78"/>
+      <c r="AE4" s="76"/>
+      <c r="AF4" s="76"/>
+      <c r="AG4" s="76"/>
+      <c r="AH4" s="76"/>
+      <c r="AI4" s="76"/>
+      <c r="AJ4" s="76"/>
+      <c r="AK4" s="76"/>
+      <c r="AL4" s="76"/>
+      <c r="AM4" s="76"/>
+      <c r="AN4" s="76"/>
+      <c r="AO4" s="76"/>
+      <c r="AP4" s="76"/>
+      <c r="AQ4" s="76"/>
+      <c r="AR4" s="76"/>
+      <c r="AS4" s="76"/>
+      <c r="AT4" s="76"/>
+      <c r="AU4" s="76"/>
+      <c r="AV4" s="76"/>
+      <c r="AW4" s="76"/>
+      <c r="AX4" s="76"/>
+      <c r="AY4" s="76"/>
+      <c r="AZ4" s="76"/>
+      <c r="BA4" s="76"/>
+      <c r="BB4" s="76"/>
+      <c r="BC4" s="80"/>
+      <c r="BD4" s="76"/>
+      <c r="BE4" s="76"/>
+      <c r="BF4" s="76"/>
+      <c r="BG4" s="76"/>
+      <c r="BH4" s="76"/>
+      <c r="BI4" s="80"/>
+      <c r="BJ4" s="76"/>
+      <c r="BK4" s="78"/>
+      <c r="BL4" s="76"/>
+      <c r="BM4" s="76"/>
+      <c r="BN4" s="76"/>
+      <c r="BO4" s="76"/>
+      <c r="BP4" s="76"/>
+      <c r="BQ4" s="76"/>
+      <c r="BR4" s="78"/>
+      <c r="BS4" s="78"/>
       <c r="BT4" s="62"/>
       <c r="BU4" s="61"/>
       <c r="BV4" s="61"/>
@@ -7307,7 +7295,7 @@
       <c r="O5" s="73"/>
       <c r="P5" s="72"/>
       <c r="Q5" s="72"/>
-      <c r="R5" s="124"/>
+      <c r="R5" s="81"/>
       <c r="S5" s="72"/>
       <c r="T5" s="61"/>
       <c r="U5" s="61"/>
@@ -7344,13 +7332,13 @@
       <c r="AZ5" s="61"/>
       <c r="BA5" s="61"/>
       <c r="BB5" s="61"/>
-      <c r="BC5" s="124"/>
+      <c r="BC5" s="81"/>
       <c r="BD5" s="61"/>
       <c r="BE5" s="61"/>
       <c r="BF5" s="61"/>
       <c r="BG5" s="61"/>
       <c r="BH5" s="61"/>
-      <c r="BI5" s="124"/>
+      <c r="BI5" s="81"/>
       <c r="BJ5" s="61"/>
       <c r="BK5" s="73"/>
       <c r="BL5" s="61"/>
@@ -7387,7 +7375,7 @@
       <c r="O6" s="73"/>
       <c r="P6" s="72"/>
       <c r="Q6" s="72"/>
-      <c r="R6" s="124"/>
+      <c r="R6" s="81"/>
       <c r="S6" s="72"/>
       <c r="T6" s="61"/>
       <c r="U6" s="61"/>
@@ -7424,13 +7412,13 @@
       <c r="AZ6" s="61"/>
       <c r="BA6" s="61"/>
       <c r="BB6" s="61"/>
-      <c r="BC6" s="124"/>
+      <c r="BC6" s="81"/>
       <c r="BD6" s="61"/>
       <c r="BE6" s="61"/>
       <c r="BF6" s="61"/>
       <c r="BG6" s="61"/>
       <c r="BH6" s="61"/>
-      <c r="BI6" s="124"/>
+      <c r="BI6" s="81"/>
       <c r="BJ6" s="61"/>
       <c r="BK6" s="73"/>
       <c r="BL6" s="61"/>
@@ -7467,7 +7455,7 @@
       <c r="O7" s="73"/>
       <c r="P7" s="72"/>
       <c r="Q7" s="72"/>
-      <c r="R7" s="124"/>
+      <c r="R7" s="81"/>
       <c r="S7" s="72"/>
       <c r="T7" s="61"/>
       <c r="U7" s="61"/>
@@ -7504,13 +7492,13 @@
       <c r="AZ7" s="61"/>
       <c r="BA7" s="61"/>
       <c r="BB7" s="61"/>
-      <c r="BC7" s="124"/>
+      <c r="BC7" s="81"/>
       <c r="BD7" s="61"/>
       <c r="BE7" s="61"/>
       <c r="BF7" s="61"/>
       <c r="BG7" s="61"/>
       <c r="BH7" s="61"/>
-      <c r="BI7" s="124"/>
+      <c r="BI7" s="81"/>
       <c r="BJ7" s="61"/>
       <c r="BK7" s="73"/>
       <c r="BL7" s="61"/>
@@ -7547,7 +7535,7 @@
       <c r="O8" s="73"/>
       <c r="P8" s="72"/>
       <c r="Q8" s="72"/>
-      <c r="R8" s="124"/>
+      <c r="R8" s="81"/>
       <c r="S8" s="72"/>
       <c r="T8" s="61"/>
       <c r="U8" s="61"/>
@@ -7584,13 +7572,13 @@
       <c r="AZ8" s="61"/>
       <c r="BA8" s="61"/>
       <c r="BB8" s="61"/>
-      <c r="BC8" s="124"/>
+      <c r="BC8" s="81"/>
       <c r="BD8" s="61"/>
       <c r="BE8" s="61"/>
       <c r="BF8" s="61"/>
       <c r="BG8" s="61"/>
       <c r="BH8" s="61"/>
-      <c r="BI8" s="124"/>
+      <c r="BI8" s="81"/>
       <c r="BJ8" s="61"/>
       <c r="BK8" s="73"/>
       <c r="BL8" s="61"/>
@@ -7627,7 +7615,7 @@
       <c r="O9" s="73"/>
       <c r="P9" s="72"/>
       <c r="Q9" s="72"/>
-      <c r="R9" s="124"/>
+      <c r="R9" s="81"/>
       <c r="S9" s="72"/>
       <c r="T9" s="61"/>
       <c r="U9" s="61"/>
@@ -7664,13 +7652,13 @@
       <c r="AZ9" s="61"/>
       <c r="BA9" s="61"/>
       <c r="BB9" s="61"/>
-      <c r="BC9" s="124"/>
+      <c r="BC9" s="81"/>
       <c r="BD9" s="61"/>
       <c r="BE9" s="61"/>
       <c r="BF9" s="61"/>
       <c r="BG9" s="61"/>
       <c r="BH9" s="61"/>
-      <c r="BI9" s="124"/>
+      <c r="BI9" s="81"/>
       <c r="BJ9" s="61"/>
       <c r="BK9" s="73"/>
       <c r="BL9" s="61"/>
@@ -7707,7 +7695,7 @@
       <c r="O10" s="73"/>
       <c r="P10" s="72"/>
       <c r="Q10" s="72"/>
-      <c r="R10" s="124"/>
+      <c r="R10" s="81"/>
       <c r="S10" s="72"/>
       <c r="T10" s="61"/>
       <c r="U10" s="61"/>
@@ -7744,13 +7732,13 @@
       <c r="AZ10" s="61"/>
       <c r="BA10" s="61"/>
       <c r="BB10" s="61"/>
-      <c r="BC10" s="124"/>
+      <c r="BC10" s="81"/>
       <c r="BD10" s="61"/>
       <c r="BE10" s="61"/>
       <c r="BF10" s="61"/>
       <c r="BG10" s="61"/>
       <c r="BH10" s="61"/>
-      <c r="BI10" s="124"/>
+      <c r="BI10" s="81"/>
       <c r="BJ10" s="61"/>
       <c r="BK10" s="73"/>
       <c r="BL10" s="61"/>
@@ -7776,9 +7764,8 @@
     <mergeCell ref="F1:BW1"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
-  <dataValidations count="50">
+  <dataValidations count="48">
     <dataValidation allowBlank="1" showErrorMessage="1" sqref="D2 AU4:AU65527"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="提示：" prompt="请参照“输入规则”中的具体要求填写" sqref="C2:C65513"/>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D3:D65513">
       <formula1>"01 银行间债券市场,02 商业银行柜台市场,03 上海证券交易所,04 深圳证券交易所,05 全国中小企业股份转让系统,06 上海期货交易所,07 郑州商品交易所,08 大连商品交易所,09 中国金融期货交易所,10 上海黄金交易所,11 区域性产权/资产交易市场,12 区域性商品交易所,13 区域性贵金属交易所,14 艺术品市场,15 基金市场,16 信托市场,17 全国银行间同业拆借市场,18 上海票据交易所,99 其他交易流通场所"</formula1>
     </dataValidation>
@@ -7803,7 +7790,6 @@
       <formula1>0</formula1>
       <formula2>999.99999</formula2>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="提示" prompt="请按照附件《中国行政区划划分》填写行政区划代码" sqref="BN4:BN65527"/>
     <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="重定价周期需大于0，且必须为n(5)格式。" sqref="BI4:BI1048576">
       <formula1>1</formula1>
       <formula2>99999</formula2>
@@ -7932,12 +7918,30 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555596" footer="0.51180555555555596"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>枚举值!$A$7:$M$7</xm:f>
           </x14:formula1>
           <xm:sqref>BX3:BX1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>币种填写规则!$C$2:$C$179</xm:f>
+          </x14:formula1>
+          <xm:sqref>E1:E1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="提示" prompt="请按照附件《中国行政区划划分》填写行政区划代码">
+          <x14:formula1>
+            <xm:f>国家或区域填写规则!$C$2:$C$240</xm:f>
+          </x14:formula1>
+          <xm:sqref>BN1:BN1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="提示：" prompt="请参照“输入规则”中的具体要求填写">
+          <x14:formula1>
+            <xm:f>各类资产应填要素列说明!$A$65:$A$68</xm:f>
+          </x14:formula1>
+          <xm:sqref>C1:C1048576</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -8007,13 +8011,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="42" customHeight="1">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="106" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="79"/>
+      <c r="B1" s="107"/>
     </row>
     <row r="2" spans="1:2" ht="20.25" customHeight="1">
-      <c r="A2" s="90" t="s">
+      <c r="A2" s="97" t="s">
         <v>30</v>
       </c>
       <c r="B2" s="29" t="s">
@@ -8021,25 +8025,25 @@
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="91"/>
+      <c r="A3" s="98"/>
       <c r="B3" s="26" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="91"/>
+      <c r="A4" s="98"/>
       <c r="B4" s="26" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="92"/>
+      <c r="A5" s="99"/>
       <c r="B5" s="24" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:2" s="17" customFormat="1">
-      <c r="A6" s="93" t="s">
+      <c r="A6" s="100" t="s">
         <v>35</v>
       </c>
       <c r="B6" s="29" t="s">
@@ -8047,13 +8051,13 @@
       </c>
     </row>
     <row r="7" spans="1:2" s="17" customFormat="1">
-      <c r="A7" s="94"/>
+      <c r="A7" s="101"/>
       <c r="B7" s="23" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:2" s="17" customFormat="1">
-      <c r="A8" s="95" t="s">
+      <c r="A8" s="102" t="s">
         <v>38</v>
       </c>
       <c r="B8" s="22" t="s">
@@ -8061,13 +8065,13 @@
       </c>
     </row>
     <row r="9" spans="1:2" s="17" customFormat="1">
-      <c r="A9" s="94"/>
+      <c r="A9" s="101"/>
       <c r="B9" s="23" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" s="83" t="s">
+      <c r="A10" s="103" t="s">
         <v>41</v>
       </c>
       <c r="B10" s="26" t="s">
@@ -8075,61 +8079,61 @@
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="96"/>
+      <c r="A11" s="104"/>
       <c r="B11" s="26" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" s="96"/>
+      <c r="A12" s="104"/>
       <c r="B12" s="26" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="13" spans="1:2">
-      <c r="A13" s="96"/>
+      <c r="A13" s="104"/>
       <c r="B13" s="26" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="96"/>
+      <c r="A14" s="104"/>
       <c r="B14" s="26" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="15" spans="1:2">
-      <c r="A15" s="96"/>
+      <c r="A15" s="104"/>
       <c r="B15" s="26" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="16" spans="1:2">
-      <c r="A16" s="96"/>
+      <c r="A16" s="104"/>
       <c r="B16" s="26" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" s="96"/>
+      <c r="A17" s="104"/>
       <c r="B17" s="26" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="18" spans="1:2">
-      <c r="A18" s="96"/>
+      <c r="A18" s="104"/>
       <c r="B18" s="26" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" s="96"/>
+      <c r="A19" s="104"/>
       <c r="B19" s="26" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="20" spans="1:2">
-      <c r="A20" s="96"/>
+      <c r="A20" s="104"/>
       <c r="B20" s="26" t="s">
         <v>52</v>
       </c>
@@ -8143,7 +8147,7 @@
       </c>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="83" t="s">
+      <c r="A22" s="103" t="s">
         <v>55</v>
       </c>
       <c r="B22" s="29" t="s">
@@ -8151,19 +8155,19 @@
       </c>
     </row>
     <row r="23" spans="1:2">
-      <c r="A23" s="96"/>
+      <c r="A23" s="104"/>
       <c r="B23" s="26" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="24" spans="1:2">
-      <c r="A24" s="84"/>
+      <c r="A24" s="105"/>
       <c r="B24" s="24" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="25" spans="1:2">
-      <c r="A25" s="83" t="s">
+      <c r="A25" s="103" t="s">
         <v>59</v>
       </c>
       <c r="B25" s="26" t="s">
@@ -8171,67 +8175,67 @@
       </c>
     </row>
     <row r="26" spans="1:2">
-      <c r="A26" s="96"/>
+      <c r="A26" s="104"/>
       <c r="B26" s="26" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="27" spans="1:2">
-      <c r="A27" s="96"/>
+      <c r="A27" s="104"/>
       <c r="B27" s="21" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="28" spans="1:2">
-      <c r="A28" s="96"/>
+      <c r="A28" s="104"/>
       <c r="B28" s="21" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="29" spans="1:2">
-      <c r="A29" s="96"/>
+      <c r="A29" s="104"/>
       <c r="B29" s="21" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="30" spans="1:2">
-      <c r="A30" s="96"/>
+      <c r="A30" s="104"/>
       <c r="B30" s="21" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="31" spans="1:2">
-      <c r="A31" s="96"/>
+      <c r="A31" s="104"/>
       <c r="B31" s="21" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="32" spans="1:2">
-      <c r="A32" s="96"/>
+      <c r="A32" s="104"/>
       <c r="B32" s="21" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="33" spans="1:2">
-      <c r="A33" s="96"/>
+      <c r="A33" s="104"/>
       <c r="B33" s="21" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="34" spans="1:2">
-      <c r="A34" s="96"/>
+      <c r="A34" s="104"/>
       <c r="B34" s="21" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="35" spans="1:2">
-      <c r="A35" s="84"/>
+      <c r="A35" s="105"/>
       <c r="B35" s="41" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="36" spans="1:2">
-      <c r="A36" s="83" t="s">
+      <c r="A36" s="103" t="s">
         <v>71</v>
       </c>
       <c r="B36" s="21" t="s">
@@ -8239,25 +8243,25 @@
       </c>
     </row>
     <row r="37" spans="1:2">
-      <c r="A37" s="96"/>
+      <c r="A37" s="104"/>
       <c r="B37" s="26" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="38" spans="1:2">
-      <c r="A38" s="96"/>
+      <c r="A38" s="104"/>
       <c r="B38" s="21" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="39" spans="1:2">
-      <c r="A39" s="84"/>
+      <c r="A39" s="105"/>
       <c r="B39" s="21" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="40" spans="1:2">
-      <c r="A40" s="83" t="s">
+      <c r="A40" s="103" t="s">
         <v>76</v>
       </c>
       <c r="B40" s="20" t="s">
@@ -8265,43 +8269,43 @@
       </c>
     </row>
     <row r="41" spans="1:2">
-      <c r="A41" s="96"/>
+      <c r="A41" s="104"/>
       <c r="B41" s="21" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="42" spans="1:2">
-      <c r="A42" s="96"/>
+      <c r="A42" s="104"/>
       <c r="B42" s="21" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="43" spans="1:2">
-      <c r="A43" s="96"/>
+      <c r="A43" s="104"/>
       <c r="B43" s="21" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="44" spans="1:2">
-      <c r="A44" s="96"/>
+      <c r="A44" s="104"/>
       <c r="B44" s="21" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="45" spans="1:2">
-      <c r="A45" s="96"/>
+      <c r="A45" s="104"/>
       <c r="B45" s="21" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="46" spans="1:2">
-      <c r="A46" s="84"/>
+      <c r="A46" s="105"/>
       <c r="B46" s="24" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="47" spans="1:2">
-      <c r="A47" s="83" t="s">
+      <c r="A47" s="103" t="s">
         <v>84</v>
       </c>
       <c r="B47" s="29" t="s">
@@ -8309,61 +8313,61 @@
       </c>
     </row>
     <row r="48" spans="1:2">
-      <c r="A48" s="96"/>
+      <c r="A48" s="104"/>
       <c r="B48" s="21" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="49" spans="1:2">
-      <c r="A49" s="96"/>
+      <c r="A49" s="104"/>
       <c r="B49" s="21" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="50" spans="1:2">
-      <c r="A50" s="96"/>
+      <c r="A50" s="104"/>
       <c r="B50" s="21" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="51" spans="1:2">
-      <c r="A51" s="96"/>
+      <c r="A51" s="104"/>
       <c r="B51" s="21" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="52" spans="1:2">
-      <c r="A52" s="96"/>
+      <c r="A52" s="104"/>
       <c r="B52" s="21" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="53" spans="1:2">
-      <c r="A53" s="96"/>
+      <c r="A53" s="104"/>
       <c r="B53" s="26" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="54" spans="1:2">
-      <c r="A54" s="96"/>
+      <c r="A54" s="104"/>
       <c r="B54" s="21" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="55" spans="1:2">
-      <c r="A55" s="96"/>
+      <c r="A55" s="104"/>
       <c r="B55" s="26" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="56" spans="1:2">
-      <c r="A56" s="84"/>
+      <c r="A56" s="105"/>
       <c r="B56" s="24" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="57" spans="1:2">
-      <c r="A57" s="83" t="s">
+      <c r="A57" s="103" t="s">
         <v>95</v>
       </c>
       <c r="B57" s="20" t="s">
@@ -8371,19 +8375,19 @@
       </c>
     </row>
     <row r="58" spans="1:2">
-      <c r="A58" s="96"/>
+      <c r="A58" s="104"/>
       <c r="B58" s="21" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="59" spans="1:2">
-      <c r="A59" s="84"/>
+      <c r="A59" s="105"/>
       <c r="B59" s="24" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="60" spans="1:2">
-      <c r="A60" s="83" t="s">
+      <c r="A60" s="103" t="s">
         <v>99</v>
       </c>
       <c r="B60" s="34" t="s">
@@ -8391,37 +8395,37 @@
       </c>
     </row>
     <row r="61" spans="1:2">
-      <c r="A61" s="96"/>
+      <c r="A61" s="104"/>
       <c r="B61" s="21" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="62" spans="1:2">
-      <c r="A62" s="96"/>
+      <c r="A62" s="104"/>
       <c r="B62" s="35" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="63" spans="1:2">
-      <c r="A63" s="96"/>
+      <c r="A63" s="104"/>
       <c r="B63" s="21" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="64" spans="1:2">
-      <c r="A64" s="96"/>
+      <c r="A64" s="104"/>
       <c r="B64" s="21" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="65" spans="1:2">
-      <c r="A65" s="84"/>
+      <c r="A65" s="105"/>
       <c r="B65" s="28" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="66" spans="1:2">
-      <c r="A66" s="83" t="s">
+      <c r="A66" s="103" t="s">
         <v>106</v>
       </c>
       <c r="B66" s="34" t="s">
@@ -8429,37 +8433,37 @@
       </c>
     </row>
     <row r="67" spans="1:2">
-      <c r="A67" s="96"/>
+      <c r="A67" s="104"/>
       <c r="B67" s="21" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="68" spans="1:2">
-      <c r="A68" s="96"/>
+      <c r="A68" s="104"/>
       <c r="B68" s="21" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="69" spans="1:2">
-      <c r="A69" s="96"/>
+      <c r="A69" s="104"/>
       <c r="B69" s="21" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="70" spans="1:2">
-      <c r="A70" s="96"/>
+      <c r="A70" s="104"/>
       <c r="B70" s="21" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="71" spans="1:2">
-      <c r="A71" s="84"/>
+      <c r="A71" s="105"/>
       <c r="B71" s="28" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="72" spans="1:2" s="17" customFormat="1">
-      <c r="A72" s="83" t="s">
+      <c r="A72" s="103" t="s">
         <v>113</v>
       </c>
       <c r="B72" s="21" t="s">
@@ -8467,103 +8471,103 @@
       </c>
     </row>
     <row r="73" spans="1:2" s="17" customFormat="1">
-      <c r="A73" s="96"/>
+      <c r="A73" s="104"/>
       <c r="B73" s="21" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="74" spans="1:2" s="17" customFormat="1">
-      <c r="A74" s="96"/>
+      <c r="A74" s="104"/>
       <c r="B74" s="21" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="75" spans="1:2" s="17" customFormat="1">
-      <c r="A75" s="96"/>
+      <c r="A75" s="104"/>
       <c r="B75" s="21" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="76" spans="1:2" s="17" customFormat="1">
-      <c r="A76" s="96"/>
+      <c r="A76" s="104"/>
       <c r="B76" s="21" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="77" spans="1:2" s="17" customFormat="1">
-      <c r="A77" s="96"/>
+      <c r="A77" s="104"/>
       <c r="B77" s="36" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="78" spans="1:2" s="17" customFormat="1">
-      <c r="A78" s="96"/>
+      <c r="A78" s="104"/>
       <c r="B78" s="21" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="79" spans="1:2" s="17" customFormat="1">
-      <c r="A79" s="96"/>
+      <c r="A79" s="104"/>
       <c r="B79" s="21" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="80" spans="1:2" s="17" customFormat="1">
-      <c r="A80" s="96"/>
+      <c r="A80" s="104"/>
       <c r="B80" s="21" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="81" spans="1:6" s="17" customFormat="1">
-      <c r="A81" s="96"/>
+      <c r="A81" s="104"/>
       <c r="B81" s="36" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="82" spans="1:6" s="17" customFormat="1">
-      <c r="A82" s="96"/>
+      <c r="A82" s="104"/>
       <c r="B82" s="21" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="83" spans="1:6" s="17" customFormat="1">
-      <c r="A83" s="96"/>
+      <c r="A83" s="104"/>
       <c r="B83" s="21" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="84" spans="1:6" s="17" customFormat="1">
-      <c r="A84" s="96"/>
+      <c r="A84" s="104"/>
       <c r="B84" s="21" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="85" spans="1:6" s="17" customFormat="1">
-      <c r="A85" s="96"/>
+      <c r="A85" s="104"/>
       <c r="B85" s="36" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="86" spans="1:6" s="17" customFormat="1">
-      <c r="A86" s="96"/>
+      <c r="A86" s="104"/>
       <c r="B86" s="36" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="87" spans="1:6" s="17" customFormat="1">
-      <c r="A87" s="96"/>
+      <c r="A87" s="104"/>
       <c r="B87" s="36" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="88" spans="1:6" s="17" customFormat="1">
-      <c r="A88" s="84"/>
+      <c r="A88" s="105"/>
       <c r="B88" s="24" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="89" spans="1:6" s="17" customFormat="1">
-      <c r="A89" s="83" t="s">
+      <c r="A89" s="103" t="s">
         <v>131</v>
       </c>
       <c r="B89" s="26" t="s">
@@ -8571,38 +8575,38 @@
       </c>
     </row>
     <row r="90" spans="1:6" s="17" customFormat="1">
-      <c r="A90" s="96"/>
+      <c r="A90" s="104"/>
       <c r="B90" s="26" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="91" spans="1:6" s="17" customFormat="1">
-      <c r="A91" s="96"/>
+      <c r="A91" s="104"/>
       <c r="B91" s="26" t="s">
         <v>134</v>
       </c>
       <c r="F91" s="42"/>
     </row>
     <row r="92" spans="1:6" s="17" customFormat="1">
-      <c r="A92" s="96"/>
+      <c r="A92" s="104"/>
       <c r="B92" s="43" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="93" spans="1:6" s="17" customFormat="1">
-      <c r="A93" s="96"/>
+      <c r="A93" s="104"/>
       <c r="B93" s="26" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="94" spans="1:6" s="17" customFormat="1">
-      <c r="A94" s="84"/>
+      <c r="A94" s="105"/>
       <c r="B94" s="24" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="95" spans="1:6" s="17" customFormat="1">
-      <c r="A95" s="83" t="s">
+      <c r="A95" s="103" t="s">
         <v>138</v>
       </c>
       <c r="B95" s="37" t="s">
@@ -8610,43 +8614,43 @@
       </c>
     </row>
     <row r="96" spans="1:6" s="17" customFormat="1">
-      <c r="A96" s="96"/>
+      <c r="A96" s="104"/>
       <c r="B96" s="36" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="97" spans="1:2" s="17" customFormat="1">
-      <c r="A97" s="96"/>
+      <c r="A97" s="104"/>
       <c r="B97" s="36" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="98" spans="1:2" s="17" customFormat="1">
-      <c r="A98" s="96"/>
+      <c r="A98" s="104"/>
       <c r="B98" s="36" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="99" spans="1:2" s="17" customFormat="1">
-      <c r="A99" s="96"/>
+      <c r="A99" s="104"/>
       <c r="B99" s="36" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="100" spans="1:2" s="17" customFormat="1">
-      <c r="A100" s="96"/>
+      <c r="A100" s="104"/>
       <c r="B100" s="36" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="101" spans="1:2" s="17" customFormat="1">
-      <c r="A101" s="84"/>
+      <c r="A101" s="105"/>
       <c r="B101" s="32" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="102" spans="1:2" s="17" customFormat="1">
-      <c r="A102" s="83" t="s">
+      <c r="A102" s="103" t="s">
         <v>146</v>
       </c>
       <c r="B102" s="20" t="s">
@@ -8654,7 +8658,7 @@
       </c>
     </row>
     <row r="103" spans="1:2" s="17" customFormat="1">
-      <c r="A103" s="84"/>
+      <c r="A103" s="105"/>
       <c r="B103" s="24" t="s">
         <v>148</v>
       </c>
@@ -8672,10 +8676,10 @@
       <c r="B105" s="27"/>
     </row>
     <row r="107" spans="1:2" ht="36.75" customHeight="1">
-      <c r="A107" s="78" t="s">
+      <c r="A107" s="106" t="s">
         <v>151</v>
       </c>
-      <c r="B107" s="79"/>
+      <c r="B107" s="107"/>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" s="47"/>
@@ -8846,17 +8850,17 @@
       </c>
     </row>
     <row r="137" spans="1:2">
-      <c r="A137" s="97" t="s">
+      <c r="A137" s="91" t="s">
         <v>180</v>
       </c>
-      <c r="B137" s="98"/>
+      <c r="B137" s="92"/>
     </row>
     <row r="138" spans="1:2" ht="81.75" customHeight="1">
-      <c r="A138" s="99"/>
-      <c r="B138" s="100"/>
+      <c r="A138" s="93"/>
+      <c r="B138" s="94"/>
     </row>
     <row r="139" spans="1:2">
-      <c r="A139" s="85" t="s">
+      <c r="A139" s="88" t="s">
         <v>181</v>
       </c>
       <c r="B139" s="49" t="s">
@@ -8864,31 +8868,31 @@
       </c>
     </row>
     <row r="140" spans="1:2">
-      <c r="A140" s="86"/>
+      <c r="A140" s="89"/>
       <c r="B140" s="50" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="141" spans="1:2">
-      <c r="A141" s="86"/>
+      <c r="A141" s="89"/>
       <c r="B141" s="50" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="142" spans="1:2">
-      <c r="A142" s="86"/>
+      <c r="A142" s="89"/>
       <c r="B142" s="50" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="143" spans="1:2">
-      <c r="A143" s="87"/>
+      <c r="A143" s="90"/>
       <c r="B143" s="52" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="144" spans="1:2">
-      <c r="A144" s="85" t="s">
+      <c r="A144" s="88" t="s">
         <v>187</v>
       </c>
       <c r="B144" s="49" t="s">
@@ -8896,43 +8900,43 @@
       </c>
     </row>
     <row r="145" spans="1:2">
-      <c r="A145" s="86"/>
+      <c r="A145" s="89"/>
       <c r="B145" s="50" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="146" spans="1:2">
-      <c r="A146" s="86"/>
+      <c r="A146" s="89"/>
       <c r="B146" s="50" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="147" spans="1:2">
-      <c r="A147" s="86"/>
+      <c r="A147" s="89"/>
       <c r="B147" s="50" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="148" spans="1:2">
-      <c r="A148" s="86"/>
+      <c r="A148" s="89"/>
       <c r="B148" s="50" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="149" spans="1:2">
-      <c r="A149" s="86"/>
+      <c r="A149" s="89"/>
       <c r="B149" s="50" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="150" spans="1:2">
-      <c r="A150" s="87"/>
+      <c r="A150" s="90"/>
       <c r="B150" s="52" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="151" spans="1:2">
-      <c r="A151" s="85" t="s">
+      <c r="A151" s="88" t="s">
         <v>195</v>
       </c>
       <c r="B151" s="49" t="s">
@@ -8940,187 +8944,187 @@
       </c>
     </row>
     <row r="152" spans="1:2">
-      <c r="A152" s="86"/>
+      <c r="A152" s="89"/>
       <c r="B152" s="50" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="153" spans="1:2">
-      <c r="A153" s="86"/>
+      <c r="A153" s="89"/>
       <c r="B153" s="50" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="154" spans="1:2">
-      <c r="A154" s="86"/>
+      <c r="A154" s="89"/>
       <c r="B154" s="50" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="155" spans="1:2">
-      <c r="A155" s="86"/>
+      <c r="A155" s="89"/>
       <c r="B155" s="50" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="156" spans="1:2">
-      <c r="A156" s="86"/>
+      <c r="A156" s="89"/>
       <c r="B156" s="50" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="157" spans="1:2">
-      <c r="A157" s="86"/>
+      <c r="A157" s="89"/>
       <c r="B157" s="50" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="158" spans="1:2">
-      <c r="A158" s="86"/>
+      <c r="A158" s="89"/>
       <c r="B158" s="50" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="159" spans="1:2">
-      <c r="A159" s="86"/>
+      <c r="A159" s="89"/>
       <c r="B159" s="50" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="160" spans="1:2">
-      <c r="A160" s="86"/>
+      <c r="A160" s="89"/>
       <c r="B160" s="50" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="161" spans="1:2">
-      <c r="A161" s="86"/>
+      <c r="A161" s="89"/>
       <c r="B161" s="50" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="162" spans="1:2">
-      <c r="A162" s="86"/>
+      <c r="A162" s="89"/>
       <c r="B162" s="50" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="163" spans="1:2">
-      <c r="A163" s="86"/>
+      <c r="A163" s="89"/>
       <c r="B163" s="50" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="164" spans="1:2">
-      <c r="A164" s="86"/>
+      <c r="A164" s="89"/>
       <c r="B164" s="50" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="165" spans="1:2">
-      <c r="A165" s="86"/>
+      <c r="A165" s="89"/>
       <c r="B165" s="50" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="166" spans="1:2">
-      <c r="A166" s="86"/>
+      <c r="A166" s="89"/>
       <c r="B166" s="50" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="167" spans="1:2">
-      <c r="A167" s="86"/>
+      <c r="A167" s="89"/>
       <c r="B167" s="50" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="168" spans="1:2">
-      <c r="A168" s="86"/>
+      <c r="A168" s="89"/>
       <c r="B168" s="50" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="169" spans="1:2">
-      <c r="A169" s="86"/>
+      <c r="A169" s="89"/>
       <c r="B169" s="50" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="170" spans="1:2">
-      <c r="A170" s="86"/>
+      <c r="A170" s="89"/>
       <c r="B170" s="50" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="171" spans="1:2">
-      <c r="A171" s="86"/>
+      <c r="A171" s="89"/>
       <c r="B171" s="50" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="172" spans="1:2">
-      <c r="A172" s="86"/>
+      <c r="A172" s="89"/>
       <c r="B172" s="50" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="173" spans="1:2">
-      <c r="A173" s="86"/>
+      <c r="A173" s="89"/>
       <c r="B173" s="50" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="174" spans="1:2">
-      <c r="A174" s="86"/>
+      <c r="A174" s="89"/>
       <c r="B174" s="50" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="175" spans="1:2">
-      <c r="A175" s="86"/>
+      <c r="A175" s="89"/>
       <c r="B175" s="50" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="176" spans="1:2">
-      <c r="A176" s="86"/>
+      <c r="A176" s="89"/>
       <c r="B176" s="50" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="177" spans="1:2">
-      <c r="A177" s="86"/>
+      <c r="A177" s="89"/>
       <c r="B177" s="50" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="178" spans="1:2">
-      <c r="A178" s="86"/>
+      <c r="A178" s="89"/>
       <c r="B178" s="50" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="179" spans="1:2">
-      <c r="A179" s="86"/>
+      <c r="A179" s="89"/>
       <c r="B179" s="50" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="180" spans="1:2">
-      <c r="A180" s="86"/>
+      <c r="A180" s="89"/>
       <c r="B180" s="50" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="181" spans="1:2">
-      <c r="A181" s="87"/>
+      <c r="A181" s="90"/>
       <c r="B181" s="52" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="182" spans="1:2">
-      <c r="A182" s="85" t="s">
+      <c r="A182" s="88" t="s">
         <v>227</v>
       </c>
       <c r="B182" s="49" t="s">
@@ -9128,19 +9132,19 @@
       </c>
     </row>
     <row r="183" spans="1:2">
-      <c r="A183" s="86"/>
+      <c r="A183" s="89"/>
       <c r="B183" s="50" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="184" spans="1:2">
-      <c r="A184" s="87"/>
+      <c r="A184" s="90"/>
       <c r="B184" s="52" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="185" spans="1:2">
-      <c r="A185" s="85" t="s">
+      <c r="A185" s="88" t="s">
         <v>231</v>
       </c>
       <c r="B185" s="49" t="s">
@@ -9148,25 +9152,25 @@
       </c>
     </row>
     <row r="186" spans="1:2">
-      <c r="A186" s="86"/>
+      <c r="A186" s="89"/>
       <c r="B186" s="50" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="187" spans="1:2">
-      <c r="A187" s="86"/>
+      <c r="A187" s="89"/>
       <c r="B187" s="50" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="188" spans="1:2">
-      <c r="A188" s="87"/>
+      <c r="A188" s="90"/>
       <c r="B188" s="52" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="189" spans="1:2">
-      <c r="A189" s="85" t="s">
+      <c r="A189" s="88" t="s">
         <v>236</v>
       </c>
       <c r="B189" s="49" t="s">
@@ -9174,13 +9178,13 @@
       </c>
     </row>
     <row r="190" spans="1:2">
-      <c r="A190" s="87"/>
+      <c r="A190" s="90"/>
       <c r="B190" s="52" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="191" spans="1:2">
-      <c r="A191" s="85" t="s">
+      <c r="A191" s="88" t="s">
         <v>239</v>
       </c>
       <c r="B191" s="49" t="s">
@@ -9188,49 +9192,49 @@
       </c>
     </row>
     <row r="192" spans="1:2">
-      <c r="A192" s="86"/>
+      <c r="A192" s="89"/>
       <c r="B192" s="50" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="193" spans="1:2">
-      <c r="A193" s="86"/>
+      <c r="A193" s="89"/>
       <c r="B193" s="50" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="194" spans="1:2">
-      <c r="A194" s="86"/>
+      <c r="A194" s="89"/>
       <c r="B194" s="50" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="195" spans="1:2">
-      <c r="A195" s="86"/>
+      <c r="A195" s="89"/>
       <c r="B195" s="50" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="196" spans="1:2">
-      <c r="A196" s="86"/>
+      <c r="A196" s="89"/>
       <c r="B196" s="50" t="s">
         <v>245</v>
       </c>
     </row>
     <row r="197" spans="1:2">
-      <c r="A197" s="86"/>
+      <c r="A197" s="89"/>
       <c r="B197" s="50" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="198" spans="1:2">
-      <c r="A198" s="87"/>
+      <c r="A198" s="90"/>
       <c r="B198" s="52" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="199" spans="1:2">
-      <c r="A199" s="85" t="s">
+      <c r="A199" s="88" t="s">
         <v>248</v>
       </c>
       <c r="B199" s="49" t="s">
@@ -9238,13 +9242,13 @@
       </c>
     </row>
     <row r="200" spans="1:2">
-      <c r="A200" s="87"/>
+      <c r="A200" s="90"/>
       <c r="B200" s="52" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="201" spans="1:2">
-      <c r="A201" s="85" t="s">
+      <c r="A201" s="88" t="s">
         <v>251</v>
       </c>
       <c r="B201" s="49" t="s">
@@ -9252,19 +9256,19 @@
       </c>
     </row>
     <row r="202" spans="1:2">
-      <c r="A202" s="86"/>
+      <c r="A202" s="89"/>
       <c r="B202" s="50" t="s">
         <v>253</v>
       </c>
     </row>
     <row r="203" spans="1:2">
-      <c r="A203" s="87"/>
+      <c r="A203" s="90"/>
       <c r="B203" s="52" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="204" spans="1:2">
-      <c r="A204" s="85" t="s">
+      <c r="A204" s="88" t="s">
         <v>255</v>
       </c>
       <c r="B204" s="49" t="s">
@@ -9272,19 +9276,19 @@
       </c>
     </row>
     <row r="205" spans="1:2">
-      <c r="A205" s="86"/>
+      <c r="A205" s="89"/>
       <c r="B205" s="50" t="s">
         <v>257</v>
       </c>
     </row>
     <row r="206" spans="1:2">
-      <c r="A206" s="86"/>
+      <c r="A206" s="89"/>
       <c r="B206" s="50" t="s">
         <v>258</v>
       </c>
     </row>
     <row r="207" spans="1:2">
-      <c r="A207" s="87"/>
+      <c r="A207" s="90"/>
       <c r="B207" s="52" t="s">
         <v>259</v>
       </c>
@@ -9298,7 +9302,7 @@
       </c>
     </row>
     <row r="209" spans="1:2">
-      <c r="A209" s="85" t="s">
+      <c r="A209" s="88" t="s">
         <v>262</v>
       </c>
       <c r="B209" s="49" t="s">
@@ -9306,13 +9310,13 @@
       </c>
     </row>
     <row r="210" spans="1:2">
-      <c r="A210" s="87"/>
+      <c r="A210" s="90"/>
       <c r="B210" s="52" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="211" spans="1:2">
-      <c r="A211" s="85" t="s">
+      <c r="A211" s="88" t="s">
         <v>265</v>
       </c>
       <c r="B211" s="49" t="s">
@@ -9320,19 +9324,19 @@
       </c>
     </row>
     <row r="212" spans="1:2">
-      <c r="A212" s="86"/>
+      <c r="A212" s="89"/>
       <c r="B212" s="50" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="213" spans="1:2">
-      <c r="A213" s="87"/>
+      <c r="A213" s="90"/>
       <c r="B213" s="52" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="214" spans="1:2">
-      <c r="A214" s="85" t="s">
+      <c r="A214" s="88" t="s">
         <v>269</v>
       </c>
       <c r="B214" s="49" t="s">
@@ -9340,19 +9344,19 @@
       </c>
     </row>
     <row r="215" spans="1:2">
-      <c r="A215" s="86"/>
+      <c r="A215" s="89"/>
       <c r="B215" s="50" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="216" spans="1:2">
-      <c r="A216" s="87"/>
+      <c r="A216" s="90"/>
       <c r="B216" s="52" t="s">
         <v>272</v>
       </c>
     </row>
     <row r="217" spans="1:2">
-      <c r="A217" s="85" t="s">
+      <c r="A217" s="88" t="s">
         <v>273</v>
       </c>
       <c r="B217" s="49" t="s">
@@ -9360,13 +9364,13 @@
       </c>
     </row>
     <row r="218" spans="1:2">
-      <c r="A218" s="86"/>
+      <c r="A218" s="89"/>
       <c r="B218" s="50" t="s">
         <v>275</v>
       </c>
     </row>
     <row r="219" spans="1:2">
-      <c r="A219" s="87"/>
+      <c r="A219" s="90"/>
       <c r="B219" s="52" t="s">
         <v>276</v>
       </c>
@@ -9380,7 +9384,7 @@
       </c>
     </row>
     <row r="221" spans="1:2">
-      <c r="A221" s="85" t="s">
+      <c r="A221" s="88" t="s">
         <v>279</v>
       </c>
       <c r="B221" s="49" t="s">
@@ -9388,13 +9392,13 @@
       </c>
     </row>
     <row r="222" spans="1:2">
-      <c r="A222" s="87"/>
+      <c r="A222" s="90"/>
       <c r="B222" s="52" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="223" spans="1:2">
-      <c r="A223" s="85" t="s">
+      <c r="A223" s="88" t="s">
         <v>282</v>
       </c>
       <c r="B223" s="49" t="s">
@@ -9402,31 +9406,31 @@
       </c>
     </row>
     <row r="224" spans="1:2">
-      <c r="A224" s="86"/>
+      <c r="A224" s="89"/>
       <c r="B224" s="50" t="s">
         <v>284</v>
       </c>
     </row>
     <row r="225" spans="1:2">
-      <c r="A225" s="86"/>
+      <c r="A225" s="89"/>
       <c r="B225" s="50" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="226" spans="1:2">
-      <c r="A226" s="86"/>
+      <c r="A226" s="89"/>
       <c r="B226" s="50" t="s">
         <v>286</v>
       </c>
     </row>
     <row r="227" spans="1:2">
-      <c r="A227" s="87"/>
+      <c r="A227" s="90"/>
       <c r="B227" s="52" t="s">
         <v>287</v>
       </c>
     </row>
     <row r="228" spans="1:2">
-      <c r="A228" s="85" t="s">
+      <c r="A228" s="88" t="s">
         <v>288</v>
       </c>
       <c r="B228" s="49" t="s">
@@ -9434,31 +9438,31 @@
       </c>
     </row>
     <row r="229" spans="1:2">
-      <c r="A229" s="86"/>
+      <c r="A229" s="89"/>
       <c r="B229" s="50" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="230" spans="1:2">
-      <c r="A230" s="86"/>
+      <c r="A230" s="89"/>
       <c r="B230" s="50" t="s">
         <v>291</v>
       </c>
     </row>
     <row r="231" spans="1:2">
-      <c r="A231" s="86"/>
+      <c r="A231" s="89"/>
       <c r="B231" s="50" t="s">
         <v>292</v>
       </c>
     </row>
     <row r="232" spans="1:2">
-      <c r="A232" s="86"/>
+      <c r="A232" s="89"/>
       <c r="B232" s="50" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="233" spans="1:2">
-      <c r="A233" s="87"/>
+      <c r="A233" s="90"/>
       <c r="B233" s="52" t="s">
         <v>294</v>
       </c>
@@ -9472,16 +9476,16 @@
       </c>
     </row>
     <row r="236" spans="1:2" ht="60" customHeight="1">
-      <c r="A236" s="80" t="s">
+      <c r="A236" s="108" t="s">
         <v>297</v>
       </c>
-      <c r="B236" s="79"/>
+      <c r="B236" s="107"/>
     </row>
     <row r="239" spans="1:2" ht="60" customHeight="1">
-      <c r="A239" s="78" t="s">
+      <c r="A239" s="106" t="s">
         <v>298</v>
       </c>
-      <c r="B239" s="79"/>
+      <c r="B239" s="107"/>
     </row>
     <row r="240" spans="1:2">
       <c r="A240" s="47"/>
@@ -9580,10 +9584,10 @@
       </c>
     </row>
     <row r="257" spans="1:2" ht="36" customHeight="1">
-      <c r="A257" s="81" t="s">
+      <c r="A257" s="109" t="s">
         <v>315</v>
       </c>
-      <c r="B257" s="82"/>
+      <c r="B257" s="110"/>
     </row>
     <row r="258" spans="1:2">
       <c r="A258" s="47"/>
@@ -9760,10 +9764,10 @@
       </c>
     </row>
     <row r="288" spans="1:2" ht="22.5">
-      <c r="A288" s="88" t="s">
+      <c r="A288" s="95" t="s">
         <v>345</v>
       </c>
-      <c r="B288" s="89"/>
+      <c r="B288" s="96"/>
     </row>
     <row r="289" spans="1:2">
       <c r="A289" s="55"/>
@@ -9954,14 +9958,22 @@
   </sheetData>
   <sheetProtection sheet="1" objects="1"/>
   <mergeCells count="40">
-    <mergeCell ref="A223:A227"/>
-    <mergeCell ref="A228:A233"/>
-    <mergeCell ref="A137:B138"/>
-    <mergeCell ref="A209:A210"/>
-    <mergeCell ref="A211:A213"/>
-    <mergeCell ref="A214:A216"/>
-    <mergeCell ref="A217:A219"/>
-    <mergeCell ref="A221:A222"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A107:B107"/>
+    <mergeCell ref="A236:B236"/>
+    <mergeCell ref="A239:B239"/>
+    <mergeCell ref="A257:B257"/>
+    <mergeCell ref="A102:A103"/>
+    <mergeCell ref="A139:A143"/>
+    <mergeCell ref="A144:A150"/>
+    <mergeCell ref="A151:A181"/>
+    <mergeCell ref="A182:A184"/>
+    <mergeCell ref="A185:A188"/>
+    <mergeCell ref="A189:A190"/>
+    <mergeCell ref="A191:A198"/>
+    <mergeCell ref="A199:A200"/>
+    <mergeCell ref="A201:A203"/>
+    <mergeCell ref="A204:A207"/>
     <mergeCell ref="A288:B288"/>
     <mergeCell ref="A2:A5"/>
     <mergeCell ref="A6:A7"/>
@@ -9978,22 +9990,14 @@
     <mergeCell ref="A72:A88"/>
     <mergeCell ref="A89:A94"/>
     <mergeCell ref="A95:A101"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A107:B107"/>
-    <mergeCell ref="A236:B236"/>
-    <mergeCell ref="A239:B239"/>
-    <mergeCell ref="A257:B257"/>
-    <mergeCell ref="A102:A103"/>
-    <mergeCell ref="A139:A143"/>
-    <mergeCell ref="A144:A150"/>
-    <mergeCell ref="A151:A181"/>
-    <mergeCell ref="A182:A184"/>
-    <mergeCell ref="A185:A188"/>
-    <mergeCell ref="A189:A190"/>
-    <mergeCell ref="A191:A198"/>
-    <mergeCell ref="A199:A200"/>
-    <mergeCell ref="A201:A203"/>
-    <mergeCell ref="A204:A207"/>
+    <mergeCell ref="A223:A227"/>
+    <mergeCell ref="A228:A233"/>
+    <mergeCell ref="A137:B138"/>
+    <mergeCell ref="A209:A210"/>
+    <mergeCell ref="A211:A213"/>
+    <mergeCell ref="A214:A216"/>
+    <mergeCell ref="A217:A219"/>
+    <mergeCell ref="A221:A222"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10013,10 +10017,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="36" customHeight="1">
-      <c r="A1" s="101" t="s">
+      <c r="A1" s="120" t="s">
         <v>377</v>
       </c>
-      <c r="B1" s="102"/>
+      <c r="B1" s="121"/>
     </row>
     <row r="2" spans="1:2" s="15" customFormat="1" ht="14.25">
       <c r="A2" s="18" t="s">
@@ -10030,7 +10034,7 @@
       <c r="A3" s="20" t="s">
         <v>380</v>
       </c>
-      <c r="B3" s="103" t="s">
+      <c r="B3" s="114" t="s">
         <v>1</v>
       </c>
     </row>
@@ -10038,25 +10042,25 @@
       <c r="A4" s="21" t="s">
         <v>381</v>
       </c>
-      <c r="B4" s="104"/>
+      <c r="B4" s="115"/>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="B5" s="104"/>
+      <c r="B5" s="115"/>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="B6" s="105"/>
+      <c r="B6" s="116"/>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="B7" s="103" t="s">
+      <c r="B7" s="114" t="s">
         <v>382</v>
       </c>
     </row>
@@ -10064,25 +10068,25 @@
       <c r="A8" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="B8" s="104"/>
+      <c r="B8" s="115"/>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="20" t="s">
         <v>147</v>
       </c>
-      <c r="B9" s="104"/>
+      <c r="B9" s="115"/>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="24" t="s">
         <v>148</v>
       </c>
-      <c r="B10" s="105"/>
+      <c r="B10" s="116"/>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="B11" s="103" t="s">
+      <c r="B11" s="114" t="s">
         <v>2</v>
       </c>
     </row>
@@ -10090,85 +10094,85 @@
       <c r="A12" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="B12" s="104"/>
+      <c r="B12" s="115"/>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="25" t="s">
         <v>44</v>
       </c>
-      <c r="B13" s="104"/>
+      <c r="B13" s="115"/>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="B14" s="104"/>
+      <c r="B14" s="115"/>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="104"/>
+      <c r="B15" s="115"/>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="104"/>
+      <c r="B16" s="115"/>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="B17" s="104"/>
+      <c r="B17" s="115"/>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="21" t="s">
         <v>383</v>
       </c>
-      <c r="B18" s="104"/>
+      <c r="B18" s="115"/>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="B19" s="104"/>
+      <c r="B19" s="115"/>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="21" t="s">
         <v>384</v>
       </c>
-      <c r="B20" s="104"/>
+      <c r="B20" s="115"/>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="26" t="s">
         <v>385</v>
       </c>
-      <c r="B21" s="104"/>
+      <c r="B21" s="115"/>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="B22" s="104"/>
+      <c r="B22" s="115"/>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="B23" s="106"/>
+      <c r="B23" s="122"/>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="B24" s="107"/>
+      <c r="B24" s="123"/>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="20" t="s">
         <v>386</v>
       </c>
-      <c r="B25" s="103" t="s">
+      <c r="B25" s="114" t="s">
         <v>3</v>
       </c>
     </row>
@@ -10176,61 +10180,61 @@
       <c r="A26" s="21" t="s">
         <v>63</v>
       </c>
-      <c r="B26" s="104"/>
+      <c r="B26" s="115"/>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="B27" s="104"/>
+      <c r="B27" s="115"/>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="B28" s="104"/>
+      <c r="B28" s="115"/>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="B29" s="104"/>
+      <c r="B29" s="115"/>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="21" t="s">
         <v>387</v>
       </c>
-      <c r="B30" s="104"/>
+      <c r="B30" s="115"/>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="B31" s="104"/>
+      <c r="B31" s="115"/>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="21" t="s">
         <v>388</v>
       </c>
-      <c r="B32" s="104"/>
+      <c r="B32" s="115"/>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="21" t="s">
         <v>389</v>
       </c>
-      <c r="B33" s="104"/>
+      <c r="B33" s="115"/>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="28" t="s">
         <v>57</v>
       </c>
-      <c r="B34" s="105"/>
+      <c r="B34" s="116"/>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="29" t="s">
         <v>390</v>
       </c>
-      <c r="B35" s="103" t="s">
+      <c r="B35" s="114" t="s">
         <v>391</v>
       </c>
     </row>
@@ -10238,13 +10242,13 @@
       <c r="A36" s="28" t="s">
         <v>392</v>
       </c>
-      <c r="B36" s="105"/>
+      <c r="B36" s="116"/>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="B37" s="103" t="s">
+      <c r="B37" s="114" t="s">
         <v>4</v>
       </c>
     </row>
@@ -10252,19 +10256,19 @@
       <c r="A38" s="26" t="s">
         <v>73</v>
       </c>
-      <c r="B38" s="104"/>
+      <c r="B38" s="115"/>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="B39" s="104"/>
+      <c r="B39" s="115"/>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="20" t="s">
         <v>393</v>
       </c>
-      <c r="B40" s="103" t="s">
+      <c r="B40" s="114" t="s">
         <v>394</v>
       </c>
     </row>
@@ -10272,37 +10276,37 @@
       <c r="A41" s="21" t="s">
         <v>395</v>
       </c>
-      <c r="B41" s="104"/>
+      <c r="B41" s="115"/>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="21" t="s">
         <v>79</v>
       </c>
-      <c r="B42" s="104"/>
+      <c r="B42" s="115"/>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="21" t="s">
         <v>396</v>
       </c>
-      <c r="B43" s="104"/>
+      <c r="B43" s="115"/>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="21" t="s">
         <v>397</v>
       </c>
-      <c r="B44" s="104"/>
+      <c r="B44" s="115"/>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="21" t="s">
         <v>82</v>
       </c>
-      <c r="B45" s="104"/>
+      <c r="B45" s="115"/>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="24" t="s">
         <v>83</v>
       </c>
-      <c r="B46" s="105"/>
+      <c r="B46" s="116"/>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="30" t="s">
@@ -10316,7 +10320,7 @@
       <c r="A48" s="21" t="s">
         <v>86</v>
       </c>
-      <c r="B48" s="103" t="s">
+      <c r="B48" s="114" t="s">
         <v>398</v>
       </c>
     </row>
@@ -10324,13 +10328,13 @@
       <c r="A49" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="B49" s="105"/>
+      <c r="B49" s="116"/>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="B50" s="103" t="s">
+      <c r="B50" s="114" t="s">
         <v>6</v>
       </c>
     </row>
@@ -10338,25 +10342,25 @@
       <c r="A51" s="21" t="s">
         <v>91</v>
       </c>
-      <c r="B51" s="104"/>
+      <c r="B51" s="115"/>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="21" t="s">
         <v>88</v>
       </c>
-      <c r="B52" s="104"/>
+      <c r="B52" s="115"/>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="B53" s="104"/>
+      <c r="B53" s="115"/>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="28" t="s">
         <v>90</v>
       </c>
-      <c r="B54" s="105"/>
+      <c r="B54" s="116"/>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="30" t="s">
@@ -10370,7 +10374,7 @@
       <c r="A56" s="29" t="s">
         <v>96</v>
       </c>
-      <c r="B56" s="103" t="s">
+      <c r="B56" s="114" t="s">
         <v>8</v>
       </c>
     </row>
@@ -10378,19 +10382,19 @@
       <c r="A57" s="26" t="s">
         <v>97</v>
       </c>
-      <c r="B57" s="104"/>
+      <c r="B57" s="115"/>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="24" t="s">
         <v>98</v>
       </c>
-      <c r="B58" s="105"/>
+      <c r="B58" s="116"/>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="21" t="s">
         <v>132</v>
       </c>
-      <c r="B59" s="103" t="s">
+      <c r="B59" s="114" t="s">
         <v>7</v>
       </c>
     </row>
@@ -10398,37 +10402,37 @@
       <c r="A60" s="21" t="s">
         <v>136</v>
       </c>
-      <c r="B60" s="104"/>
+      <c r="B60" s="115"/>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="21" t="s">
         <v>133</v>
       </c>
-      <c r="B61" s="104"/>
+      <c r="B61" s="115"/>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="21" t="s">
         <v>134</v>
       </c>
-      <c r="B62" s="104"/>
+      <c r="B62" s="115"/>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="21" t="s">
         <v>137</v>
       </c>
-      <c r="B63" s="104"/>
+      <c r="B63" s="115"/>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="32" t="s">
         <v>135</v>
       </c>
-      <c r="B64" s="105"/>
+      <c r="B64" s="116"/>
     </row>
     <row r="65" spans="1:5" ht="13.5" customHeight="1">
       <c r="A65" s="21" t="s">
         <v>401</v>
       </c>
-      <c r="B65" s="111" t="s">
+      <c r="B65" s="117" t="s">
         <v>402</v>
       </c>
     </row>
@@ -10436,26 +10440,26 @@
       <c r="A66" s="21" t="s">
         <v>75</v>
       </c>
-      <c r="B66" s="112"/>
+      <c r="B66" s="118"/>
       <c r="E66" s="33"/>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="26" t="s">
         <v>94</v>
       </c>
-      <c r="B67" s="112"/>
+      <c r="B67" s="118"/>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="21" t="s">
         <v>403</v>
       </c>
-      <c r="B68" s="113"/>
+      <c r="B68" s="119"/>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="34" t="s">
         <v>100</v>
       </c>
-      <c r="B69" s="103" t="s">
+      <c r="B69" s="114" t="s">
         <v>9</v>
       </c>
     </row>
@@ -10463,37 +10467,37 @@
       <c r="A70" s="21" t="s">
         <v>101</v>
       </c>
-      <c r="B70" s="104"/>
+      <c r="B70" s="115"/>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="35" t="s">
         <v>102</v>
       </c>
-      <c r="B71" s="104"/>
+      <c r="B71" s="115"/>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="B72" s="104"/>
+      <c r="B72" s="115"/>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="B73" s="104"/>
+      <c r="B73" s="115"/>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="21" t="s">
         <v>105</v>
       </c>
-      <c r="B74" s="105"/>
+      <c r="B74" s="116"/>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="34" t="s">
         <v>107</v>
       </c>
-      <c r="B75" s="103" t="s">
+      <c r="B75" s="114" t="s">
         <v>10</v>
       </c>
     </row>
@@ -10501,139 +10505,139 @@
       <c r="A76" s="21" t="s">
         <v>108</v>
       </c>
-      <c r="B76" s="104"/>
+      <c r="B76" s="115"/>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="21" t="s">
         <v>109</v>
       </c>
-      <c r="B77" s="104"/>
+      <c r="B77" s="115"/>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="21" t="s">
         <v>110</v>
       </c>
-      <c r="B78" s="104"/>
+      <c r="B78" s="115"/>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="21" t="s">
         <v>111</v>
       </c>
-      <c r="B79" s="104"/>
+      <c r="B79" s="115"/>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="21" t="s">
         <v>112</v>
       </c>
-      <c r="B80" s="104"/>
+      <c r="B80" s="115"/>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="21" t="s">
         <v>114</v>
       </c>
-      <c r="B81" s="104"/>
+      <c r="B81" s="115"/>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="21" t="s">
         <v>115</v>
       </c>
-      <c r="B82" s="104"/>
+      <c r="B82" s="115"/>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="21" t="s">
         <v>116</v>
       </c>
-      <c r="B83" s="104"/>
+      <c r="B83" s="115"/>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="21" t="s">
         <v>117</v>
       </c>
-      <c r="B84" s="104"/>
+      <c r="B84" s="115"/>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="21" t="s">
         <v>118</v>
       </c>
-      <c r="B85" s="104"/>
+      <c r="B85" s="115"/>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="36" t="s">
         <v>119</v>
       </c>
-      <c r="B86" s="104"/>
+      <c r="B86" s="115"/>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="21" t="s">
         <v>120</v>
       </c>
-      <c r="B87" s="104"/>
+      <c r="B87" s="115"/>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="21" t="s">
         <v>121</v>
       </c>
-      <c r="B88" s="104"/>
+      <c r="B88" s="115"/>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="21" t="s">
         <v>122</v>
       </c>
-      <c r="B89" s="104"/>
+      <c r="B89" s="115"/>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="36" t="s">
         <v>123</v>
       </c>
-      <c r="B90" s="104"/>
+      <c r="B90" s="115"/>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="21" t="s">
         <v>124</v>
       </c>
-      <c r="B91" s="104"/>
+      <c r="B91" s="115"/>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="21" t="s">
         <v>125</v>
       </c>
-      <c r="B92" s="104"/>
+      <c r="B92" s="115"/>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="21" t="s">
         <v>126</v>
       </c>
-      <c r="B93" s="104"/>
+      <c r="B93" s="115"/>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="36" t="s">
         <v>127</v>
       </c>
-      <c r="B94" s="104"/>
+      <c r="B94" s="115"/>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="36" t="s">
         <v>128</v>
       </c>
-      <c r="B95" s="104"/>
+      <c r="B95" s="115"/>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="36" t="s">
         <v>129</v>
       </c>
-      <c r="B96" s="104"/>
+      <c r="B96" s="115"/>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="21" t="s">
         <v>130</v>
       </c>
-      <c r="B97" s="104"/>
+      <c r="B97" s="115"/>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" s="37" t="s">
         <v>139</v>
       </c>
-      <c r="B98" s="108" t="s">
+      <c r="B98" s="111" t="s">
         <v>11</v>
       </c>
     </row>
@@ -10641,37 +10645,37 @@
       <c r="A99" s="36" t="s">
         <v>140</v>
       </c>
-      <c r="B99" s="109"/>
+      <c r="B99" s="112"/>
     </row>
     <row r="100" spans="1:2" s="16" customFormat="1">
       <c r="A100" s="36" t="s">
         <v>141</v>
       </c>
-      <c r="B100" s="109"/>
+      <c r="B100" s="112"/>
     </row>
     <row r="101" spans="1:2" s="16" customFormat="1">
       <c r="A101" s="36" t="s">
         <v>142</v>
       </c>
-      <c r="B101" s="109"/>
+      <c r="B101" s="112"/>
     </row>
     <row r="102" spans="1:2" s="16" customFormat="1">
       <c r="A102" s="36" t="s">
         <v>143</v>
       </c>
-      <c r="B102" s="109"/>
+      <c r="B102" s="112"/>
     </row>
     <row r="103" spans="1:2" s="16" customFormat="1">
       <c r="A103" s="36" t="s">
         <v>144</v>
       </c>
-      <c r="B103" s="109"/>
+      <c r="B103" s="112"/>
     </row>
     <row r="104" spans="1:2" s="16" customFormat="1">
       <c r="A104" s="32" t="s">
         <v>145</v>
       </c>
-      <c r="B104" s="110"/>
+      <c r="B104" s="113"/>
     </row>
     <row r="105" spans="1:2" s="16" customFormat="1">
       <c r="A105" s="38" t="s">
@@ -10683,22 +10687,22 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="B3:B6"/>
+    <mergeCell ref="B7:B10"/>
+    <mergeCell ref="B11:B24"/>
+    <mergeCell ref="B25:B34"/>
+    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="B37:B39"/>
+    <mergeCell ref="B40:B46"/>
+    <mergeCell ref="B48:B49"/>
+    <mergeCell ref="B50:B54"/>
     <mergeCell ref="B98:B104"/>
     <mergeCell ref="B56:B58"/>
     <mergeCell ref="B59:B64"/>
     <mergeCell ref="B65:B68"/>
     <mergeCell ref="B69:B74"/>
     <mergeCell ref="B75:B97"/>
-    <mergeCell ref="B35:B36"/>
-    <mergeCell ref="B37:B39"/>
-    <mergeCell ref="B40:B46"/>
-    <mergeCell ref="B48:B49"/>
-    <mergeCell ref="B50:B54"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="B3:B6"/>
-    <mergeCell ref="B7:B10"/>
-    <mergeCell ref="B11:B24"/>
-    <mergeCell ref="B25:B34"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <hyperlinks>
@@ -10736,15 +10740,16 @@
   <cols>
     <col min="1" max="1" width="18" style="9" customWidth="1"/>
     <col min="2" max="2" width="35.5" style="10" customWidth="1"/>
-    <col min="3" max="256" width="9.125" style="9"/>
+    <col min="3" max="3" width="26.5" style="9" customWidth="1"/>
+    <col min="4" max="256" width="9.125" style="9"/>
     <col min="257" max="16384" width="9.125" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="27" customHeight="1">
-      <c r="A1" s="114" t="s">
+      <c r="A1" s="124" t="s">
         <v>405</v>
       </c>
-      <c r="B1" s="115"/>
+      <c r="B1" s="125"/>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="11" t="s">
@@ -10753,6 +10758,10 @@
       <c r="B2" s="4" t="s">
         <v>407</v>
       </c>
+      <c r="C2" s="9" t="str">
+        <f xml:space="preserve"> A2 &amp; " " &amp; B2</f>
+        <v>AFG 阿富汗</v>
+      </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="12" t="s">
@@ -10761,6 +10770,10 @@
       <c r="B3" s="6" t="s">
         <v>409</v>
       </c>
+      <c r="C3" s="9" t="str">
+        <f t="shared" ref="C3:C66" si="0" xml:space="preserve"> A3 &amp; " " &amp; B3</f>
+        <v>ALB 阿尔巴尼亚</v>
+      </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="12" t="s">
@@ -10769,6 +10782,10 @@
       <c r="B4" s="6" t="s">
         <v>411</v>
       </c>
+      <c r="C4" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>DZA 阿尔及利亚</v>
+      </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="12" t="s">
@@ -10777,6 +10794,10 @@
       <c r="B5" s="6" t="s">
         <v>413</v>
       </c>
+      <c r="C5" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>ASM 美属萨摩亚</v>
+      </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="12" t="s">
@@ -10785,6 +10806,10 @@
       <c r="B6" s="6" t="s">
         <v>415</v>
       </c>
+      <c r="C6" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>AND 安道尔</v>
+      </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="12" t="s">
@@ -10793,6 +10818,10 @@
       <c r="B7" s="6" t="s">
         <v>417</v>
       </c>
+      <c r="C7" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>AGO 安哥拉</v>
+      </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="12" t="s">
@@ -10801,6 +10830,10 @@
       <c r="B8" s="6" t="s">
         <v>419</v>
       </c>
+      <c r="C8" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>AIA 安圭拉</v>
+      </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="12" t="s">
@@ -10809,6 +10842,10 @@
       <c r="B9" s="6" t="s">
         <v>421</v>
       </c>
+      <c r="C9" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>ATA 南极洲</v>
+      </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="12" t="s">
@@ -10817,6 +10854,10 @@
       <c r="B10" s="6" t="s">
         <v>423</v>
       </c>
+      <c r="C10" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>ATG 安提瓜和巴布达</v>
+      </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="12" t="s">
@@ -10825,6 +10866,10 @@
       <c r="B11" s="6" t="s">
         <v>425</v>
       </c>
+      <c r="C11" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>ARG 阿根廷</v>
+      </c>
       <c r="D11" s="13"/>
     </row>
     <row r="12" spans="1:4">
@@ -10834,6 +10879,10 @@
       <c r="B12" s="6" t="s">
         <v>427</v>
       </c>
+      <c r="C12" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>ARM 亚美尼亚</v>
+      </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="12" t="s">
@@ -10842,6 +10891,10 @@
       <c r="B13" s="6" t="s">
         <v>429</v>
       </c>
+      <c r="C13" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>ABW 阿鲁巴</v>
+      </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="12" t="s">
@@ -10850,6 +10903,10 @@
       <c r="B14" s="6" t="s">
         <v>431</v>
       </c>
+      <c r="C14" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>AUS 澳大利亚</v>
+      </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="12" t="s">
@@ -10858,6 +10915,10 @@
       <c r="B15" s="6" t="s">
         <v>433</v>
       </c>
+      <c r="C15" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>AUT 奥地利</v>
+      </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="12" t="s">
@@ -10866,1801 +10927,2700 @@
       <c r="B16" s="6" t="s">
         <v>435</v>
       </c>
-    </row>
-    <row r="17" spans="1:2">
+      <c r="C16" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>AZE 阿塞拜疆</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
       <c r="A17" s="12" t="s">
         <v>436</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>437</v>
       </c>
-    </row>
-    <row r="18" spans="1:2">
+      <c r="C17" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>BHS 巴哈马</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
       <c r="A18" s="12" t="s">
         <v>438</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>439</v>
       </c>
-    </row>
-    <row r="19" spans="1:2">
+      <c r="C18" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>BHR 巴林</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
       <c r="A19" s="12" t="s">
         <v>440</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>441</v>
       </c>
-    </row>
-    <row r="20" spans="1:2">
+      <c r="C19" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>BGD 孟加拉国</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
       <c r="A20" s="12" t="s">
         <v>442</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>443</v>
       </c>
-    </row>
-    <row r="21" spans="1:2">
+      <c r="C20" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>BRB 巴巴多斯</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
       <c r="A21" s="12" t="s">
         <v>444</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="22" spans="1:2">
+      <c r="C21" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>BLR 白俄罗斯</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
       <c r="A22" s="12" t="s">
         <v>446</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>447</v>
       </c>
-    </row>
-    <row r="23" spans="1:2">
+      <c r="C22" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>BEL 比利时</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
       <c r="A23" s="12" t="s">
         <v>448</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>449</v>
       </c>
-    </row>
-    <row r="24" spans="1:2">
+      <c r="C23" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>BLZ 伯利兹</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
       <c r="A24" s="12" t="s">
         <v>450</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>451</v>
       </c>
-    </row>
-    <row r="25" spans="1:2">
+      <c r="C24" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>BEN 贝宁</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
       <c r="A25" s="12" t="s">
         <v>452</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>453</v>
       </c>
-    </row>
-    <row r="26" spans="1:2">
+      <c r="C25" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>BMU 百慕大</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
       <c r="A26" s="12" t="s">
         <v>454</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>455</v>
       </c>
-    </row>
-    <row r="27" spans="1:2">
+      <c r="C26" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>BTN 不丹</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
       <c r="A27" s="12" t="s">
         <v>456</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>457</v>
       </c>
-    </row>
-    <row r="28" spans="1:2">
+      <c r="C27" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>BOL 玻利维亚</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
       <c r="A28" s="12" t="s">
         <v>458</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>459</v>
       </c>
-    </row>
-    <row r="29" spans="1:2">
+      <c r="C28" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>BIH 波黑</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
       <c r="A29" s="12" t="s">
         <v>460</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>461</v>
       </c>
-    </row>
-    <row r="30" spans="1:2">
+      <c r="C29" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>BWA 博茨瓦纳</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
       <c r="A30" s="12" t="s">
         <v>462</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>463</v>
       </c>
-    </row>
-    <row r="31" spans="1:2">
+      <c r="C30" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>BVT 布维岛</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
       <c r="A31" s="12" t="s">
         <v>464</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>465</v>
       </c>
-    </row>
-    <row r="32" spans="1:2">
+      <c r="C31" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>BRA 巴西</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
       <c r="A32" s="12" t="s">
         <v>466</v>
       </c>
       <c r="B32" s="6" t="s">
         <v>467</v>
       </c>
-    </row>
-    <row r="33" spans="1:2">
+      <c r="C32" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>IOT 英属印度洋领土</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
       <c r="A33" s="12" t="s">
         <v>468</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>469</v>
       </c>
-    </row>
-    <row r="34" spans="1:2">
+      <c r="C33" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>BRN 文莱</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
       <c r="A34" s="12" t="s">
         <v>470</v>
       </c>
       <c r="B34" s="6" t="s">
         <v>471</v>
       </c>
-    </row>
-    <row r="35" spans="1:2">
+      <c r="C34" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>BGR 保加利亚</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
       <c r="A35" s="12" t="s">
         <v>472</v>
       </c>
       <c r="B35" s="6" t="s">
         <v>473</v>
       </c>
-    </row>
-    <row r="36" spans="1:2">
+      <c r="C35" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>BFA 布基纳法索</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
       <c r="A36" s="12" t="s">
         <v>474</v>
       </c>
       <c r="B36" s="6" t="s">
         <v>475</v>
       </c>
-    </row>
-    <row r="37" spans="1:2">
+      <c r="C36" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>BDI 布隆迪</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
       <c r="A37" s="12" t="s">
         <v>476</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>477</v>
       </c>
-    </row>
-    <row r="38" spans="1:2">
+      <c r="C37" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>KHM 柬埔寨</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
       <c r="A38" s="12" t="s">
         <v>478</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>479</v>
       </c>
-    </row>
-    <row r="39" spans="1:2">
+      <c r="C38" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>CMR 喀麦隆</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
       <c r="A39" s="12" t="s">
         <v>480</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>481</v>
       </c>
-    </row>
-    <row r="40" spans="1:2">
+      <c r="C39" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>CAN 加拿大</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
       <c r="A40" s="12" t="s">
         <v>482</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>483</v>
       </c>
-    </row>
-    <row r="41" spans="1:2">
+      <c r="C40" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>CPV 佛得角</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
       <c r="A41" s="12" t="s">
         <v>484</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>485</v>
       </c>
-    </row>
-    <row r="42" spans="1:2">
+      <c r="C41" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>CYM 开曼群岛</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
       <c r="A42" s="12" t="s">
         <v>486</v>
       </c>
       <c r="B42" s="6" t="s">
         <v>487</v>
       </c>
-    </row>
-    <row r="43" spans="1:2">
+      <c r="C42" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>CAF 中非</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
       <c r="A43" s="12" t="s">
         <v>488</v>
       </c>
       <c r="B43" s="6" t="s">
         <v>489</v>
       </c>
-    </row>
-    <row r="44" spans="1:2">
+      <c r="C43" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>TCD 乍得</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
       <c r="A44" s="12" t="s">
         <v>490</v>
       </c>
       <c r="B44" s="6" t="s">
         <v>491</v>
       </c>
-    </row>
-    <row r="45" spans="1:2">
+      <c r="C44" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>CHL 智利</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
       <c r="A45" s="12" t="s">
         <v>492</v>
       </c>
       <c r="B45" s="6" t="s">
         <v>493</v>
       </c>
-    </row>
-    <row r="46" spans="1:2">
+      <c r="C45" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>CHN 中国</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
       <c r="A46" s="12" t="s">
         <v>494</v>
       </c>
       <c r="B46" s="6" t="s">
         <v>495</v>
       </c>
-    </row>
-    <row r="47" spans="1:2">
+      <c r="C46" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>HKG 香港</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
       <c r="A47" s="12" t="s">
         <v>496</v>
       </c>
       <c r="B47" s="6" t="s">
         <v>497</v>
       </c>
-    </row>
-    <row r="48" spans="1:2">
+      <c r="C47" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>MAC 澳门</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
       <c r="A48" s="12" t="s">
         <v>498</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>499</v>
       </c>
-    </row>
-    <row r="49" spans="1:2">
+      <c r="C48" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>TWN 台湾</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
       <c r="A49" s="12" t="s">
         <v>500</v>
       </c>
       <c r="B49" s="6" t="s">
         <v>501</v>
       </c>
-    </row>
-    <row r="50" spans="1:2">
+      <c r="C49" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>CSR 圣诞岛</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
       <c r="A50" s="12" t="s">
         <v>502</v>
       </c>
       <c r="B50" s="6" t="s">
         <v>503</v>
       </c>
-    </row>
-    <row r="51" spans="1:2">
+      <c r="C50" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>CCK 科科斯(基林)群岛</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
       <c r="A51" s="12" t="s">
         <v>504</v>
       </c>
       <c r="B51" s="6" t="s">
         <v>505</v>
       </c>
-    </row>
-    <row r="52" spans="1:2">
+      <c r="C51" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>COL 哥伦比亚</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
       <c r="A52" s="12" t="s">
         <v>506</v>
       </c>
       <c r="B52" s="6" t="s">
         <v>507</v>
       </c>
-    </row>
-    <row r="53" spans="1:2">
+      <c r="C52" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>COM 科摩罗</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
       <c r="A53" s="12" t="s">
         <v>508</v>
       </c>
       <c r="B53" s="6" t="s">
         <v>509</v>
       </c>
-    </row>
-    <row r="54" spans="1:2">
+      <c r="C53" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>COG 刚果（布）</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
       <c r="A54" s="12" t="s">
         <v>510</v>
       </c>
       <c r="B54" s="6" t="s">
         <v>511</v>
       </c>
-    </row>
-    <row r="55" spans="1:2">
+      <c r="C54" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>COD 刚果（金）</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
       <c r="A55" s="12" t="s">
         <v>512</v>
       </c>
       <c r="B55" s="6" t="s">
         <v>513</v>
       </c>
-    </row>
-    <row r="56" spans="1:2">
+      <c r="C55" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>COK 库克群岛</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
       <c r="A56" s="12" t="s">
         <v>514</v>
       </c>
       <c r="B56" s="6" t="s">
         <v>515</v>
       </c>
-    </row>
-    <row r="57" spans="1:2">
+      <c r="C56" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>CRI 哥斯达黎加</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
       <c r="A57" s="12" t="s">
         <v>516</v>
       </c>
       <c r="B57" s="6" t="s">
         <v>517</v>
       </c>
-    </row>
-    <row r="58" spans="1:2">
+      <c r="C57" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>CIV 科特迪瓦</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3">
       <c r="A58" s="12" t="s">
         <v>518</v>
       </c>
       <c r="B58" s="6" t="s">
         <v>519</v>
       </c>
-    </row>
-    <row r="59" spans="1:2">
+      <c r="C58" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>HRV 克罗地亚</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
       <c r="A59" s="12" t="s">
         <v>520</v>
       </c>
       <c r="B59" s="6" t="s">
         <v>521</v>
       </c>
-    </row>
-    <row r="60" spans="1:2">
+      <c r="C59" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>CUB 古巴</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3">
       <c r="A60" s="12" t="s">
         <v>522</v>
       </c>
       <c r="B60" s="6" t="s">
         <v>523</v>
       </c>
-    </row>
-    <row r="61" spans="1:2">
+      <c r="C60" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>CYP 塞浦路斯</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3">
       <c r="A61" s="12" t="s">
         <v>524</v>
       </c>
       <c r="B61" s="6" t="s">
         <v>525</v>
       </c>
-    </row>
-    <row r="62" spans="1:2">
+      <c r="C61" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>CZE 捷克</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3">
       <c r="A62" s="12" t="s">
         <v>526</v>
       </c>
       <c r="B62" s="6" t="s">
         <v>527</v>
       </c>
-    </row>
-    <row r="63" spans="1:2">
+      <c r="C62" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>DNK 丹麦</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3">
       <c r="A63" s="12" t="s">
         <v>528</v>
       </c>
       <c r="B63" s="6" t="s">
         <v>529</v>
       </c>
-    </row>
-    <row r="64" spans="1:2">
+      <c r="C63" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>DJI 吉布提</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3">
       <c r="A64" s="12" t="s">
         <v>530</v>
       </c>
       <c r="B64" s="6" t="s">
         <v>531</v>
       </c>
-    </row>
-    <row r="65" spans="1:2">
+      <c r="C64" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>DMA 多米尼克</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
       <c r="A65" s="12" t="s">
         <v>532</v>
       </c>
       <c r="B65" s="6" t="s">
         <v>533</v>
       </c>
-    </row>
-    <row r="66" spans="1:2">
+      <c r="C65" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>DOM 多米尼加共和国</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
       <c r="A66" s="12" t="s">
         <v>534</v>
       </c>
       <c r="B66" s="6" t="s">
         <v>535</v>
       </c>
-    </row>
-    <row r="67" spans="1:2">
+      <c r="C66" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>TMP 东帝汶</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3">
       <c r="A67" s="12" t="s">
         <v>536</v>
       </c>
       <c r="B67" s="6" t="s">
         <v>537</v>
       </c>
-    </row>
-    <row r="68" spans="1:2">
+      <c r="C67" s="9" t="str">
+        <f t="shared" ref="C67:C130" si="1" xml:space="preserve"> A67 &amp; " " &amp; B67</f>
+        <v>ECU 厄瓜多尔</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3">
       <c r="A68" s="12" t="s">
         <v>538</v>
       </c>
       <c r="B68" s="6" t="s">
         <v>539</v>
       </c>
-    </row>
-    <row r="69" spans="1:2">
+      <c r="C68" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>EGY 埃及</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3">
       <c r="A69" s="12" t="s">
         <v>540</v>
       </c>
       <c r="B69" s="6" t="s">
         <v>541</v>
       </c>
-    </row>
-    <row r="70" spans="1:2">
+      <c r="C69" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>SLV 萨尔瓦多</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3">
       <c r="A70" s="12" t="s">
         <v>542</v>
       </c>
       <c r="B70" s="6" t="s">
         <v>543</v>
       </c>
-    </row>
-    <row r="71" spans="1:2">
+      <c r="C70" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>GNQ 赤道几内亚</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3">
       <c r="A71" s="12" t="s">
         <v>544</v>
       </c>
       <c r="B71" s="6" t="s">
         <v>545</v>
       </c>
-    </row>
-    <row r="72" spans="1:2">
+      <c r="C71" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>ERI 厄立特里亚</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3">
       <c r="A72" s="12" t="s">
         <v>546</v>
       </c>
       <c r="B72" s="6" t="s">
         <v>547</v>
       </c>
-    </row>
-    <row r="73" spans="1:2">
+      <c r="C72" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>EST 爱沙尼亚</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3">
       <c r="A73" s="12" t="s">
         <v>548</v>
       </c>
       <c r="B73" s="6" t="s">
         <v>549</v>
       </c>
-    </row>
-    <row r="74" spans="1:2">
+      <c r="C73" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>ETH 埃塞俄比亚</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3">
       <c r="A74" s="12" t="s">
         <v>550</v>
       </c>
       <c r="B74" s="6" t="s">
         <v>551</v>
       </c>
-    </row>
-    <row r="75" spans="1:2">
+      <c r="C74" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>FLK 福克兰群岛(马尔维纳斯)</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3">
       <c r="A75" s="12" t="s">
         <v>552</v>
       </c>
       <c r="B75" s="6" t="s">
         <v>553</v>
       </c>
-    </row>
-    <row r="76" spans="1:2">
+      <c r="C75" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>FRO 法罗群岛</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3">
       <c r="A76" s="12" t="s">
         <v>554</v>
       </c>
       <c r="B76" s="6" t="s">
         <v>555</v>
       </c>
-    </row>
-    <row r="77" spans="1:2">
+      <c r="C76" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>FJI 斐济</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3">
       <c r="A77" s="12" t="s">
         <v>556</v>
       </c>
       <c r="B77" s="6" t="s">
         <v>557</v>
       </c>
-    </row>
-    <row r="78" spans="1:2">
+      <c r="C77" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>FIN 芬兰</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3">
       <c r="A78" s="12" t="s">
         <v>558</v>
       </c>
       <c r="B78" s="6" t="s">
         <v>559</v>
       </c>
-    </row>
-    <row r="79" spans="1:2">
+      <c r="C78" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>FRA 法国</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3">
       <c r="A79" s="12" t="s">
         <v>560</v>
       </c>
       <c r="B79" s="6" t="s">
         <v>561</v>
       </c>
-    </row>
-    <row r="80" spans="1:2">
+      <c r="C79" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>GUF 法属圭亚那</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3">
       <c r="A80" s="12" t="s">
         <v>562</v>
       </c>
       <c r="B80" s="6" t="s">
         <v>563</v>
       </c>
-    </row>
-    <row r="81" spans="1:2">
+      <c r="C80" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>PYF 法属波利尼西亚</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3">
       <c r="A81" s="12" t="s">
         <v>564</v>
       </c>
       <c r="B81" s="6" t="s">
         <v>565</v>
       </c>
-    </row>
-    <row r="82" spans="1:2">
+      <c r="C81" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>ATF 法属南部领土</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3">
       <c r="A82" s="12" t="s">
         <v>566</v>
       </c>
       <c r="B82" s="6" t="s">
         <v>567</v>
       </c>
-    </row>
-    <row r="83" spans="1:2">
+      <c r="C82" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>GAB 加蓬</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3">
       <c r="A83" s="12" t="s">
         <v>568</v>
       </c>
       <c r="B83" s="6" t="s">
         <v>569</v>
       </c>
-    </row>
-    <row r="84" spans="1:2">
+      <c r="C83" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>GMB 冈比亚Gambia</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3">
       <c r="A84" s="12" t="s">
         <v>570</v>
       </c>
       <c r="B84" s="6" t="s">
         <v>571</v>
       </c>
-    </row>
-    <row r="85" spans="1:2">
+      <c r="C84" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>GEO 格鲁吉亚</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3">
       <c r="A85" s="12" t="s">
         <v>572</v>
       </c>
       <c r="B85" s="6" t="s">
         <v>573</v>
       </c>
-    </row>
-    <row r="86" spans="1:2">
+      <c r="C85" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>DEU 德国</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3">
       <c r="A86" s="12" t="s">
         <v>574</v>
       </c>
       <c r="B86" s="6" t="s">
         <v>575</v>
       </c>
-    </row>
-    <row r="87" spans="1:2">
+      <c r="C86" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>GHA 加纳</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3">
       <c r="A87" s="12" t="s">
         <v>576</v>
       </c>
       <c r="B87" s="6" t="s">
         <v>577</v>
       </c>
-    </row>
-    <row r="88" spans="1:2">
+      <c r="C87" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>GIB 直布罗陀</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3">
       <c r="A88" s="12" t="s">
         <v>578</v>
       </c>
       <c r="B88" s="6" t="s">
         <v>579</v>
       </c>
-    </row>
-    <row r="89" spans="1:2">
+      <c r="C88" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>GRC 希腊</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3">
       <c r="A89" s="12" t="s">
         <v>580</v>
       </c>
       <c r="B89" s="6" t="s">
         <v>581</v>
       </c>
-    </row>
-    <row r="90" spans="1:2">
+      <c r="C89" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>GRL 格陵兰</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3">
       <c r="A90" s="12" t="s">
         <v>582</v>
       </c>
       <c r="B90" s="6" t="s">
         <v>583</v>
       </c>
-    </row>
-    <row r="91" spans="1:2">
+      <c r="C90" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>GRD 格林纳达</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3">
       <c r="A91" s="12" t="s">
         <v>584</v>
       </c>
       <c r="B91" s="6" t="s">
         <v>585</v>
       </c>
-    </row>
-    <row r="92" spans="1:2">
+      <c r="C91" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>GLP 瓜德罗普</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3">
       <c r="A92" s="12" t="s">
         <v>586</v>
       </c>
       <c r="B92" s="6" t="s">
         <v>587</v>
       </c>
-    </row>
-    <row r="93" spans="1:2">
+      <c r="C92" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>GUM 关岛</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3">
       <c r="A93" s="12" t="s">
         <v>588</v>
       </c>
       <c r="B93" s="6" t="s">
         <v>589</v>
       </c>
-    </row>
-    <row r="94" spans="1:2">
+      <c r="C93" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>GTM 危地马拉</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3">
       <c r="A94" s="12" t="s">
         <v>590</v>
       </c>
       <c r="B94" s="6" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="95" spans="1:2">
+      <c r="C94" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>GIN 几内亚</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3">
       <c r="A95" s="12" t="s">
         <v>592</v>
       </c>
       <c r="B95" s="6" t="s">
         <v>593</v>
       </c>
-    </row>
-    <row r="96" spans="1:2">
+      <c r="C95" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>GNB 几内亚比绍</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3">
       <c r="A96" s="12" t="s">
         <v>594</v>
       </c>
       <c r="B96" s="6" t="s">
         <v>595</v>
       </c>
-    </row>
-    <row r="97" spans="1:2">
+      <c r="C96" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>GUY 圭亚那</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3">
       <c r="A97" s="12" t="s">
         <v>596</v>
       </c>
       <c r="B97" s="6" t="s">
         <v>597</v>
       </c>
-    </row>
-    <row r="98" spans="1:2">
+      <c r="C97" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>HTI 海地</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3">
       <c r="A98" s="12" t="s">
         <v>598</v>
       </c>
       <c r="B98" s="6" t="s">
         <v>599</v>
       </c>
-    </row>
-    <row r="99" spans="1:2">
+      <c r="C98" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>HMD 赫德岛和麦克唐纳岛</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3">
       <c r="A99" s="12" t="s">
         <v>600</v>
       </c>
       <c r="B99" s="6" t="s">
         <v>601</v>
       </c>
-    </row>
-    <row r="100" spans="1:2">
+      <c r="C99" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>HND 洪都拉斯</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3">
       <c r="A100" s="12" t="s">
         <v>602</v>
       </c>
       <c r="B100" s="6" t="s">
         <v>603</v>
       </c>
-    </row>
-    <row r="101" spans="1:2">
+      <c r="C100" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>HUN 匈牙利</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3">
       <c r="A101" s="12" t="s">
         <v>604</v>
       </c>
       <c r="B101" s="6" t="s">
         <v>605</v>
       </c>
-    </row>
-    <row r="102" spans="1:2">
+      <c r="C101" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>ISL 冰岛</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3">
       <c r="A102" s="12" t="s">
         <v>606</v>
       </c>
       <c r="B102" s="6" t="s">
         <v>607</v>
       </c>
-    </row>
-    <row r="103" spans="1:2">
+      <c r="C102" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>IND 印度</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3">
       <c r="A103" s="12" t="s">
         <v>608</v>
       </c>
       <c r="B103" s="6" t="s">
         <v>609</v>
       </c>
-    </row>
-    <row r="104" spans="1:2">
+      <c r="C103" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>IDN 印度尼西亚</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3">
       <c r="A104" s="12" t="s">
         <v>610</v>
       </c>
       <c r="B104" s="6" t="s">
         <v>611</v>
       </c>
-    </row>
-    <row r="105" spans="1:2">
+      <c r="C104" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>IRN 伊朗</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3">
       <c r="A105" s="12" t="s">
         <v>612</v>
       </c>
       <c r="B105" s="6" t="s">
         <v>613</v>
       </c>
-    </row>
-    <row r="106" spans="1:2">
+      <c r="C105" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>IRQ 伊拉克</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3">
       <c r="A106" s="12" t="s">
         <v>614</v>
       </c>
       <c r="B106" s="6" t="s">
         <v>615</v>
       </c>
-    </row>
-    <row r="107" spans="1:2">
+      <c r="C106" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>IRL 爱尔兰</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3">
       <c r="A107" s="12" t="s">
         <v>616</v>
       </c>
       <c r="B107" s="6" t="s">
         <v>617</v>
       </c>
-    </row>
-    <row r="108" spans="1:2">
+      <c r="C107" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>ISR 以色列</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3">
       <c r="A108" s="12" t="s">
         <v>618</v>
       </c>
       <c r="B108" s="6" t="s">
         <v>619</v>
       </c>
-    </row>
-    <row r="109" spans="1:2">
+      <c r="C108" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>ITA 意大利</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3">
       <c r="A109" s="12" t="s">
         <v>620</v>
       </c>
       <c r="B109" s="6" t="s">
         <v>621</v>
       </c>
-    </row>
-    <row r="110" spans="1:2">
+      <c r="C109" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>JAM 牙买加</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3">
       <c r="A110" s="12" t="s">
         <v>622</v>
       </c>
       <c r="B110" s="6" t="s">
         <v>623</v>
       </c>
-    </row>
-    <row r="111" spans="1:2">
+      <c r="C110" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>JPN 日本</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3">
       <c r="A111" s="12" t="s">
         <v>624</v>
       </c>
       <c r="B111" s="6" t="s">
         <v>625</v>
       </c>
-    </row>
-    <row r="112" spans="1:2">
+      <c r="C111" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>JOR 约旦</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3">
       <c r="A112" s="12" t="s">
         <v>626</v>
       </c>
       <c r="B112" s="6" t="s">
         <v>627</v>
       </c>
-    </row>
-    <row r="113" spans="1:2">
+      <c r="C112" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>KAZ 哈萨克斯坦</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3">
       <c r="A113" s="12" t="s">
         <v>628</v>
       </c>
       <c r="B113" s="6" t="s">
         <v>629</v>
       </c>
-    </row>
-    <row r="114" spans="1:2">
+      <c r="C113" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>KEN 肯尼亚</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3">
       <c r="A114" s="12" t="s">
         <v>630</v>
       </c>
       <c r="B114" s="6" t="s">
         <v>631</v>
       </c>
-    </row>
-    <row r="115" spans="1:2">
+      <c r="C114" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>KIR 基里巴斯</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3">
       <c r="A115" s="12" t="s">
         <v>632</v>
       </c>
       <c r="B115" s="6" t="s">
         <v>633</v>
       </c>
-    </row>
-    <row r="116" spans="1:2">
+      <c r="C115" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>PRK 朝鲜</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3">
       <c r="A116" s="12" t="s">
         <v>634</v>
       </c>
       <c r="B116" s="6" t="s">
         <v>635</v>
       </c>
-    </row>
-    <row r="117" spans="1:2">
+      <c r="C116" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>KOR 韩国</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3">
       <c r="A117" s="12" t="s">
         <v>636</v>
       </c>
       <c r="B117" s="6" t="s">
         <v>637</v>
       </c>
-    </row>
-    <row r="118" spans="1:2">
+      <c r="C117" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>KWT 科威特</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3">
       <c r="A118" s="12" t="s">
         <v>638</v>
       </c>
       <c r="B118" s="6" t="s">
         <v>639</v>
       </c>
-    </row>
-    <row r="119" spans="1:2">
+      <c r="C118" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>KGZ 吉尔吉斯斯坦</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3">
       <c r="A119" s="12" t="s">
         <v>640</v>
       </c>
       <c r="B119" s="6" t="s">
         <v>641</v>
       </c>
-    </row>
-    <row r="120" spans="1:2">
+      <c r="C119" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>LAO 老挝</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3">
       <c r="A120" s="12" t="s">
         <v>642</v>
       </c>
       <c r="B120" s="6" t="s">
         <v>643</v>
       </c>
-    </row>
-    <row r="121" spans="1:2">
+      <c r="C120" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>LVA 拉脱维亚</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3">
       <c r="A121" s="12" t="s">
         <v>644</v>
       </c>
       <c r="B121" s="6" t="s">
         <v>645</v>
       </c>
-    </row>
-    <row r="122" spans="1:2">
+      <c r="C121" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>LBN 黎巴嫩</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3">
       <c r="A122" s="12" t="s">
         <v>646</v>
       </c>
       <c r="B122" s="6" t="s">
         <v>647</v>
       </c>
-    </row>
-    <row r="123" spans="1:2">
+      <c r="C122" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>LSO 莱索托</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3">
       <c r="A123" s="12" t="s">
         <v>648</v>
       </c>
       <c r="B123" s="6" t="s">
         <v>649</v>
       </c>
-    </row>
-    <row r="124" spans="1:2">
+      <c r="C123" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>LBR 利比里亚</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3">
       <c r="A124" s="12" t="s">
         <v>650</v>
       </c>
       <c r="B124" s="6" t="s">
         <v>651</v>
       </c>
-    </row>
-    <row r="125" spans="1:2">
+      <c r="C124" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>LBY 利比亚</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3">
       <c r="A125" s="12" t="s">
         <v>652</v>
       </c>
       <c r="B125" s="6" t="s">
         <v>653</v>
       </c>
-    </row>
-    <row r="126" spans="1:2">
+      <c r="C125" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>LIE 列支敦士登</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3">
       <c r="A126" s="12" t="s">
         <v>654</v>
       </c>
       <c r="B126" s="6" t="s">
         <v>655</v>
       </c>
-    </row>
-    <row r="127" spans="1:2">
+      <c r="C126" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>LTU 立陶宛</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3">
       <c r="A127" s="12" t="s">
         <v>656</v>
       </c>
       <c r="B127" s="6" t="s">
         <v>657</v>
       </c>
-    </row>
-    <row r="128" spans="1:2">
+      <c r="C127" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>LUX 卢森堡</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3">
       <c r="A128" s="12" t="s">
         <v>658</v>
       </c>
       <c r="B128" s="6" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="129" spans="1:2">
+      <c r="C128" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>MKD 前南马其顿</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3">
       <c r="A129" s="12" t="s">
         <v>660</v>
       </c>
       <c r="B129" s="6" t="s">
         <v>661</v>
       </c>
-    </row>
-    <row r="130" spans="1:2">
+      <c r="C129" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>MDG 马达加斯加</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3">
       <c r="A130" s="12" t="s">
         <v>662</v>
       </c>
       <c r="B130" s="6" t="s">
         <v>663</v>
       </c>
-    </row>
-    <row r="131" spans="1:2">
+      <c r="C130" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>MWI 马拉维</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3">
       <c r="A131" s="12" t="s">
         <v>664</v>
       </c>
       <c r="B131" s="6" t="s">
         <v>665</v>
       </c>
-    </row>
-    <row r="132" spans="1:2">
+      <c r="C131" s="9" t="str">
+        <f t="shared" ref="C131:C194" si="2" xml:space="preserve"> A131 &amp; " " &amp; B131</f>
+        <v>MYS 马来西亚</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3">
       <c r="A132" s="12" t="s">
         <v>666</v>
       </c>
       <c r="B132" s="6" t="s">
         <v>667</v>
       </c>
-    </row>
-    <row r="133" spans="1:2">
+      <c r="C132" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>MDV 马尔代夫</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3">
       <c r="A133" s="12" t="s">
         <v>668</v>
       </c>
       <c r="B133" s="6" t="s">
         <v>669</v>
       </c>
-    </row>
-    <row r="134" spans="1:2">
+      <c r="C133" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>MLI 马里</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3">
       <c r="A134" s="12" t="s">
         <v>670</v>
       </c>
       <c r="B134" s="6" t="s">
         <v>671</v>
       </c>
-    </row>
-    <row r="135" spans="1:2">
+      <c r="C134" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>MLT 马耳他</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3">
       <c r="A135" s="12" t="s">
         <v>672</v>
       </c>
       <c r="B135" s="6" t="s">
         <v>673</v>
       </c>
-    </row>
-    <row r="136" spans="1:2">
+      <c r="C135" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>MHL 马绍尔群岛</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3">
       <c r="A136" s="12" t="s">
         <v>674</v>
       </c>
       <c r="B136" s="6" t="s">
         <v>675</v>
       </c>
-    </row>
-    <row r="137" spans="1:2">
+      <c r="C136" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>MTQ 马提尼克</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3">
       <c r="A137" s="12" t="s">
         <v>676</v>
       </c>
       <c r="B137" s="6" t="s">
         <v>677</v>
       </c>
-    </row>
-    <row r="138" spans="1:2">
+      <c r="C137" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>MRT 毛里塔尼亚</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3">
       <c r="A138" s="12" t="s">
         <v>678</v>
       </c>
       <c r="B138" s="6" t="s">
         <v>679</v>
       </c>
-    </row>
-    <row r="139" spans="1:2">
+      <c r="C138" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>MUS 毛里求斯</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3">
       <c r="A139" s="12" t="s">
         <v>680</v>
       </c>
       <c r="B139" s="6" t="s">
         <v>681</v>
       </c>
-    </row>
-    <row r="140" spans="1:2">
+      <c r="C139" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>MYT 马约特</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3">
       <c r="A140" s="12" t="s">
         <v>682</v>
       </c>
       <c r="B140" s="6" t="s">
         <v>683</v>
       </c>
-    </row>
-    <row r="141" spans="1:2">
+      <c r="C140" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>MEX 墨西哥</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3">
       <c r="A141" s="12" t="s">
         <v>684</v>
       </c>
       <c r="B141" s="6" t="s">
         <v>685</v>
       </c>
-    </row>
-    <row r="142" spans="1:2">
+      <c r="C141" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>FSM 密克罗尼西亚联邦</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3">
       <c r="A142" s="12" t="s">
         <v>686</v>
       </c>
       <c r="B142" s="6" t="s">
         <v>687</v>
       </c>
-    </row>
-    <row r="143" spans="1:2">
+      <c r="C142" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>MDA 摩尔多瓦</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3">
       <c r="A143" s="12" t="s">
         <v>688</v>
       </c>
       <c r="B143" s="6" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="144" spans="1:2">
+      <c r="C143" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>MCO 摩纳哥</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3">
       <c r="A144" s="12" t="s">
         <v>690</v>
       </c>
       <c r="B144" s="6" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="145" spans="1:2">
+      <c r="C144" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>MNG 蒙古</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3">
       <c r="A145" s="12" t="s">
         <v>692</v>
       </c>
       <c r="B145" s="6" t="s">
         <v>693</v>
       </c>
-    </row>
-    <row r="146" spans="1:2">
+      <c r="C145" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>MSR 蒙特塞拉特</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3">
       <c r="A146" s="12" t="s">
         <v>694</v>
       </c>
       <c r="B146" s="6" t="s">
         <v>695</v>
       </c>
-    </row>
-    <row r="147" spans="1:2">
+      <c r="C146" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>MAR 摩洛哥</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3">
       <c r="A147" s="12" t="s">
         <v>696</v>
       </c>
       <c r="B147" s="6" t="s">
         <v>697</v>
       </c>
-    </row>
-    <row r="148" spans="1:2">
+      <c r="C147" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>MOZ 莫桑比克</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3">
       <c r="A148" s="12" t="s">
         <v>698</v>
       </c>
       <c r="B148" s="6" t="s">
         <v>699</v>
       </c>
-    </row>
-    <row r="149" spans="1:2">
+      <c r="C148" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>MMR 缅甸</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3">
       <c r="A149" s="12" t="s">
         <v>700</v>
       </c>
       <c r="B149" s="6" t="s">
         <v>701</v>
       </c>
-    </row>
-    <row r="150" spans="1:2">
+      <c r="C149" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>NAM 纳米比亚</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3">
       <c r="A150" s="12" t="s">
         <v>702</v>
       </c>
       <c r="B150" s="6" t="s">
         <v>703</v>
       </c>
-    </row>
-    <row r="151" spans="1:2">
+      <c r="C150" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>NRU 瑙鲁</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3">
       <c r="A151" s="12" t="s">
         <v>704</v>
       </c>
       <c r="B151" s="6" t="s">
         <v>705</v>
       </c>
-    </row>
-    <row r="152" spans="1:2">
+      <c r="C151" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>NPL 尼泊尔</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3">
       <c r="A152" s="12" t="s">
         <v>706</v>
       </c>
       <c r="B152" s="6" t="s">
         <v>707</v>
       </c>
-    </row>
-    <row r="153" spans="1:2">
+      <c r="C152" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>NLD 荷兰</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3">
       <c r="A153" s="12" t="s">
         <v>708</v>
       </c>
       <c r="B153" s="6" t="s">
         <v>709</v>
       </c>
-    </row>
-    <row r="154" spans="1:2">
+      <c r="C153" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>ANT 荷属安的列斯</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3">
       <c r="A154" s="12" t="s">
         <v>710</v>
       </c>
       <c r="B154" s="6" t="s">
         <v>711</v>
       </c>
-    </row>
-    <row r="155" spans="1:2">
+      <c r="C154" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>NCL 新喀里多尼亚</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3">
       <c r="A155" s="12" t="s">
         <v>712</v>
       </c>
       <c r="B155" s="6" t="s">
         <v>713</v>
       </c>
-    </row>
-    <row r="156" spans="1:2">
+      <c r="C155" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>NZL 新西兰</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3">
       <c r="A156" s="12" t="s">
         <v>714</v>
       </c>
       <c r="B156" s="6" t="s">
         <v>715</v>
       </c>
-    </row>
-    <row r="157" spans="1:2">
+      <c r="C156" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>NIC 尼加拉瓜</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3">
       <c r="A157" s="12" t="s">
         <v>716</v>
       </c>
       <c r="B157" s="6" t="s">
         <v>717</v>
       </c>
-    </row>
-    <row r="158" spans="1:2">
+      <c r="C157" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>NER 尼日尔</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3">
       <c r="A158" s="12" t="s">
         <v>718</v>
       </c>
       <c r="B158" s="6" t="s">
         <v>719</v>
       </c>
-    </row>
-    <row r="159" spans="1:2">
+      <c r="C158" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>NGA 尼日利亚</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3">
       <c r="A159" s="12" t="s">
         <v>720</v>
       </c>
       <c r="B159" s="6" t="s">
         <v>721</v>
       </c>
-    </row>
-    <row r="160" spans="1:2">
+      <c r="C159" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>NIU 纽埃</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3">
       <c r="A160" s="12" t="s">
         <v>722</v>
       </c>
       <c r="B160" s="6" t="s">
         <v>723</v>
       </c>
-    </row>
-    <row r="161" spans="1:2">
+      <c r="C160" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>NFK 诺福克岛</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3">
       <c r="A161" s="12" t="s">
         <v>724</v>
       </c>
       <c r="B161" s="6" t="s">
         <v>725</v>
       </c>
-    </row>
-    <row r="162" spans="1:2">
+      <c r="C161" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>MNP 北马里亚纳</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3">
       <c r="A162" s="12" t="s">
         <v>726</v>
       </c>
       <c r="B162" s="6" t="s">
         <v>727</v>
       </c>
-    </row>
-    <row r="163" spans="1:2">
+      <c r="C162" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>NOR 挪威</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3">
       <c r="A163" s="12" t="s">
         <v>728</v>
       </c>
       <c r="B163" s="6" t="s">
         <v>729</v>
       </c>
-    </row>
-    <row r="164" spans="1:2">
+      <c r="C163" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>OMN 阿曼</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3">
       <c r="A164" s="12" t="s">
         <v>730</v>
       </c>
       <c r="B164" s="6" t="s">
         <v>731</v>
       </c>
-    </row>
-    <row r="165" spans="1:2">
+      <c r="C164" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>PAK 巴基斯坦</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3">
       <c r="A165" s="12" t="s">
         <v>732</v>
       </c>
       <c r="B165" s="6" t="s">
         <v>733</v>
       </c>
-    </row>
-    <row r="166" spans="1:2">
+      <c r="C165" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>PLW 帕劳</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3">
       <c r="A166" s="12" t="s">
         <v>734</v>
       </c>
       <c r="B166" s="6" t="s">
         <v>735</v>
       </c>
-    </row>
-    <row r="167" spans="1:2">
+      <c r="C166" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>PST 巴勒斯坦</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3">
       <c r="A167" s="12" t="s">
         <v>736</v>
       </c>
       <c r="B167" s="6" t="s">
         <v>737</v>
       </c>
-    </row>
-    <row r="168" spans="1:2">
+      <c r="C167" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>PAN 巴拿马</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3">
       <c r="A168" s="12" t="s">
         <v>738</v>
       </c>
       <c r="B168" s="6" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="169" spans="1:2">
+      <c r="C168" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>PNG 巴布亚新几内亚</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3">
       <c r="A169" s="12" t="s">
         <v>740</v>
       </c>
       <c r="B169" s="6" t="s">
         <v>741</v>
       </c>
-    </row>
-    <row r="170" spans="1:2">
+      <c r="C169" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>PRY 巴拉圭</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3">
       <c r="A170" s="12" t="s">
         <v>742</v>
       </c>
       <c r="B170" s="6" t="s">
         <v>743</v>
       </c>
-    </row>
-    <row r="171" spans="1:2">
+      <c r="C170" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>PER 秘鲁</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3">
       <c r="A171" s="12" t="s">
         <v>744</v>
       </c>
       <c r="B171" s="6" t="s">
         <v>745</v>
       </c>
-    </row>
-    <row r="172" spans="1:2">
+      <c r="C171" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>PHL 菲律宾</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3">
       <c r="A172" s="12" t="s">
         <v>746</v>
       </c>
       <c r="B172" s="6" t="s">
         <v>747</v>
       </c>
-    </row>
-    <row r="173" spans="1:2">
+      <c r="C172" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>PCN 皮特凯恩群岛</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3">
       <c r="A173" s="12" t="s">
         <v>748</v>
       </c>
       <c r="B173" s="6" t="s">
         <v>749</v>
       </c>
-    </row>
-    <row r="174" spans="1:2">
+      <c r="C173" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>POL 波兰</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3">
       <c r="A174" s="12" t="s">
         <v>750</v>
       </c>
       <c r="B174" s="6" t="s">
         <v>751</v>
       </c>
-    </row>
-    <row r="175" spans="1:2">
+      <c r="C174" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>PRT 葡萄牙</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3">
       <c r="A175" s="12" t="s">
         <v>752</v>
       </c>
       <c r="B175" s="6" t="s">
         <v>753</v>
       </c>
-    </row>
-    <row r="176" spans="1:2">
+      <c r="C175" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>PRI 波多黎各</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3">
       <c r="A176" s="12" t="s">
         <v>754</v>
       </c>
       <c r="B176" s="6" t="s">
         <v>755</v>
       </c>
-    </row>
-    <row r="177" spans="1:2">
+      <c r="C176" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>QAT 卡塔尔</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3">
       <c r="A177" s="12" t="s">
         <v>756</v>
       </c>
       <c r="B177" s="6" t="s">
         <v>757</v>
       </c>
-    </row>
-    <row r="178" spans="1:2">
+      <c r="C177" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>REU 留尼汪</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3">
       <c r="A178" s="12" t="s">
         <v>758</v>
       </c>
       <c r="B178" s="6" t="s">
         <v>759</v>
       </c>
-    </row>
-    <row r="179" spans="1:2">
+      <c r="C178" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>ROM 罗马尼亚</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3">
       <c r="A179" s="12" t="s">
         <v>760</v>
       </c>
       <c r="B179" s="6" t="s">
         <v>761</v>
       </c>
-    </row>
-    <row r="180" spans="1:2">
+      <c r="C179" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>RUS 俄罗斯联邦</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3">
       <c r="A180" s="12" t="s">
         <v>762</v>
       </c>
       <c r="B180" s="6" t="s">
         <v>763</v>
       </c>
-    </row>
-    <row r="181" spans="1:2">
+      <c r="C180" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>RWA 卢旺达</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3">
       <c r="A181" s="12" t="s">
         <v>764</v>
       </c>
       <c r="B181" s="6" t="s">
         <v>765</v>
       </c>
-    </row>
-    <row r="182" spans="1:2">
+      <c r="C181" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>SHN 圣赫勒拿</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3">
       <c r="A182" s="12" t="s">
         <v>766</v>
       </c>
       <c r="B182" s="6" t="s">
         <v>767</v>
       </c>
-    </row>
-    <row r="183" spans="1:2">
+      <c r="C182" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>KNA 圣基茨和尼维斯</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3">
       <c r="A183" s="12" t="s">
         <v>768</v>
       </c>
       <c r="B183" s="6" t="s">
         <v>769</v>
       </c>
-    </row>
-    <row r="184" spans="1:2">
+      <c r="C183" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>LCA 圣卢西亚</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3">
       <c r="A184" s="12" t="s">
         <v>770</v>
       </c>
       <c r="B184" s="6" t="s">
         <v>771</v>
       </c>
-    </row>
-    <row r="185" spans="1:2">
+      <c r="C184" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>SPM 圣皮埃尔和密克隆</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3">
       <c r="A185" s="12" t="s">
         <v>772</v>
       </c>
       <c r="B185" s="6" t="s">
         <v>773</v>
       </c>
-    </row>
-    <row r="186" spans="1:2">
+      <c r="C185" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>VCT 圣文森特和格林纳丁斯</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3">
       <c r="A186" s="12" t="s">
         <v>774</v>
       </c>
       <c r="B186" s="6" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="187" spans="1:2">
+      <c r="C186" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>WSM 萨摩亚</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3">
       <c r="A187" s="12" t="s">
         <v>776</v>
       </c>
       <c r="B187" s="6" t="s">
         <v>777</v>
       </c>
-    </row>
-    <row r="188" spans="1:2">
+      <c r="C187" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>SMR 圣马力诺</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3">
       <c r="A188" s="12" t="s">
         <v>778</v>
       </c>
       <c r="B188" s="6" t="s">
         <v>779</v>
       </c>
-    </row>
-    <row r="189" spans="1:2">
+      <c r="C188" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>STP 圣多美和普林西比</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3">
       <c r="A189" s="12" t="s">
         <v>780</v>
       </c>
       <c r="B189" s="6" t="s">
         <v>781</v>
       </c>
-    </row>
-    <row r="190" spans="1:2">
+      <c r="C189" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>SAU 沙特阿拉伯</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3">
       <c r="A190" s="12" t="s">
         <v>782</v>
       </c>
       <c r="B190" s="6" t="s">
         <v>783</v>
       </c>
-    </row>
-    <row r="191" spans="1:2">
+      <c r="C190" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>SEN 塞内加尔</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3">
       <c r="A191" s="12" t="s">
         <v>784</v>
       </c>
       <c r="B191" s="6" t="s">
         <v>785</v>
       </c>
-    </row>
-    <row r="192" spans="1:2">
+      <c r="C191" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>SYC 塞舌尔</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3">
       <c r="A192" s="12" t="s">
         <v>786</v>
       </c>
       <c r="B192" s="6" t="s">
         <v>787</v>
       </c>
-    </row>
-    <row r="193" spans="1:2">
+      <c r="C192" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>SLE 塞拉利昂</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3">
       <c r="A193" s="12" t="s">
         <v>788</v>
       </c>
       <c r="B193" s="6" t="s">
         <v>789</v>
       </c>
-    </row>
-    <row r="194" spans="1:2">
+      <c r="C193" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>SGP 新加坡</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3">
       <c r="A194" s="12" t="s">
         <v>790</v>
       </c>
       <c r="B194" s="6" t="s">
         <v>791</v>
       </c>
-    </row>
-    <row r="195" spans="1:2">
+      <c r="C194" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>SVK 斯洛伐克</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3">
       <c r="A195" s="12" t="s">
         <v>792</v>
       </c>
       <c r="B195" s="6" t="s">
         <v>793</v>
       </c>
-    </row>
-    <row r="196" spans="1:2">
+      <c r="C195" s="9" t="str">
+        <f t="shared" ref="C195:C240" si="3" xml:space="preserve"> A195 &amp; " " &amp; B195</f>
+        <v>SVN 斯洛文尼亚</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3">
       <c r="A196" s="12" t="s">
         <v>794</v>
       </c>
       <c r="B196" s="6" t="s">
         <v>795</v>
       </c>
-    </row>
-    <row r="197" spans="1:2">
+      <c r="C196" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>SLB 所罗门群岛</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3">
       <c r="A197" s="12" t="s">
         <v>796</v>
       </c>
       <c r="B197" s="6" t="s">
         <v>797</v>
       </c>
-    </row>
-    <row r="198" spans="1:2">
+      <c r="C197" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>SOM 索马里</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3">
       <c r="A198" s="12" t="s">
         <v>798</v>
       </c>
       <c r="B198" s="6" t="s">
         <v>799</v>
       </c>
-    </row>
-    <row r="199" spans="1:2">
+      <c r="C198" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>ZAF 南非</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3">
       <c r="A199" s="12" t="s">
         <v>800</v>
       </c>
       <c r="B199" s="6" t="s">
         <v>801</v>
       </c>
-    </row>
-    <row r="200" spans="1:2">
+      <c r="C199" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>SGS 南乔治亚岛和南桑德韦奇岛</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3">
       <c r="A200" s="12" t="s">
         <v>802</v>
       </c>
       <c r="B200" s="6" t="s">
         <v>803</v>
       </c>
-    </row>
-    <row r="201" spans="1:2">
+      <c r="C200" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>ESP 西班牙</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3">
       <c r="A201" s="12" t="s">
         <v>804</v>
       </c>
       <c r="B201" s="6" t="s">
         <v>805</v>
       </c>
-    </row>
-    <row r="202" spans="1:2">
+      <c r="C201" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>LKA 斯里兰卡</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3">
       <c r="A202" s="12" t="s">
         <v>806</v>
       </c>
       <c r="B202" s="6" t="s">
         <v>807</v>
       </c>
-    </row>
-    <row r="203" spans="1:2">
+      <c r="C202" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>SDN 苏丹</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3">
       <c r="A203" s="12" t="s">
         <v>808</v>
       </c>
       <c r="B203" s="6" t="s">
         <v>809</v>
       </c>
-    </row>
-    <row r="204" spans="1:2">
+      <c r="C203" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>SUR 苏里南</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3">
       <c r="A204" s="12" t="s">
         <v>810</v>
       </c>
       <c r="B204" s="6" t="s">
         <v>811</v>
       </c>
-    </row>
-    <row r="205" spans="1:2">
+      <c r="C204" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>SJM 斯瓦尔巴群岛</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3">
       <c r="A205" s="12" t="s">
         <v>812</v>
       </c>
       <c r="B205" s="6" t="s">
         <v>813</v>
       </c>
-    </row>
-    <row r="206" spans="1:2">
+      <c r="C205" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>SWZ 斯威士兰</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3">
       <c r="A206" s="12" t="s">
         <v>814</v>
       </c>
       <c r="B206" s="6" t="s">
         <v>815</v>
       </c>
-    </row>
-    <row r="207" spans="1:2">
+      <c r="C206" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>SWE 瑞典</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3">
       <c r="A207" s="12" t="s">
         <v>816</v>
       </c>
       <c r="B207" s="6" t="s">
         <v>817</v>
       </c>
-    </row>
-    <row r="208" spans="1:2">
+      <c r="C207" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>CHE 瑞士</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3">
       <c r="A208" s="12" t="s">
         <v>818</v>
       </c>
       <c r="B208" s="6" t="s">
         <v>819</v>
       </c>
-    </row>
-    <row r="209" spans="1:2">
+      <c r="C208" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>SYR 叙利亚</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3">
       <c r="A209" s="12" t="s">
         <v>820</v>
       </c>
       <c r="B209" s="6" t="s">
         <v>821</v>
       </c>
-    </row>
-    <row r="210" spans="1:2">
+      <c r="C209" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>TJK 塔吉克斯坦</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3">
       <c r="A210" s="12" t="s">
         <v>822</v>
       </c>
       <c r="B210" s="6" t="s">
         <v>823</v>
       </c>
-    </row>
-    <row r="211" spans="1:2">
+      <c r="C210" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>TZA 坦桑尼亚</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3">
       <c r="A211" s="12" t="s">
         <v>824</v>
       </c>
       <c r="B211" s="6" t="s">
         <v>825</v>
       </c>
-    </row>
-    <row r="212" spans="1:2">
+      <c r="C211" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>THA 泰国</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3">
       <c r="A212" s="12" t="s">
         <v>826</v>
       </c>
       <c r="B212" s="6" t="s">
         <v>827</v>
       </c>
-    </row>
-    <row r="213" spans="1:2">
+      <c r="C212" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>TGO 多哥</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3">
       <c r="A213" s="12" t="s">
         <v>828</v>
       </c>
       <c r="B213" s="6" t="s">
         <v>829</v>
       </c>
-    </row>
-    <row r="214" spans="1:2">
+      <c r="C213" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>TKL 托克劳</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3">
       <c r="A214" s="12" t="s">
         <v>830</v>
       </c>
       <c r="B214" s="6" t="s">
         <v>831</v>
       </c>
-    </row>
-    <row r="215" spans="1:2">
+      <c r="C214" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>TON 汤加</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3">
       <c r="A215" s="12" t="s">
         <v>832</v>
       </c>
       <c r="B215" s="6" t="s">
         <v>833</v>
       </c>
-    </row>
-    <row r="216" spans="1:2">
+      <c r="C215" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>TTO 特立尼达和多巴哥</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3">
       <c r="A216" s="12" t="s">
         <v>834</v>
       </c>
       <c r="B216" s="6" t="s">
         <v>835</v>
       </c>
-    </row>
-    <row r="217" spans="1:2">
+      <c r="C216" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>TUN 突尼斯</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3">
       <c r="A217" s="12" t="s">
         <v>836</v>
       </c>
       <c r="B217" s="6" t="s">
         <v>837</v>
       </c>
-    </row>
-    <row r="218" spans="1:2">
+      <c r="C217" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>TUR 土耳其</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3">
       <c r="A218" s="12" t="s">
         <v>838</v>
       </c>
       <c r="B218" s="6" t="s">
         <v>839</v>
       </c>
-    </row>
-    <row r="219" spans="1:2">
+      <c r="C218" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>TKM 土库曼斯坦</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3">
       <c r="A219" s="12" t="s">
         <v>840</v>
       </c>
       <c r="B219" s="6" t="s">
         <v>841</v>
       </c>
-    </row>
-    <row r="220" spans="1:2">
+      <c r="C219" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>TCA 特克斯科斯群岛</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3">
       <c r="A220" s="12" t="s">
         <v>842</v>
       </c>
       <c r="B220" s="6" t="s">
         <v>843</v>
       </c>
-    </row>
-    <row r="221" spans="1:2">
+      <c r="C220" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>TUV 图瓦卢</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3">
       <c r="A221" s="12" t="s">
         <v>844</v>
       </c>
       <c r="B221" s="6" t="s">
         <v>845</v>
       </c>
-    </row>
-    <row r="222" spans="1:2">
+      <c r="C221" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>UGA 乌干达</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3">
       <c r="A222" s="12" t="s">
         <v>846</v>
       </c>
       <c r="B222" s="6" t="s">
         <v>847</v>
       </c>
-    </row>
-    <row r="223" spans="1:2">
+      <c r="C222" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>UKR 乌克兰</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3">
       <c r="A223" s="12" t="s">
         <v>848</v>
       </c>
       <c r="B223" s="6" t="s">
         <v>849</v>
       </c>
-    </row>
-    <row r="224" spans="1:2">
+      <c r="C223" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>ARE 阿联酋</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3">
       <c r="A224" s="12" t="s">
         <v>850</v>
       </c>
       <c r="B224" s="6" t="s">
         <v>851</v>
       </c>
-    </row>
-    <row r="225" spans="1:2">
+      <c r="C224" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>GBR 英国</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3">
       <c r="A225" s="12" t="s">
         <v>852</v>
       </c>
       <c r="B225" s="6" t="s">
         <v>853</v>
       </c>
-    </row>
-    <row r="226" spans="1:2">
+      <c r="C225" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>USA 美国</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3">
       <c r="A226" s="12" t="s">
         <v>854</v>
       </c>
       <c r="B226" s="6" t="s">
         <v>855</v>
       </c>
-    </row>
-    <row r="227" spans="1:2">
+      <c r="C226" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>UMI 美国本土外小岛屿</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3">
       <c r="A227" s="12" t="s">
         <v>856</v>
       </c>
       <c r="B227" s="6" t="s">
         <v>857</v>
       </c>
-    </row>
-    <row r="228" spans="1:2">
+      <c r="C227" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>URY 乌拉圭</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3">
       <c r="A228" s="12" t="s">
         <v>858</v>
       </c>
       <c r="B228" s="6" t="s">
         <v>859</v>
       </c>
-    </row>
-    <row r="229" spans="1:2">
+      <c r="C228" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>UZB 乌兹别克斯坦</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3">
       <c r="A229" s="12" t="s">
         <v>860</v>
       </c>
       <c r="B229" s="6" t="s">
         <v>861</v>
       </c>
-    </row>
-    <row r="230" spans="1:2">
+      <c r="C229" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>VUT 瓦努阿图</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3">
       <c r="A230" s="12" t="s">
         <v>862</v>
       </c>
       <c r="B230" s="6" t="s">
         <v>863</v>
       </c>
-    </row>
-    <row r="231" spans="1:2">
+      <c r="C230" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>VAT 梵蒂冈</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3">
       <c r="A231" s="12" t="s">
         <v>864</v>
       </c>
       <c r="B231" s="6" t="s">
         <v>865</v>
       </c>
-    </row>
-    <row r="232" spans="1:2">
+      <c r="C231" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>VEN 委内瑞拉</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3">
       <c r="A232" s="12" t="s">
         <v>866</v>
       </c>
       <c r="B232" s="6" t="s">
         <v>867</v>
       </c>
-    </row>
-    <row r="233" spans="1:2">
+      <c r="C232" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>VNM 越南</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3">
       <c r="A233" s="12" t="s">
         <v>868</v>
       </c>
       <c r="B233" s="6" t="s">
         <v>869</v>
       </c>
-    </row>
-    <row r="234" spans="1:2">
+      <c r="C233" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>VGB 英属维尔京群岛</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3">
       <c r="A234" s="12" t="s">
         <v>870</v>
       </c>
       <c r="B234" s="6" t="s">
         <v>871</v>
       </c>
-    </row>
-    <row r="235" spans="1:2">
+      <c r="C234" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>VIR 美属维尔京群岛</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3">
       <c r="A235" s="12" t="s">
         <v>872</v>
       </c>
       <c r="B235" s="6" t="s">
         <v>873</v>
       </c>
-    </row>
-    <row r="236" spans="1:2">
+      <c r="C235" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>WLF 瓦利斯和富图纳</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3">
       <c r="A236" s="12" t="s">
         <v>874</v>
       </c>
       <c r="B236" s="6" t="s">
         <v>875</v>
       </c>
-    </row>
-    <row r="237" spans="1:2">
+      <c r="C236" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>ESH 西撒哈拉</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3">
       <c r="A237" s="12" t="s">
         <v>876</v>
       </c>
       <c r="B237" s="6" t="s">
         <v>877</v>
       </c>
-    </row>
-    <row r="238" spans="1:2">
+      <c r="C237" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>YEM 也门</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3">
       <c r="A238" s="12" t="s">
         <v>878</v>
       </c>
       <c r="B238" s="6" t="s">
         <v>879</v>
       </c>
-    </row>
-    <row r="239" spans="1:2">
+      <c r="C238" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>YUG 南斯拉夫</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3">
       <c r="A239" s="12" t="s">
         <v>880</v>
       </c>
       <c r="B239" s="6" t="s">
         <v>881</v>
       </c>
-    </row>
-    <row r="240" spans="1:2">
+      <c r="C239" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>ZMB 赞比亚</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3">
       <c r="A240" s="14" t="s">
         <v>882</v>
       </c>
       <c r="B240" s="8" t="s">
         <v>883</v>
       </c>
+      <c r="C240" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>ZWE 津巴布韦</v>
+      </c>
     </row>
   </sheetData>
-  <sheetProtection sheet="1" objects="1"/>
   <mergeCells count="1">
     <mergeCell ref="A1:B1"/>
   </mergeCells>
@@ -12671,1442 +13631,2155 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B179"/>
+  <dimension ref="A1:C179"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="18" style="1" customWidth="1"/>
     <col min="2" max="2" width="35.5" style="2" customWidth="1"/>
-    <col min="3" max="16384" width="9" style="2"/>
+    <col min="3" max="3" width="37.125" style="2" customWidth="1"/>
+    <col min="4" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="22.5" customHeight="1">
-      <c r="A1" s="116" t="s">
+    <row r="1" spans="1:3" ht="22.5" customHeight="1">
+      <c r="A1" s="126" t="s">
         <v>884</v>
       </c>
-      <c r="B1" s="116"/>
-    </row>
-    <row r="2" spans="1:2">
+      <c r="B1" s="126"/>
+    </row>
+    <row r="2" spans="1:3">
       <c r="A2" s="3" t="s">
         <v>885</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>886</v>
       </c>
-    </row>
-    <row r="3" spans="1:2">
+      <c r="C2" s="2" t="str">
+        <f xml:space="preserve"> A2 &amp; " " &amp; B2</f>
+        <v>CNY 人民币</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3" s="5" t="s">
         <v>887</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>888</v>
       </c>
-    </row>
-    <row r="4" spans="1:2">
+      <c r="C3" s="2" t="str">
+        <f xml:space="preserve"> A3 &amp; " " &amp; B3</f>
+        <v>HKD 港元</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4" s="5" t="s">
         <v>889</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>890</v>
       </c>
-    </row>
-    <row r="5" spans="1:2">
+      <c r="C4" s="2" t="str">
+        <f xml:space="preserve"> A4 &amp; " " &amp; B4</f>
+        <v>USD 美元</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
       <c r="A5" s="5" t="s">
         <v>891</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>892</v>
       </c>
-    </row>
-    <row r="6" spans="1:2">
+      <c r="C5" s="2" t="str">
+        <f xml:space="preserve"> A5 &amp; " " &amp; B5</f>
+        <v>EUR 欧元</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
       <c r="A6" s="5" t="s">
         <v>893</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>894</v>
       </c>
-    </row>
-    <row r="7" spans="1:2">
+      <c r="C6" s="2" t="str">
+        <f xml:space="preserve"> A6 &amp; " " &amp; B6</f>
+        <v>JPY 日元</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
       <c r="A7" s="5" t="s">
         <v>895</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>896</v>
       </c>
-    </row>
-    <row r="8" spans="1:2">
+      <c r="C7" s="2" t="str">
+        <f xml:space="preserve"> A7 &amp; " " &amp; B7</f>
+        <v>MOP 澳门元</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
       <c r="A8" s="5" t="s">
         <v>897</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>898</v>
       </c>
-    </row>
-    <row r="9" spans="1:2">
+      <c r="C8" s="2" t="str">
+        <f xml:space="preserve"> A8 &amp; " " &amp; B8</f>
+        <v>CHF 瑞士法郎</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
       <c r="A9" s="5" t="s">
         <v>899</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>900</v>
       </c>
-    </row>
-    <row r="10" spans="1:2">
+      <c r="C9" s="2" t="str">
+        <f xml:space="preserve"> A9 &amp; " " &amp; B9</f>
+        <v>GBP 英镑</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
       <c r="A10" s="5" t="s">
         <v>901</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>902</v>
       </c>
-    </row>
-    <row r="11" spans="1:2">
+      <c r="C10" s="2" t="str">
+        <f xml:space="preserve"> A10 &amp; " " &amp; B10</f>
+        <v>RUB 俄罗斯卢布</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
       <c r="A11" s="5" t="s">
         <v>903</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>904</v>
       </c>
-    </row>
-    <row r="12" spans="1:2">
+      <c r="C11" s="2" t="str">
+        <f xml:space="preserve"> A11 &amp; " " &amp; B11</f>
+        <v>CAD 加拿大元</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
       <c r="A12" s="5" t="s">
         <v>905</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>906</v>
       </c>
-    </row>
-    <row r="13" spans="1:2">
+      <c r="C12" s="2" t="str">
+        <f xml:space="preserve"> A12 &amp; " " &amp; B12</f>
+        <v>DKK 丹麦克朗</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
       <c r="A13" s="5" t="s">
         <v>907</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>908</v>
       </c>
-    </row>
-    <row r="14" spans="1:2">
+      <c r="C13" s="2" t="str">
+        <f xml:space="preserve"> A13 &amp; " " &amp; B13</f>
+        <v>AUD 澳大利亚元</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
       <c r="A14" s="5" t="s">
         <v>909</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>910</v>
       </c>
-    </row>
-    <row r="15" spans="1:2">
+      <c r="C14" s="2" t="str">
+        <f xml:space="preserve"> A14 &amp; " " &amp; B14</f>
+        <v>SEK 瑞典克朗</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
       <c r="A15" s="5" t="s">
         <v>911</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>912</v>
       </c>
-    </row>
-    <row r="16" spans="1:2">
+      <c r="C15" s="2" t="str">
+        <f xml:space="preserve"> A15 &amp; " " &amp; B15</f>
+        <v>SGD 新加坡元</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
       <c r="A16" s="5" t="s">
         <v>913</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>914</v>
       </c>
-    </row>
-    <row r="17" spans="1:2">
+      <c r="C16" s="2" t="str">
+        <f xml:space="preserve"> A16 &amp; " " &amp; B16</f>
+        <v>TWD 新台币</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
       <c r="A17" s="5" t="s">
         <v>915</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>916</v>
       </c>
-    </row>
-    <row r="18" spans="1:2">
+      <c r="C17" s="2" t="str">
+        <f xml:space="preserve"> A17 &amp; " " &amp; B17</f>
+        <v>AED 阿拉伯联合酋长国迪尔汗</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
       <c r="A18" s="5" t="s">
         <v>917</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>918</v>
       </c>
-    </row>
-    <row r="19" spans="1:2">
+      <c r="C18" s="2" t="str">
+        <f xml:space="preserve"> A18 &amp; " " &amp; B18</f>
+        <v>AFN 阿富汗阿富汗尼</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
       <c r="A19" s="5" t="s">
         <v>919</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>920</v>
       </c>
-    </row>
-    <row r="20" spans="1:2">
+      <c r="C19" s="2" t="str">
+        <f xml:space="preserve"> A19 &amp; " " &amp; B19</f>
+        <v>ALL 阿尔巴尼亚列克</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
       <c r="A20" s="5" t="s">
         <v>921</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>922</v>
       </c>
-    </row>
-    <row r="21" spans="1:2">
+      <c r="C20" s="2" t="str">
+        <f xml:space="preserve"> A20 &amp; " " &amp; B20</f>
+        <v>AMD 亚美尼亚德拉姆</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
       <c r="A21" s="5" t="s">
         <v>923</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>924</v>
       </c>
-    </row>
-    <row r="22" spans="1:2">
+      <c r="C21" s="2" t="str">
+        <f xml:space="preserve"> A21 &amp; " " &amp; B21</f>
+        <v>ANG 荷属安的列斯盾</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
       <c r="A22" s="5" t="s">
         <v>925</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>926</v>
       </c>
-    </row>
-    <row r="23" spans="1:2">
+      <c r="C22" s="2" t="str">
+        <f xml:space="preserve"> A22 &amp; " " &amp; B22</f>
+        <v>AOA 安哥拉宽扎</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
       <c r="A23" s="5" t="s">
         <v>927</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>928</v>
       </c>
-    </row>
-    <row r="24" spans="1:2">
+      <c r="C23" s="2" t="str">
+        <f xml:space="preserve"> A23 &amp; " " &amp; B23</f>
+        <v>ARS 阿根廷比索</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
       <c r="A24" s="5" t="s">
         <v>929</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>930</v>
       </c>
-    </row>
-    <row r="25" spans="1:2">
+      <c r="C24" s="2" t="str">
+        <f xml:space="preserve"> A24 &amp; " " &amp; B24</f>
+        <v>AWG 阿鲁巴弗罗林</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
       <c r="A25" s="5" t="s">
         <v>931</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>932</v>
       </c>
-    </row>
-    <row r="26" spans="1:2">
+      <c r="C25" s="2" t="str">
+        <f xml:space="preserve"> A25 &amp; " " &amp; B25</f>
+        <v>AZN 阿塞拜疆马纳特</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
       <c r="A26" s="5" t="s">
         <v>933</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>934</v>
       </c>
-    </row>
-    <row r="27" spans="1:2">
+      <c r="C26" s="2" t="str">
+        <f xml:space="preserve"> A26 &amp; " " &amp; B26</f>
+        <v>BAM 波斯尼亚和黑塞哥维那可兑换马克</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
       <c r="A27" s="5" t="s">
         <v>935</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>936</v>
       </c>
-    </row>
-    <row r="28" spans="1:2">
+      <c r="C27" s="2" t="str">
+        <f xml:space="preserve"> A27 &amp; " " &amp; B27</f>
+        <v>BBD 巴巴多斯元</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
       <c r="A28" s="5" t="s">
         <v>937</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>938</v>
       </c>
-    </row>
-    <row r="29" spans="1:2">
+      <c r="C28" s="2" t="str">
+        <f xml:space="preserve"> A28 &amp; " " &amp; B28</f>
+        <v>BDT 孟加拉塔卡</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
       <c r="A29" s="5" t="s">
         <v>939</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>940</v>
       </c>
-    </row>
-    <row r="30" spans="1:2">
+      <c r="C29" s="2" t="str">
+        <f xml:space="preserve"> A29 &amp; " " &amp; B29</f>
+        <v>BGN 保加利亚列弗</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
       <c r="A30" s="5" t="s">
         <v>941</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>942</v>
       </c>
-    </row>
-    <row r="31" spans="1:2">
+      <c r="C30" s="2" t="str">
+        <f xml:space="preserve"> A30 &amp; " " &amp; B30</f>
+        <v>BHD 巴林第纳尔</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
       <c r="A31" s="5" t="s">
         <v>943</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>944</v>
       </c>
-    </row>
-    <row r="32" spans="1:2">
+      <c r="C31" s="2" t="str">
+        <f xml:space="preserve"> A31 &amp; " " &amp; B31</f>
+        <v>BIF 布隆迪法郎</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
       <c r="A32" s="5" t="s">
         <v>945</v>
       </c>
       <c r="B32" s="6" t="s">
         <v>946</v>
       </c>
-    </row>
-    <row r="33" spans="1:2">
+      <c r="C32" s="2" t="str">
+        <f xml:space="preserve"> A32 &amp; " " &amp; B32</f>
+        <v>BMD 百慕大元</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
       <c r="A33" s="5" t="s">
         <v>947</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>948</v>
       </c>
-    </row>
-    <row r="34" spans="1:2">
+      <c r="C33" s="2" t="str">
+        <f xml:space="preserve"> A33 &amp; " " &amp; B33</f>
+        <v>BND 文莱元</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
       <c r="A34" s="5" t="s">
         <v>949</v>
       </c>
       <c r="B34" s="6" t="s">
         <v>950</v>
       </c>
-    </row>
-    <row r="35" spans="1:2">
+      <c r="C34" s="2" t="str">
+        <f xml:space="preserve"> A34 &amp; " " &amp; B34</f>
+        <v>BOB 玻利维亚诺</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
       <c r="A35" s="5" t="s">
         <v>951</v>
       </c>
       <c r="B35" s="6" t="s">
         <v>952</v>
       </c>
-    </row>
-    <row r="36" spans="1:2">
+      <c r="C35" s="2" t="str">
+        <f xml:space="preserve"> A35 &amp; " " &amp; B35</f>
+        <v>BOV 玻利维亚Mvdol基金</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
       <c r="A36" s="5" t="s">
         <v>953</v>
       </c>
       <c r="B36" s="6" t="s">
         <v>954</v>
       </c>
-    </row>
-    <row r="37" spans="1:2">
+      <c r="C36" s="2" t="str">
+        <f xml:space="preserve"> A36 &amp; " " &amp; B36</f>
+        <v>BRL 巴西雷亚尔</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
       <c r="A37" s="5" t="s">
         <v>955</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>956</v>
       </c>
-    </row>
-    <row r="38" spans="1:2">
+      <c r="C37" s="2" t="str">
+        <f xml:space="preserve"> A37 &amp; " " &amp; B37</f>
+        <v>BSD 巴哈马元</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
       <c r="A38" s="5" t="s">
         <v>454</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>957</v>
       </c>
-    </row>
-    <row r="39" spans="1:2">
+      <c r="C38" s="2" t="str">
+        <f xml:space="preserve"> A38 &amp; " " &amp; B38</f>
+        <v>BTN 不丹努扎姆</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
       <c r="A39" s="5" t="s">
         <v>958</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>959</v>
       </c>
-    </row>
-    <row r="40" spans="1:2">
+      <c r="C39" s="2" t="str">
+        <f xml:space="preserve"> A39 &amp; " " &amp; B39</f>
+        <v>BWP 博茨瓦纳普拉</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
       <c r="A40" s="5" t="s">
         <v>960</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>961</v>
       </c>
-    </row>
-    <row r="41" spans="1:2">
+      <c r="C40" s="2" t="str">
+        <f xml:space="preserve"> A40 &amp; " " &amp; B40</f>
+        <v>BYR 白俄罗斯卢布</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
       <c r="A41" s="5" t="s">
         <v>962</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>963</v>
       </c>
-    </row>
-    <row r="42" spans="1:2">
+      <c r="C41" s="2" t="str">
+        <f xml:space="preserve"> A41 &amp; " " &amp; B41</f>
+        <v>BZD 伯利兹元</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
       <c r="A42" s="5" t="s">
         <v>964</v>
       </c>
       <c r="B42" s="6" t="s">
         <v>965</v>
       </c>
-    </row>
-    <row r="43" spans="1:2">
+      <c r="C42" s="2" t="str">
+        <f xml:space="preserve"> A42 &amp; " " &amp; B42</f>
+        <v>CDF 刚果民主共和国刚果法郎</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
       <c r="A43" s="5" t="s">
         <v>816</v>
       </c>
       <c r="B43" s="6" t="s">
         <v>966</v>
       </c>
-    </row>
-    <row r="44" spans="1:2">
+      <c r="C43" s="2" t="str">
+        <f xml:space="preserve"> A43 &amp; " " &amp; B43</f>
+        <v>CHE WIR欧元</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
       <c r="A44" s="5" t="s">
         <v>967</v>
       </c>
       <c r="B44" s="6" t="s">
         <v>968</v>
       </c>
-    </row>
-    <row r="45" spans="1:2">
+      <c r="C44" s="2" t="str">
+        <f xml:space="preserve"> A44 &amp; " " &amp; B44</f>
+        <v>CHW WIR法郎</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
       <c r="A45" s="5" t="s">
         <v>969</v>
       </c>
       <c r="B45" s="6" t="s">
         <v>970</v>
       </c>
-    </row>
-    <row r="46" spans="1:2">
+      <c r="C45" s="2" t="str">
+        <f xml:space="preserve"> A45 &amp; " " &amp; B45</f>
+        <v>CLF 智利UF基金</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
       <c r="A46" s="5" t="s">
         <v>971</v>
       </c>
       <c r="B46" s="6" t="s">
         <v>972</v>
       </c>
-    </row>
-    <row r="47" spans="1:2">
+      <c r="C46" s="2" t="str">
+        <f xml:space="preserve"> A46 &amp; " " &amp; B46</f>
+        <v>CLP 智利比索</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
       <c r="A47" s="5" t="s">
         <v>973</v>
       </c>
       <c r="B47" s="6" t="s">
         <v>974</v>
       </c>
-    </row>
-    <row r="48" spans="1:2">
+      <c r="C47" s="2" t="str">
+        <f xml:space="preserve"> A47 &amp; " " &amp; B47</f>
+        <v>COP 哥伦比亚比索</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
       <c r="A48" s="5" t="s">
         <v>975</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>976</v>
       </c>
-    </row>
-    <row r="49" spans="1:2">
+      <c r="C48" s="2" t="str">
+        <f xml:space="preserve"> A48 &amp; " " &amp; B48</f>
+        <v>COU 哥伦比亚UVR基金</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
       <c r="A49" s="5" t="s">
         <v>977</v>
       </c>
       <c r="B49" s="6" t="s">
         <v>978</v>
       </c>
-    </row>
-    <row r="50" spans="1:2">
+      <c r="C49" s="2" t="str">
+        <f xml:space="preserve"> A49 &amp; " " &amp; B49</f>
+        <v>CRC 哥斯达黎加科朗</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
       <c r="A50" s="5" t="s">
         <v>979</v>
       </c>
       <c r="B50" s="6" t="s">
         <v>980</v>
       </c>
-    </row>
-    <row r="51" spans="1:2">
+      <c r="C50" s="2" t="str">
+        <f xml:space="preserve"> A50 &amp; " " &amp; B50</f>
+        <v>CUC 古巴可兑换比索</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
       <c r="A51" s="5" t="s">
         <v>981</v>
       </c>
       <c r="B51" s="6" t="s">
         <v>982</v>
       </c>
-    </row>
-    <row r="52" spans="1:2">
+      <c r="C51" s="2" t="str">
+        <f xml:space="preserve"> A51 &amp; " " &amp; B51</f>
+        <v>CUP 古巴比索</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
       <c r="A52" s="5" t="s">
         <v>983</v>
       </c>
       <c r="B52" s="6" t="s">
         <v>984</v>
       </c>
-    </row>
-    <row r="53" spans="1:2">
+      <c r="C52" s="2" t="str">
+        <f xml:space="preserve"> A52 &amp; " " &amp; B52</f>
+        <v>CVE 佛得角埃斯库多</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
       <c r="A53" s="5" t="s">
         <v>985</v>
       </c>
       <c r="B53" s="6" t="s">
         <v>986</v>
       </c>
-    </row>
-    <row r="54" spans="1:2">
+      <c r="C53" s="2" t="str">
+        <f xml:space="preserve"> A53 &amp; " " &amp; B53</f>
+        <v>CZK 捷克克朗</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
       <c r="A54" s="5" t="s">
         <v>987</v>
       </c>
       <c r="B54" s="6" t="s">
         <v>988</v>
       </c>
-    </row>
-    <row r="55" spans="1:2">
+      <c r="C54" s="2" t="str">
+        <f xml:space="preserve"> A54 &amp; " " &amp; B54</f>
+        <v>DJF 吉布提法郎</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
       <c r="A55" s="5" t="s">
         <v>989</v>
       </c>
       <c r="B55" s="6" t="s">
         <v>990</v>
       </c>
-    </row>
-    <row r="56" spans="1:2">
+      <c r="C55" s="2" t="str">
+        <f xml:space="preserve"> A55 &amp; " " &amp; B55</f>
+        <v>DOP 多米尼加比索</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
       <c r="A56" s="5" t="s">
         <v>991</v>
       </c>
       <c r="B56" s="6" t="s">
         <v>992</v>
       </c>
-    </row>
-    <row r="57" spans="1:2">
+      <c r="C56" s="2" t="str">
+        <f xml:space="preserve"> A56 &amp; " " &amp; B56</f>
+        <v>DZD 阿尔及利亚第纳尔</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
       <c r="A57" s="5" t="s">
         <v>993</v>
       </c>
       <c r="B57" s="6" t="s">
         <v>994</v>
       </c>
-    </row>
-    <row r="58" spans="1:2">
+      <c r="C57" s="2" t="str">
+        <f xml:space="preserve"> A57 &amp; " " &amp; B57</f>
+        <v>EGP 埃及镑</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3">
       <c r="A58" s="5" t="s">
         <v>995</v>
       </c>
       <c r="B58" s="6" t="s">
         <v>996</v>
       </c>
-    </row>
-    <row r="59" spans="1:2">
+      <c r="C58" s="2" t="str">
+        <f xml:space="preserve"> A58 &amp; " " &amp; B58</f>
+        <v>ERN 厄立特里亚纳克法</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
       <c r="A59" s="5" t="s">
         <v>997</v>
       </c>
       <c r="B59" s="6" t="s">
         <v>998</v>
       </c>
-    </row>
-    <row r="60" spans="1:2">
+      <c r="C59" s="2" t="str">
+        <f xml:space="preserve"> A59 &amp; " " &amp; B59</f>
+        <v>ETB 埃塞俄比亚比尔</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3">
       <c r="A60" s="5" t="s">
         <v>999</v>
       </c>
       <c r="B60" s="6" t="s">
         <v>1000</v>
       </c>
-    </row>
-    <row r="61" spans="1:2">
+      <c r="C60" s="2" t="str">
+        <f xml:space="preserve"> A60 &amp; " " &amp; B60</f>
+        <v>FJD 斐济元</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3">
       <c r="A61" s="5" t="s">
         <v>1001</v>
       </c>
       <c r="B61" s="6" t="s">
         <v>1002</v>
       </c>
-    </row>
-    <row r="62" spans="1:2">
+      <c r="C61" s="2" t="str">
+        <f xml:space="preserve"> A61 &amp; " " &amp; B61</f>
+        <v>FKP 福克兰镑</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3">
       <c r="A62" s="5" t="s">
         <v>1003</v>
       </c>
       <c r="B62" s="6" t="s">
         <v>1004</v>
       </c>
-    </row>
-    <row r="63" spans="1:2">
+      <c r="C62" s="2" t="str">
+        <f xml:space="preserve"> A62 &amp; " " &amp; B62</f>
+        <v>GEL 格鲁吉亚拉里</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3">
       <c r="A63" s="5" t="s">
         <v>1005</v>
       </c>
       <c r="B63" s="6" t="s">
         <v>1006</v>
       </c>
-    </row>
-    <row r="64" spans="1:2">
+      <c r="C63" s="2" t="str">
+        <f xml:space="preserve"> A63 &amp; " " &amp; B63</f>
+        <v>GHS 加纳塞地</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3">
       <c r="A64" s="5" t="s">
         <v>1007</v>
       </c>
       <c r="B64" s="6" t="s">
         <v>1008</v>
       </c>
-    </row>
-    <row r="65" spans="1:2">
+      <c r="C64" s="2" t="str">
+        <f xml:space="preserve"> A64 &amp; " " &amp; B64</f>
+        <v>GIP 直布罗陀镑</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
       <c r="A65" s="5" t="s">
         <v>1009</v>
       </c>
       <c r="B65" s="6" t="s">
         <v>1010</v>
       </c>
-    </row>
-    <row r="66" spans="1:2">
+      <c r="C65" s="2" t="str">
+        <f xml:space="preserve"> A65 &amp; " " &amp; B65</f>
+        <v>GMD 冈比亚达拉西</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
       <c r="A66" s="5" t="s">
         <v>1011</v>
       </c>
       <c r="B66" s="6" t="s">
         <v>1012</v>
       </c>
-    </row>
-    <row r="67" spans="1:2">
+      <c r="C66" s="2" t="str">
+        <f xml:space="preserve"> A66 &amp; " " &amp; B66</f>
+        <v>GNF 几内亚法郎</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3">
       <c r="A67" s="5" t="s">
         <v>1013</v>
       </c>
       <c r="B67" s="6" t="s">
         <v>1014</v>
       </c>
-    </row>
-    <row r="68" spans="1:2">
+      <c r="C67" s="2" t="str">
+        <f xml:space="preserve"> A67 &amp; " " &amp; B67</f>
+        <v>GTQ 危地马拉格查尔</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3">
       <c r="A68" s="5" t="s">
         <v>1015</v>
       </c>
       <c r="B68" s="6" t="s">
         <v>1016</v>
       </c>
-    </row>
-    <row r="69" spans="1:2">
+      <c r="C68" s="2" t="str">
+        <f xml:space="preserve"> A68 &amp; " " &amp; B68</f>
+        <v>GYD 圭亚那元</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3">
       <c r="A69" s="5" t="s">
         <v>1017</v>
       </c>
       <c r="B69" s="6" t="s">
         <v>1018</v>
       </c>
-    </row>
-    <row r="70" spans="1:2">
+      <c r="C69" s="2" t="str">
+        <f xml:space="preserve"> A69 &amp; " " &amp; B69</f>
+        <v>HNL 洪都拉斯伦皮拉</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3">
       <c r="A70" s="5" t="s">
         <v>1019</v>
       </c>
       <c r="B70" s="6" t="s">
         <v>1020</v>
       </c>
-    </row>
-    <row r="71" spans="1:2">
+      <c r="C70" s="2" t="str">
+        <f xml:space="preserve"> A70 &amp; " " &amp; B70</f>
+        <v>HRK 克罗地亚库纳</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3">
       <c r="A71" s="5" t="s">
         <v>1021</v>
       </c>
       <c r="B71" s="6" t="s">
         <v>1022</v>
       </c>
-    </row>
-    <row r="72" spans="1:2">
+      <c r="C71" s="2" t="str">
+        <f xml:space="preserve"> A71 &amp; " " &amp; B71</f>
+        <v>HTG 海地古德</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3">
       <c r="A72" s="5" t="s">
         <v>1023</v>
       </c>
       <c r="B72" s="6" t="s">
         <v>1024</v>
       </c>
-    </row>
-    <row r="73" spans="1:2">
+      <c r="C72" s="2" t="str">
+        <f xml:space="preserve"> A72 &amp; " " &amp; B72</f>
+        <v>HUF 匈牙利福林</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3">
       <c r="A73" s="5" t="s">
         <v>1025</v>
       </c>
       <c r="B73" s="6" t="s">
         <v>1026</v>
       </c>
-    </row>
-    <row r="74" spans="1:2">
+      <c r="C73" s="2" t="str">
+        <f xml:space="preserve"> A73 &amp; " " &amp; B73</f>
+        <v>IDR 印度尼西亚卢比</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3">
       <c r="A74" s="5" t="s">
         <v>1027</v>
       </c>
       <c r="B74" s="6" t="s">
         <v>1028</v>
       </c>
-    </row>
-    <row r="75" spans="1:2">
+      <c r="C74" s="2" t="str">
+        <f xml:space="preserve"> A74 &amp; " " &amp; B74</f>
+        <v>ILS 以色列新谢克尔</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3">
       <c r="A75" s="5" t="s">
         <v>1029</v>
       </c>
       <c r="B75" s="6" t="s">
         <v>1030</v>
       </c>
-    </row>
-    <row r="76" spans="1:2">
+      <c r="C75" s="2" t="str">
+        <f xml:space="preserve"> A75 &amp; " " &amp; B75</f>
+        <v>INR 印度卢比</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3">
       <c r="A76" s="5" t="s">
         <v>1031</v>
       </c>
       <c r="B76" s="6" t="s">
         <v>1032</v>
       </c>
-    </row>
-    <row r="77" spans="1:2">
+      <c r="C76" s="2" t="str">
+        <f xml:space="preserve"> A76 &amp; " " &amp; B76</f>
+        <v>IQD 伊拉克第纳尔</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3">
       <c r="A77" s="5" t="s">
         <v>1033</v>
       </c>
       <c r="B77" s="6" t="s">
         <v>1034</v>
       </c>
-    </row>
-    <row r="78" spans="1:2">
+      <c r="C77" s="2" t="str">
+        <f xml:space="preserve"> A77 &amp; " " &amp; B77</f>
+        <v>IRR 伊朗里亚尔</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3">
       <c r="A78" s="5" t="s">
         <v>1035</v>
       </c>
       <c r="B78" s="6" t="s">
         <v>1036</v>
       </c>
-    </row>
-    <row r="79" spans="1:2">
+      <c r="C78" s="2" t="str">
+        <f xml:space="preserve"> A78 &amp; " " &amp; B78</f>
+        <v>ISK 冰岛克朗</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3">
       <c r="A79" s="5" t="s">
         <v>1037</v>
       </c>
       <c r="B79" s="6" t="s">
         <v>1038</v>
       </c>
-    </row>
-    <row r="80" spans="1:2">
+      <c r="C79" s="2" t="str">
+        <f xml:space="preserve"> A79 &amp; " " &amp; B79</f>
+        <v>JMD 牙买加元</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3">
       <c r="A80" s="5" t="s">
         <v>1039</v>
       </c>
       <c r="B80" s="6" t="s">
         <v>1040</v>
       </c>
-    </row>
-    <row r="81" spans="1:2">
+      <c r="C80" s="2" t="str">
+        <f xml:space="preserve"> A80 &amp; " " &amp; B80</f>
+        <v>JOD 约旦第纳尔</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3">
       <c r="A81" s="5" t="s">
         <v>1041</v>
       </c>
       <c r="B81" s="6" t="s">
         <v>1042</v>
       </c>
-    </row>
-    <row r="82" spans="1:2">
+      <c r="C81" s="2" t="str">
+        <f xml:space="preserve"> A81 &amp; " " &amp; B81</f>
+        <v>KES 肯尼亚先令</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3">
       <c r="A82" s="5" t="s">
         <v>1043</v>
       </c>
       <c r="B82" s="6" t="s">
         <v>1044</v>
       </c>
-    </row>
-    <row r="83" spans="1:2">
+      <c r="C82" s="2" t="str">
+        <f xml:space="preserve"> A82 &amp; " " &amp; B82</f>
+        <v>KGS 吉尔吉斯斯坦索姆</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3">
       <c r="A83" s="5" t="s">
         <v>1045</v>
       </c>
       <c r="B83" s="6" t="s">
         <v>1046</v>
       </c>
-    </row>
-    <row r="84" spans="1:2">
+      <c r="C83" s="2" t="str">
+        <f xml:space="preserve"> A83 &amp; " " &amp; B83</f>
+        <v>KHR 柬埔寨瑞尔</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3">
       <c r="A84" s="5" t="s">
         <v>1047</v>
       </c>
       <c r="B84" s="6" t="s">
         <v>1048</v>
       </c>
-    </row>
-    <row r="85" spans="1:2">
+      <c r="C84" s="2" t="str">
+        <f xml:space="preserve"> A84 &amp; " " &amp; B84</f>
+        <v>KMF 科摩罗法郎</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3">
       <c r="A85" s="5" t="s">
         <v>1049</v>
       </c>
       <c r="B85" s="6" t="s">
         <v>1050</v>
       </c>
-    </row>
-    <row r="86" spans="1:2">
+      <c r="C85" s="2" t="str">
+        <f xml:space="preserve"> A85 &amp; " " &amp; B85</f>
+        <v>KPW 朝鲜元</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3">
       <c r="A86" s="5" t="s">
         <v>1051</v>
       </c>
       <c r="B86" s="6" t="s">
         <v>1052</v>
       </c>
-    </row>
-    <row r="87" spans="1:2">
+      <c r="C86" s="2" t="str">
+        <f xml:space="preserve"> A86 &amp; " " &amp; B86</f>
+        <v>KRW 韩元</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3">
       <c r="A87" s="5" t="s">
         <v>1053</v>
       </c>
       <c r="B87" s="6" t="s">
         <v>1054</v>
       </c>
-    </row>
-    <row r="88" spans="1:2">
+      <c r="C87" s="2" t="str">
+        <f xml:space="preserve"> A87 &amp; " " &amp; B87</f>
+        <v>KWD 科威特第纳尔</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3">
       <c r="A88" s="5" t="s">
         <v>1055</v>
       </c>
       <c r="B88" s="6" t="s">
         <v>1056</v>
       </c>
-    </row>
-    <row r="89" spans="1:2">
+      <c r="C88" s="2" t="str">
+        <f xml:space="preserve"> A88 &amp; " " &amp; B88</f>
+        <v>KYD 开曼群岛元</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3">
       <c r="A89" s="5" t="s">
         <v>1057</v>
       </c>
       <c r="B89" s="6" t="s">
         <v>1058</v>
       </c>
-    </row>
-    <row r="90" spans="1:2">
+      <c r="C89" s="2" t="str">
+        <f xml:space="preserve"> A89 &amp; " " &amp; B89</f>
+        <v>KZT 哈萨克斯坦坚戈</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3">
       <c r="A90" s="5" t="s">
         <v>1059</v>
       </c>
       <c r="B90" s="6" t="s">
         <v>1060</v>
       </c>
-    </row>
-    <row r="91" spans="1:2">
+      <c r="C90" s="2" t="str">
+        <f xml:space="preserve"> A90 &amp; " " &amp; B90</f>
+        <v>LAK 老挝基普</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3">
       <c r="A91" s="5" t="s">
         <v>1061</v>
       </c>
       <c r="B91" s="6" t="s">
         <v>1062</v>
       </c>
-    </row>
-    <row r="92" spans="1:2">
+      <c r="C91" s="2" t="str">
+        <f xml:space="preserve"> A91 &amp; " " &amp; B91</f>
+        <v>LBP 黎巴嫩镑</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3">
       <c r="A92" s="5" t="s">
         <v>1063</v>
       </c>
       <c r="B92" s="6" t="s">
         <v>1064</v>
       </c>
-    </row>
-    <row r="93" spans="1:2">
+      <c r="C92" s="2" t="str">
+        <f xml:space="preserve"> A92 &amp; " " &amp; B92</f>
+        <v>LKR 斯里兰卡卢比</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3">
       <c r="A93" s="5" t="s">
         <v>1065</v>
       </c>
       <c r="B93" s="6" t="s">
         <v>1066</v>
       </c>
-    </row>
-    <row r="94" spans="1:2">
+      <c r="C93" s="2" t="str">
+        <f xml:space="preserve"> A93 &amp; " " &amp; B93</f>
+        <v>LRD 利比里亚元</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3">
       <c r="A94" s="5" t="s">
         <v>1067</v>
       </c>
       <c r="B94" s="6" t="s">
         <v>1068</v>
       </c>
-    </row>
-    <row r="95" spans="1:2">
+      <c r="C94" s="2" t="str">
+        <f xml:space="preserve"> A94 &amp; " " &amp; B94</f>
+        <v>LSL 莱索托洛蒂</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3">
       <c r="A95" s="5" t="s">
         <v>1069</v>
       </c>
       <c r="B95" s="6" t="s">
         <v>1070</v>
       </c>
-    </row>
-    <row r="96" spans="1:2">
+      <c r="C95" s="2" t="str">
+        <f xml:space="preserve"> A95 &amp; " " &amp; B95</f>
+        <v>LYD 利比亚第纳尔</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3">
       <c r="A96" s="5" t="s">
         <v>1071</v>
       </c>
       <c r="B96" s="6" t="s">
         <v>1072</v>
       </c>
-    </row>
-    <row r="97" spans="1:2">
+      <c r="C96" s="2" t="str">
+        <f xml:space="preserve"> A96 &amp; " " &amp; B96</f>
+        <v>MAD 摩洛哥迪拉姆</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3">
       <c r="A97" s="5" t="s">
         <v>1073</v>
       </c>
       <c r="B97" s="6" t="s">
         <v>1074</v>
       </c>
-    </row>
-    <row r="98" spans="1:2">
+      <c r="C97" s="2" t="str">
+        <f xml:space="preserve"> A97 &amp; " " &amp; B97</f>
+        <v>MDL 摩尔多瓦列伊</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3">
       <c r="A98" s="5" t="s">
         <v>1075</v>
       </c>
       <c r="B98" s="6" t="s">
         <v>1076</v>
       </c>
-    </row>
-    <row r="99" spans="1:2">
+      <c r="C98" s="2" t="str">
+        <f xml:space="preserve"> A98 &amp; " " &amp; B98</f>
+        <v>MGA 马达加斯加阿里亚里</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3">
       <c r="A99" s="5" t="s">
         <v>658</v>
       </c>
       <c r="B99" s="6" t="s">
         <v>1077</v>
       </c>
-    </row>
-    <row r="100" spans="1:2">
+      <c r="C99" s="2" t="str">
+        <f xml:space="preserve"> A99 &amp; " " &amp; B99</f>
+        <v>MKD 马其顿代纳尔</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3">
       <c r="A100" s="5" t="s">
         <v>1078</v>
       </c>
       <c r="B100" s="6" t="s">
         <v>1079</v>
       </c>
-    </row>
-    <row r="101" spans="1:2">
+      <c r="C100" s="2" t="str">
+        <f xml:space="preserve"> A100 &amp; " " &amp; B100</f>
+        <v>MMK 缅甸元</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3">
       <c r="A101" s="5" t="s">
         <v>1080</v>
       </c>
       <c r="B101" s="6" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="102" spans="1:2">
+      <c r="C101" s="2" t="str">
+        <f xml:space="preserve"> A101 &amp; " " &amp; B101</f>
+        <v>MNT 蒙古图格里克</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3">
       <c r="A102" s="5" t="s">
         <v>1082</v>
       </c>
       <c r="B102" s="6" t="s">
         <v>1083</v>
       </c>
-    </row>
-    <row r="103" spans="1:2">
+      <c r="C102" s="2" t="str">
+        <f xml:space="preserve"> A102 &amp; " " &amp; B102</f>
+        <v>MRO 毛里塔尼亚乌吉亚</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3">
       <c r="A103" s="5" t="s">
         <v>1084</v>
       </c>
       <c r="B103" s="6" t="s">
         <v>1085</v>
       </c>
-    </row>
-    <row r="104" spans="1:2">
+      <c r="C103" s="2" t="str">
+        <f xml:space="preserve"> A103 &amp; " " &amp; B103</f>
+        <v>MUR 毛里求斯卢比</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3">
       <c r="A104" s="5" t="s">
         <v>1086</v>
       </c>
       <c r="B104" s="6" t="s">
         <v>1087</v>
       </c>
-    </row>
-    <row r="105" spans="1:2">
+      <c r="C104" s="2" t="str">
+        <f xml:space="preserve"> A104 &amp; " " &amp; B104</f>
+        <v>MVR 马尔代夫拉菲亚</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3">
       <c r="A105" s="5" t="s">
         <v>1088</v>
       </c>
       <c r="B105" s="6" t="s">
         <v>1089</v>
       </c>
-    </row>
-    <row r="106" spans="1:2">
+      <c r="C105" s="2" t="str">
+        <f xml:space="preserve"> A105 &amp; " " &amp; B105</f>
+        <v>MWK 马拉维克瓦查</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3">
       <c r="A106" s="5" t="s">
         <v>1090</v>
       </c>
       <c r="B106" s="6" t="s">
         <v>1091</v>
       </c>
-    </row>
-    <row r="107" spans="1:2">
+      <c r="C106" s="2" t="str">
+        <f xml:space="preserve"> A106 &amp; " " &amp; B106</f>
+        <v>MXN 墨西哥比索</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3">
       <c r="A107" s="5" t="s">
         <v>1092</v>
       </c>
       <c r="B107" s="6" t="s">
         <v>1093</v>
       </c>
-    </row>
-    <row r="108" spans="1:2">
+      <c r="C107" s="2" t="str">
+        <f xml:space="preserve"> A107 &amp; " " &amp; B107</f>
+        <v>MXV 墨西哥UDI基金</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3">
       <c r="A108" s="5" t="s">
         <v>1094</v>
       </c>
       <c r="B108" s="6" t="s">
         <v>1095</v>
       </c>
-    </row>
-    <row r="109" spans="1:2">
+      <c r="C108" s="2" t="str">
+        <f xml:space="preserve"> A108 &amp; " " &amp; B108</f>
+        <v>MYR 马来西亚令吉</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3">
       <c r="A109" s="5" t="s">
         <v>1096</v>
       </c>
       <c r="B109" s="6" t="s">
         <v>1097</v>
       </c>
-    </row>
-    <row r="110" spans="1:2">
+      <c r="C109" s="2" t="str">
+        <f xml:space="preserve"> A109 &amp; " " &amp; B109</f>
+        <v>MZN 莫桑比克梅蒂卡尔</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3">
       <c r="A110" s="5" t="s">
         <v>1098</v>
       </c>
       <c r="B110" s="6" t="s">
         <v>1099</v>
       </c>
-    </row>
-    <row r="111" spans="1:2">
+      <c r="C110" s="2" t="str">
+        <f xml:space="preserve"> A110 &amp; " " &amp; B110</f>
+        <v>NAD 纳米比亚元</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3">
       <c r="A111" s="5" t="s">
         <v>1100</v>
       </c>
       <c r="B111" s="6" t="s">
         <v>1101</v>
       </c>
-    </row>
-    <row r="112" spans="1:2">
+      <c r="C111" s="2" t="str">
+        <f xml:space="preserve"> A111 &amp; " " &amp; B111</f>
+        <v>NGN 尼日利亚奈拉</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3">
       <c r="A112" s="5" t="s">
         <v>1102</v>
       </c>
       <c r="B112" s="6" t="s">
         <v>1103</v>
       </c>
-    </row>
-    <row r="113" spans="1:2">
+      <c r="C112" s="2" t="str">
+        <f xml:space="preserve"> A112 &amp; " " &amp; B112</f>
+        <v>NIO 尼加拉瓜科多巴</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3">
       <c r="A113" s="5" t="s">
         <v>1104</v>
       </c>
       <c r="B113" s="6" t="s">
         <v>1105</v>
       </c>
-    </row>
-    <row r="114" spans="1:2">
+      <c r="C113" s="2" t="str">
+        <f xml:space="preserve"> A113 &amp; " " &amp; B113</f>
+        <v>NOK 挪威克朗</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3">
       <c r="A114" s="5" t="s">
         <v>1106</v>
       </c>
       <c r="B114" s="6" t="s">
         <v>1107</v>
       </c>
-    </row>
-    <row r="115" spans="1:2">
+      <c r="C114" s="2" t="str">
+        <f xml:space="preserve"> A114 &amp; " " &amp; B114</f>
+        <v>NPR 尼泊尔卢比</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3">
       <c r="A115" s="5" t="s">
         <v>1108</v>
       </c>
       <c r="B115" s="6" t="s">
         <v>1109</v>
       </c>
-    </row>
-    <row r="116" spans="1:2">
+      <c r="C115" s="2" t="str">
+        <f xml:space="preserve"> A115 &amp; " " &amp; B115</f>
+        <v>NZD 新西兰元</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3">
       <c r="A116" s="5" t="s">
         <v>1110</v>
       </c>
       <c r="B116" s="6" t="s">
         <v>1111</v>
       </c>
-    </row>
-    <row r="117" spans="1:2">
+      <c r="C116" s="2" t="str">
+        <f xml:space="preserve"> A116 &amp; " " &amp; B116</f>
+        <v>OMR 阿曼里亚尔</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3">
       <c r="A117" s="5" t="s">
         <v>1112</v>
       </c>
       <c r="B117" s="6" t="s">
         <v>1113</v>
       </c>
-    </row>
-    <row r="118" spans="1:2">
+      <c r="C117" s="2" t="str">
+        <f xml:space="preserve"> A117 &amp; " " &amp; B117</f>
+        <v>PAB 巴拿马巴波亚</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3">
       <c r="A118" s="5" t="s">
         <v>1114</v>
       </c>
       <c r="B118" s="6" t="s">
         <v>1115</v>
       </c>
-    </row>
-    <row r="119" spans="1:2">
+      <c r="C118" s="2" t="str">
+        <f xml:space="preserve"> A118 &amp; " " &amp; B118</f>
+        <v>PEN 秘鲁新索尔</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3">
       <c r="A119" s="5" t="s">
         <v>1116</v>
       </c>
       <c r="B119" s="6" t="s">
         <v>1117</v>
       </c>
-    </row>
-    <row r="120" spans="1:2">
+      <c r="C119" s="2" t="str">
+        <f xml:space="preserve"> A119 &amp; " " &amp; B119</f>
+        <v>PGK 巴布亚新几内亚基那</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3">
       <c r="A120" s="5" t="s">
         <v>1118</v>
       </c>
       <c r="B120" s="6" t="s">
         <v>1119</v>
       </c>
-    </row>
-    <row r="121" spans="1:2">
+      <c r="C120" s="2" t="str">
+        <f xml:space="preserve"> A120 &amp; " " &amp; B120</f>
+        <v>PHP 菲律宾比索</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3">
       <c r="A121" s="5" t="s">
         <v>1120</v>
       </c>
       <c r="B121" s="6" t="s">
         <v>1121</v>
       </c>
-    </row>
-    <row r="122" spans="1:2">
+      <c r="C121" s="2" t="str">
+        <f xml:space="preserve"> A121 &amp; " " &amp; B121</f>
+        <v>PKR 巴基斯坦卢比</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3">
       <c r="A122" s="5" t="s">
         <v>1122</v>
       </c>
       <c r="B122" s="6" t="s">
         <v>1123</v>
       </c>
-    </row>
-    <row r="123" spans="1:2">
+      <c r="C122" s="2" t="str">
+        <f xml:space="preserve"> A122 &amp; " " &amp; B122</f>
+        <v>PLN 波兰兹罗提</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3">
       <c r="A123" s="5" t="s">
         <v>1124</v>
       </c>
       <c r="B123" s="6" t="s">
         <v>1125</v>
       </c>
-    </row>
-    <row r="124" spans="1:2">
+      <c r="C123" s="2" t="str">
+        <f xml:space="preserve"> A123 &amp; " " &amp; B123</f>
+        <v>PYG 巴拉圭瓜拉尼</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3">
       <c r="A124" s="5" t="s">
         <v>1126</v>
       </c>
       <c r="B124" s="6" t="s">
         <v>1127</v>
       </c>
-    </row>
-    <row r="125" spans="1:2">
+      <c r="C124" s="2" t="str">
+        <f xml:space="preserve"> A124 &amp; " " &amp; B124</f>
+        <v>QAR 卡塔尔里亚尔</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3">
       <c r="A125" s="5" t="s">
         <v>1128</v>
       </c>
       <c r="B125" s="6" t="s">
         <v>1129</v>
       </c>
-    </row>
-    <row r="126" spans="1:2">
+      <c r="C125" s="2" t="str">
+        <f xml:space="preserve"> A125 &amp; " " &amp; B125</f>
+        <v>RON 罗马尼亚列伊</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3">
       <c r="A126" s="5" t="s">
         <v>1130</v>
       </c>
       <c r="B126" s="6" t="s">
         <v>1131</v>
       </c>
-    </row>
-    <row r="127" spans="1:2">
+      <c r="C126" s="2" t="str">
+        <f xml:space="preserve"> A126 &amp; " " &amp; B126</f>
+        <v>RSD 塞尔维亚第纳尔</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3">
       <c r="A127" s="5" t="s">
         <v>1132</v>
       </c>
       <c r="B127" s="6" t="s">
         <v>1133</v>
       </c>
-    </row>
-    <row r="128" spans="1:2">
+      <c r="C127" s="2" t="str">
+        <f xml:space="preserve"> A127 &amp; " " &amp; B127</f>
+        <v>RWF 卢旺达法郎</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3">
       <c r="A128" s="5" t="s">
         <v>1134</v>
       </c>
       <c r="B128" s="6" t="s">
         <v>1135</v>
       </c>
-    </row>
-    <row r="129" spans="1:2">
+      <c r="C128" s="2" t="str">
+        <f xml:space="preserve"> A128 &amp; " " &amp; B128</f>
+        <v>SAR 沙特里亚尔</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3">
       <c r="A129" s="5" t="s">
         <v>1136</v>
       </c>
       <c r="B129" s="6" t="s">
         <v>1137</v>
       </c>
-    </row>
-    <row r="130" spans="1:2">
+      <c r="C129" s="2" t="str">
+        <f xml:space="preserve"> A129 &amp; " " &amp; B129</f>
+        <v>SBD 所罗门群岛元</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3">
       <c r="A130" s="5" t="s">
         <v>1138</v>
       </c>
       <c r="B130" s="6" t="s">
         <v>1139</v>
       </c>
-    </row>
-    <row r="131" spans="1:2">
+      <c r="C130" s="2" t="str">
+        <f xml:space="preserve"> A130 &amp; " " &amp; B130</f>
+        <v>SCR 塞舌尔卢比</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3">
       <c r="A131" s="5" t="s">
         <v>1140</v>
       </c>
       <c r="B131" s="6" t="s">
         <v>1141</v>
       </c>
-    </row>
-    <row r="132" spans="1:2">
+      <c r="C131" s="2" t="str">
+        <f xml:space="preserve"> A131 &amp; " " &amp; B131</f>
+        <v>SDG 苏丹镑</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3">
       <c r="A132" s="5" t="s">
         <v>1142</v>
       </c>
       <c r="B132" s="6" t="s">
         <v>1143</v>
       </c>
-    </row>
-    <row r="133" spans="1:2">
+      <c r="C132" s="2" t="str">
+        <f xml:space="preserve"> A132 &amp; " " &amp; B132</f>
+        <v>SHP 圣赫勒拿镑</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3">
       <c r="A133" s="5" t="s">
         <v>1144</v>
       </c>
       <c r="B133" s="6" t="s">
         <v>1145</v>
       </c>
-    </row>
-    <row r="134" spans="1:2">
+      <c r="C133" s="2" t="str">
+        <f xml:space="preserve"> A133 &amp; " " &amp; B133</f>
+        <v>SLL 塞拉利昂利昂</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3">
       <c r="A134" s="5" t="s">
         <v>1146</v>
       </c>
       <c r="B134" s="6" t="s">
         <v>1147</v>
       </c>
-    </row>
-    <row r="135" spans="1:2">
+      <c r="C134" s="2" t="str">
+        <f xml:space="preserve"> A134 &amp; " " &amp; B134</f>
+        <v>SOS 索马里先令</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3">
       <c r="A135" s="5" t="s">
         <v>1148</v>
       </c>
       <c r="B135" s="6" t="s">
         <v>1149</v>
       </c>
-    </row>
-    <row r="136" spans="1:2">
+      <c r="C135" s="2" t="str">
+        <f xml:space="preserve"> A135 &amp; " " &amp; B135</f>
+        <v>SRD 苏里南元</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3">
       <c r="A136" s="5" t="s">
         <v>1150</v>
       </c>
       <c r="B136" s="6" t="s">
         <v>1151</v>
       </c>
-    </row>
-    <row r="137" spans="1:2">
+      <c r="C136" s="2" t="str">
+        <f xml:space="preserve"> A136 &amp; " " &amp; B136</f>
+        <v>SSP 南苏丹镑</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3">
       <c r="A137" s="5" t="s">
         <v>1152</v>
       </c>
       <c r="B137" s="6" t="s">
         <v>1153</v>
       </c>
-    </row>
-    <row r="138" spans="1:2">
+      <c r="C137" s="2" t="str">
+        <f xml:space="preserve"> A137 &amp; " " &amp; B137</f>
+        <v>STD 圣多美和普林西比多布拉</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3">
       <c r="A138" s="5" t="s">
         <v>1154</v>
       </c>
       <c r="B138" s="6" t="s">
         <v>1155</v>
       </c>
-    </row>
-    <row r="139" spans="1:2">
+      <c r="C138" s="2" t="str">
+        <f xml:space="preserve"> A138 &amp; " " &amp; B138</f>
+        <v>SVC 萨尔瓦多科朗</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3">
       <c r="A139" s="5" t="s">
         <v>1156</v>
       </c>
       <c r="B139" s="6" t="s">
         <v>1157</v>
       </c>
-    </row>
-    <row r="140" spans="1:2">
+      <c r="C139" s="2" t="str">
+        <f xml:space="preserve"> A139 &amp; " " &amp; B139</f>
+        <v>SYP 叙利亚镑</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3">
       <c r="A140" s="5" t="s">
         <v>1158</v>
       </c>
       <c r="B140" s="6" t="s">
         <v>1159</v>
       </c>
-    </row>
-    <row r="141" spans="1:2">
+      <c r="C140" s="2" t="str">
+        <f xml:space="preserve"> A140 &amp; " " &amp; B140</f>
+        <v>SZL 斯威士兰里兰吉尼</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3">
       <c r="A141" s="5" t="s">
         <v>1160</v>
       </c>
       <c r="B141" s="6" t="s">
         <v>1161</v>
       </c>
-    </row>
-    <row r="142" spans="1:2">
+      <c r="C141" s="2" t="str">
+        <f xml:space="preserve"> A141 &amp; " " &amp; B141</f>
+        <v>THB 泰铢</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3">
       <c r="A142" s="5" t="s">
         <v>1162</v>
       </c>
       <c r="B142" s="6" t="s">
         <v>1163</v>
       </c>
-    </row>
-    <row r="143" spans="1:2">
+      <c r="C142" s="2" t="str">
+        <f xml:space="preserve"> A142 &amp; " " &amp; B142</f>
+        <v>TJS 塔吉克斯坦索莫尼</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3">
       <c r="A143" s="5" t="s">
         <v>1164</v>
       </c>
       <c r="B143" s="6" t="s">
         <v>1165</v>
       </c>
-    </row>
-    <row r="144" spans="1:2">
+      <c r="C143" s="2" t="str">
+        <f xml:space="preserve"> A143 &amp; " " &amp; B143</f>
+        <v>TMT 土库曼斯坦马纳特</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3">
       <c r="A144" s="5" t="s">
         <v>1166</v>
       </c>
       <c r="B144" s="6" t="s">
         <v>1167</v>
       </c>
-    </row>
-    <row r="145" spans="1:2">
+      <c r="C144" s="2" t="str">
+        <f xml:space="preserve"> A144 &amp; " " &amp; B144</f>
+        <v>TND 突尼斯第纳尔</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3">
       <c r="A145" s="5" t="s">
         <v>1168</v>
       </c>
       <c r="B145" s="6" t="s">
         <v>1169</v>
       </c>
-    </row>
-    <row r="146" spans="1:2">
+      <c r="C145" s="2" t="str">
+        <f xml:space="preserve"> A145 &amp; " " &amp; B145</f>
+        <v>TOP 汤加潘加</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3">
       <c r="A146" s="5" t="s">
         <v>1170</v>
       </c>
       <c r="B146" s="6" t="s">
         <v>1171</v>
       </c>
-    </row>
-    <row r="147" spans="1:2">
+      <c r="C146" s="2" t="str">
+        <f xml:space="preserve"> A146 &amp; " " &amp; B146</f>
+        <v>TRY 土耳其里拉</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3">
       <c r="A147" s="5" t="s">
         <v>1172</v>
       </c>
       <c r="B147" s="6" t="s">
         <v>1173</v>
       </c>
-    </row>
-    <row r="148" spans="1:2">
+      <c r="C147" s="2" t="str">
+        <f xml:space="preserve"> A147 &amp; " " &amp; B147</f>
+        <v>TTD 特立尼达和多巴哥元</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3">
       <c r="A148" s="5" t="s">
         <v>1174</v>
       </c>
       <c r="B148" s="6" t="s">
         <v>1175</v>
       </c>
-    </row>
-    <row r="149" spans="1:2">
+      <c r="C148" s="2" t="str">
+        <f xml:space="preserve"> A148 &amp; " " &amp; B148</f>
+        <v>TZS 坦桑尼亚先令</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3">
       <c r="A149" s="5" t="s">
         <v>1176</v>
       </c>
       <c r="B149" s="6" t="s">
         <v>1177</v>
       </c>
-    </row>
-    <row r="150" spans="1:2">
+      <c r="C149" s="2" t="str">
+        <f xml:space="preserve"> A149 &amp; " " &amp; B149</f>
+        <v>UAH 乌克兰格里夫尼亚</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3">
       <c r="A150" s="5" t="s">
         <v>1178</v>
       </c>
       <c r="B150" s="6" t="s">
         <v>1179</v>
       </c>
-    </row>
-    <row r="151" spans="1:2">
+      <c r="C150" s="2" t="str">
+        <f xml:space="preserve"> A150 &amp; " " &amp; B150</f>
+        <v>UGX 乌干达先令</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3">
       <c r="A151" s="5" t="s">
         <v>1180</v>
       </c>
       <c r="B151" s="6" t="s">
         <v>1181</v>
       </c>
-    </row>
-    <row r="152" spans="1:2">
+      <c r="C151" s="2" t="str">
+        <f xml:space="preserve"> A151 &amp; " " &amp; B151</f>
+        <v>USN 美元翌日基金</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3">
       <c r="A152" s="5" t="s">
         <v>1182</v>
       </c>
       <c r="B152" s="6" t="s">
         <v>1183</v>
       </c>
-    </row>
-    <row r="153" spans="1:2">
+      <c r="C152" s="2" t="str">
+        <f xml:space="preserve"> A152 &amp; " " &amp; B152</f>
+        <v>UYI 乌拉圭URUIURUI基金</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3">
       <c r="A153" s="5" t="s">
         <v>1184</v>
       </c>
       <c r="B153" s="6" t="s">
         <v>1185</v>
       </c>
-    </row>
-    <row r="154" spans="1:2">
+      <c r="C153" s="2" t="str">
+        <f xml:space="preserve"> A153 &amp; " " &amp; B153</f>
+        <v>UYU 乌拉圭比索</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3">
       <c r="A154" s="5" t="s">
         <v>1186</v>
       </c>
       <c r="B154" s="6" t="s">
         <v>1187</v>
       </c>
-    </row>
-    <row r="155" spans="1:2">
+      <c r="C154" s="2" t="str">
+        <f xml:space="preserve"> A154 &amp; " " &amp; B154</f>
+        <v>UZS 乌兹别克斯坦苏姆</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3">
       <c r="A155" s="5" t="s">
         <v>1188</v>
       </c>
       <c r="B155" s="6" t="s">
         <v>1189</v>
       </c>
-    </row>
-    <row r="156" spans="1:2">
+      <c r="C155" s="2" t="str">
+        <f xml:space="preserve"> A155 &amp; " " &amp; B155</f>
+        <v>VEF 委内瑞拉博利瓦</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3">
       <c r="A156" s="5" t="s">
         <v>1190</v>
       </c>
       <c r="B156" s="6" t="s">
         <v>1191</v>
       </c>
-    </row>
-    <row r="157" spans="1:2">
+      <c r="C156" s="2" t="str">
+        <f xml:space="preserve"> A156 &amp; " " &amp; B156</f>
+        <v>VND 越南盾</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3">
       <c r="A157" s="5" t="s">
         <v>1192</v>
       </c>
       <c r="B157" s="6" t="s">
         <v>1193</v>
       </c>
-    </row>
-    <row r="158" spans="1:2">
+      <c r="C157" s="2" t="str">
+        <f xml:space="preserve"> A157 &amp; " " &amp; B157</f>
+        <v>VUV 瓦努阿图瓦图</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3">
       <c r="A158" s="5" t="s">
         <v>1194</v>
       </c>
       <c r="B158" s="6" t="s">
         <v>1195</v>
       </c>
-    </row>
-    <row r="159" spans="1:2">
+      <c r="C158" s="2" t="str">
+        <f xml:space="preserve"> A158 &amp; " " &amp; B158</f>
+        <v>WST 萨摩亚塔拉</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3">
       <c r="A159" s="5" t="s">
         <v>1196</v>
       </c>
       <c r="B159" s="6" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="160" spans="1:2">
+      <c r="C159" s="2" t="str">
+        <f xml:space="preserve"> A159 &amp; " " &amp; B159</f>
+        <v>XAF 中非金融合作法郎（中非法郎）</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3">
       <c r="A160" s="5" t="s">
         <v>1198</v>
       </c>
       <c r="B160" s="6" t="s">
         <v>1199</v>
       </c>
-    </row>
-    <row r="161" spans="1:2">
+      <c r="C160" s="2" t="str">
+        <f xml:space="preserve"> A160 &amp; " " &amp; B160</f>
+        <v>XAG 银（一盎司）</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3">
       <c r="A161" s="5" t="s">
         <v>1200</v>
       </c>
       <c r="B161" s="6" t="s">
         <v>1201</v>
       </c>
-    </row>
-    <row r="162" spans="1:2">
+      <c r="C161" s="2" t="str">
+        <f xml:space="preserve"> A161 &amp; " " &amp; B161</f>
+        <v>XAU 金（一盎司）</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3">
       <c r="A162" s="5" t="s">
         <v>1202</v>
       </c>
       <c r="B162" s="6" t="s">
         <v>1203</v>
       </c>
-    </row>
-    <row r="163" spans="1:2">
+      <c r="C162" s="2" t="str">
+        <f xml:space="preserve"> A162 &amp; " " &amp; B162</f>
+        <v>XBA 欧洲混合单位（债券市场单位）</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3">
       <c r="A163" s="5" t="s">
         <v>1204</v>
       </c>
       <c r="B163" s="6" t="s">
         <v>1205</v>
       </c>
-    </row>
-    <row r="164" spans="1:2">
+      <c r="C163" s="2" t="str">
+        <f xml:space="preserve"> A163 &amp; " " &amp; B163</f>
+        <v>XBB 欧洲货币单位（债券市场单位）</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3">
       <c r="A164" s="5" t="s">
         <v>1206</v>
       </c>
       <c r="B164" s="6" t="s">
         <v>1207</v>
       </c>
-    </row>
-    <row r="165" spans="1:2">
+      <c r="C164" s="2" t="str">
+        <f xml:space="preserve"> A164 &amp; " " &amp; B164</f>
+        <v>XBC 欧洲计算单位9（债券市场单位）</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3">
       <c r="A165" s="5" t="s">
         <v>1208</v>
       </c>
       <c r="B165" s="6" t="s">
         <v>1209</v>
       </c>
-    </row>
-    <row r="166" spans="1:2">
+      <c r="C165" s="2" t="str">
+        <f xml:space="preserve"> A165 &amp; " " &amp; B165</f>
+        <v>XBD 欧洲计算单位17（债券市场单位）</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3">
       <c r="A166" s="5" t="s">
         <v>1210</v>
       </c>
       <c r="B166" s="6" t="s">
         <v>1211</v>
       </c>
-    </row>
-    <row r="167" spans="1:2">
+      <c r="C166" s="2" t="str">
+        <f xml:space="preserve"> A166 &amp; " " &amp; B166</f>
+        <v>XCD 东加勒比元</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3">
       <c r="A167" s="5" t="s">
         <v>1212</v>
       </c>
       <c r="B167" s="6" t="s">
         <v>1213</v>
       </c>
-    </row>
-    <row r="168" spans="1:2">
+      <c r="C167" s="2" t="str">
+        <f xml:space="preserve"> A167 &amp; " " &amp; B167</f>
+        <v>XDR 特别提款权（国际货币基金）</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3">
       <c r="A168" s="5" t="s">
         <v>1214</v>
       </c>
       <c r="B168" s="6" t="s">
         <v>1215</v>
       </c>
-    </row>
-    <row r="169" spans="1:2">
+      <c r="C168" s="2" t="str">
+        <f xml:space="preserve"> A168 &amp; " " &amp; B168</f>
+        <v>XOF 非洲金融共同体法郎（西非法郎）</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3">
       <c r="A169" s="5" t="s">
         <v>1216</v>
       </c>
       <c r="B169" s="6" t="s">
         <v>1217</v>
       </c>
-    </row>
-    <row r="170" spans="1:2">
+      <c r="C169" s="2" t="str">
+        <f xml:space="preserve"> A169 &amp; " " &amp; B169</f>
+        <v>XPD 钯（一盎司）</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3">
       <c r="A170" s="5" t="s">
         <v>1218</v>
       </c>
       <c r="B170" s="6" t="s">
         <v>1219</v>
       </c>
-    </row>
-    <row r="171" spans="1:2">
+      <c r="C170" s="2" t="str">
+        <f xml:space="preserve"> A170 &amp; " " &amp; B170</f>
+        <v>XPF 太平洋法兰西共同体法郎（CFP法郎）</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3">
       <c r="A171" s="5" t="s">
         <v>1220</v>
       </c>
       <c r="B171" s="6" t="s">
         <v>1221</v>
       </c>
-    </row>
-    <row r="172" spans="1:2">
+      <c r="C171" s="2" t="str">
+        <f xml:space="preserve"> A171 &amp; " " &amp; B171</f>
+        <v>XPT 铂（一盎司）</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3">
       <c r="A172" s="5" t="s">
         <v>1222</v>
       </c>
       <c r="B172" s="6" t="s">
         <v>1223</v>
       </c>
-    </row>
-    <row r="173" spans="1:2">
+      <c r="C172" s="2" t="str">
+        <f xml:space="preserve"> A172 &amp; " " &amp; B172</f>
+        <v>XSU 厄瓜多尔苏克雷</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3">
       <c r="A173" s="5" t="s">
         <v>1224</v>
       </c>
       <c r="B173" s="6" t="s">
         <v>1225</v>
       </c>
-    </row>
-    <row r="174" spans="1:2">
+      <c r="C173" s="2" t="str">
+        <f xml:space="preserve"> A173 &amp; " " &amp; B173</f>
+        <v>XTS 为测试保留的代码</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3">
       <c r="A174" s="5" t="s">
         <v>1226</v>
       </c>
       <c r="B174" s="6" t="s">
         <v>1227</v>
       </c>
-    </row>
-    <row r="175" spans="1:2">
+      <c r="C174" s="2" t="str">
+        <f xml:space="preserve"> A174 &amp; " " &amp; B174</f>
+        <v>XUA 非洲开发银行账户单位</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3">
       <c r="A175" s="5" t="s">
         <v>1228</v>
       </c>
       <c r="B175" s="6" t="s">
         <v>1229</v>
       </c>
-    </row>
-    <row r="176" spans="1:2">
+      <c r="C175" s="2" t="str">
+        <f xml:space="preserve"> A175 &amp; " " &amp; B175</f>
+        <v>XXX 非货币交易单位</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3">
       <c r="A176" s="5" t="s">
         <v>1230</v>
       </c>
       <c r="B176" s="6" t="s">
         <v>1231</v>
       </c>
-    </row>
-    <row r="177" spans="1:2">
+      <c r="C176" s="2" t="str">
+        <f xml:space="preserve"> A176 &amp; " " &amp; B176</f>
+        <v>YER 也门里亚尔</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3">
       <c r="A177" s="5" t="s">
         <v>1232</v>
       </c>
       <c r="B177" s="6" t="s">
         <v>1233</v>
       </c>
-    </row>
-    <row r="178" spans="1:2">
+      <c r="C177" s="2" t="str">
+        <f xml:space="preserve"> A177 &amp; " " &amp; B177</f>
+        <v>ZAR 南非兰特</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3">
       <c r="A178" s="5" t="s">
         <v>1234</v>
       </c>
       <c r="B178" s="6" t="s">
         <v>1235</v>
       </c>
-    </row>
-    <row r="179" spans="1:2">
+      <c r="C178" s="2" t="str">
+        <f xml:space="preserve"> A178 &amp; " " &amp; B178</f>
+        <v>ZMW 赞比亚克瓦查</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3">
       <c r="A179" s="7" t="s">
         <v>1236</v>
       </c>
       <c r="B179" s="8" t="s">
         <v>1237</v>
+      </c>
+      <c r="C179" s="2" t="str">
+        <f xml:space="preserve"> A179 &amp; " " &amp; B179</f>
+        <v>ZWL 津巴布韦元</v>
       </c>
     </row>
   </sheetData>
